--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127291489</v>
+        <v>127295019</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437044</v>
+        <v>437299</v>
       </c>
       <c r="R2" t="n">
-        <v>6763790</v>
+        <v>6763962</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,60 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127290437</v>
+        <v>127293337</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437157</v>
+        <v>437130</v>
       </c>
       <c r="R3" t="n">
-        <v>6763806</v>
+        <v>6763889</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +902,7 @@
         <v>127295759</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295923</v>
+        <v>127293774</v>
       </c>
       <c r="B5" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437244</v>
+        <v>437187</v>
       </c>
       <c r="R5" t="n">
-        <v>6763901</v>
+        <v>6763964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294422</v>
+        <v>127295923</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437193</v>
+        <v>437244</v>
       </c>
       <c r="R6" t="n">
-        <v>6764064</v>
+        <v>6763901</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,65 +1208,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295019</v>
+        <v>127294146</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437299</v>
+        <v>437131</v>
       </c>
       <c r="R7" t="n">
-        <v>6763962</v>
+        <v>6764010</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,62 +1315,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127293337</v>
+        <v>127294422</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437130</v>
+        <v>437193</v>
       </c>
       <c r="R8" t="n">
-        <v>6763889</v>
+        <v>6764064</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295045</v>
+        <v>127291489</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437295</v>
+        <v>437044</v>
       </c>
       <c r="R9" t="n">
-        <v>6763947</v>
+        <v>6763790</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127293774</v>
+        <v>127290437</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437187</v>
+        <v>437157</v>
       </c>
       <c r="R10" t="n">
-        <v>6763964</v>
+        <v>6763806</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127294146</v>
+        <v>127295045</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,17 +1679,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437131</v>
+        <v>437295</v>
       </c>
       <c r="R11" t="n">
-        <v>6764010</v>
+        <v>6763947</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294041</v>
+        <v>127294354</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437152</v>
+        <v>437188</v>
       </c>
       <c r="R12" t="n">
-        <v>6764014</v>
+        <v>6764029</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,12 +1850,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1865,7 +1865,7 @@
         <v>127294721</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294738</v>
+        <v>127291056</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437220</v>
+        <v>437040</v>
       </c>
       <c r="R14" t="n">
-        <v>6764061</v>
+        <v>6763751</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,22 +2064,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127294354</v>
+        <v>127294041</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,17 +2107,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437188</v>
+        <v>437152</v>
       </c>
       <c r="R15" t="n">
-        <v>6764029</v>
+        <v>6764014</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,22 +2171,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127291056</v>
+        <v>127294738</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,17 +2214,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437040</v>
+        <v>437220</v>
       </c>
       <c r="R16" t="n">
-        <v>6763751</v>
+        <v>6764061</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,22 +2278,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127291525</v>
+        <v>127293263</v>
       </c>
       <c r="B17" t="n">
-        <v>79629</v>
+        <v>91345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437044</v>
+        <v>437138</v>
       </c>
       <c r="R17" t="n">
-        <v>6763790</v>
+        <v>6763887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293263</v>
+        <v>127293099</v>
       </c>
       <c r="B18" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437138</v>
+        <v>437109</v>
       </c>
       <c r="R18" t="n">
-        <v>6763887</v>
+        <v>6763908</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127293099</v>
+        <v>127291525</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437109</v>
+        <v>437044</v>
       </c>
       <c r="R19" t="n">
-        <v>6763908</v>
+        <v>6763790</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>127294351</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,48 +2718,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295240</v>
+        <v>127295941</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437308</v>
+        <v>437223</v>
       </c>
       <c r="R21" t="n">
-        <v>6763966</v>
+        <v>6763922</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2932,48 +2932,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295941</v>
+        <v>127295240</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437223</v>
+        <v>437308</v>
       </c>
       <c r="R23" t="n">
-        <v>6763922</v>
+        <v>6763966</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,22 +3027,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293820</v>
+        <v>127293735</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,39 +3050,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437201</v>
+        <v>437156</v>
       </c>
       <c r="R24" t="n">
-        <v>6763976</v>
+        <v>6763978</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3151,48 +3146,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127292736</v>
+        <v>127295078</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436991</v>
+        <v>437293</v>
       </c>
       <c r="R25" t="n">
-        <v>6763816</v>
+        <v>6763940</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,22 +3241,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127293735</v>
+        <v>127294346</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,17 +3284,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437156</v>
+        <v>437187</v>
       </c>
       <c r="R26" t="n">
-        <v>6763978</v>
+        <v>6764029</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3328,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,57 +3348,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293161</v>
+        <v>127293820</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437098</v>
+        <v>437201</v>
       </c>
       <c r="R27" t="n">
-        <v>6763941</v>
+        <v>6763976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,53 +3472,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127293241</v>
+        <v>127295384</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437135</v>
+        <v>437233</v>
       </c>
       <c r="R28" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,57 +3572,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295078</v>
+        <v>127293241</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437293</v>
+        <v>437135</v>
       </c>
       <c r="R29" t="n">
-        <v>6763940</v>
+        <v>6763885</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3654,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3664,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,50 +3696,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295384</v>
+        <v>127293161</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437233</v>
+        <v>437098</v>
       </c>
       <c r="R30" t="n">
-        <v>6763867</v>
+        <v>6763941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3803,48 +3803,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127294346</v>
+        <v>127292736</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437187</v>
+        <v>436991</v>
       </c>
       <c r="R31" t="n">
-        <v>6764029</v>
+        <v>6763816</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,12 +3898,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
         <v>127293914</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>127293203</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293696</v>
+        <v>127295057</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4155,17 +4155,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437156</v>
+        <v>437295</v>
       </c>
       <c r="R34" t="n">
-        <v>6763982</v>
+        <v>6763942</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,22 +4219,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127293981</v>
+        <v>127293696</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437177</v>
+        <v>437156</v>
       </c>
       <c r="R35" t="n">
-        <v>6764017</v>
+        <v>6763982</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,53 +4338,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294136</v>
+        <v>127293981</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437182</v>
+        <v>437177</v>
       </c>
       <c r="R36" t="n">
-        <v>6763976</v>
+        <v>6764017</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,57 +4433,62 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295057</v>
+        <v>127294136</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437295</v>
+        <v>437182</v>
       </c>
       <c r="R37" t="n">
-        <v>6763942</v>
+        <v>6763976</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127291424</v>
+        <v>127292669</v>
       </c>
       <c r="B38" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437058</v>
+        <v>437023</v>
       </c>
       <c r="R38" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127293212</v>
+        <v>127295245</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437120</v>
+        <v>437308</v>
       </c>
       <c r="R39" t="n">
-        <v>6763919</v>
+        <v>6763966</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127292669</v>
+        <v>127292954</v>
       </c>
       <c r="B40" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,37 +4782,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437023</v>
+        <v>437050</v>
       </c>
       <c r="R40" t="n">
-        <v>6763818</v>
+        <v>6763860</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,22 +4866,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295245</v>
+        <v>127290586</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,17 +4909,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437308</v>
+        <v>437065</v>
       </c>
       <c r="R41" t="n">
-        <v>6763966</v>
+        <v>6763754</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,22 +4973,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127292954</v>
+        <v>127291424</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4996,37 +4996,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437050</v>
+        <v>437058</v>
       </c>
       <c r="R42" t="n">
-        <v>6763860</v>
+        <v>6763796</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,60 +5080,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127290586</v>
+        <v>127293212</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437065</v>
+        <v>437120</v>
       </c>
       <c r="R43" t="n">
-        <v>6763754</v>
+        <v>6763919</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,12 +5187,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5306,10 +5306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127291031</v>
+        <v>127292927</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437097</v>
+        <v>437032</v>
       </c>
       <c r="R45" t="n">
-        <v>6763850</v>
+        <v>6763858</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127293956</v>
+        <v>127294741</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5444,17 +5444,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437202</v>
+        <v>437209</v>
       </c>
       <c r="R46" t="n">
-        <v>6764007</v>
+        <v>6764061</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5508,22 +5508,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292927</v>
+        <v>127292980</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,17 +5551,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437032</v>
+        <v>437068</v>
       </c>
       <c r="R47" t="n">
         <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,44 +5615,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127290540</v>
+        <v>127295897</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437113</v>
+        <v>437244</v>
       </c>
       <c r="R48" t="n">
-        <v>6763817</v>
+        <v>6763890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127290803</v>
+        <v>127293956</v>
       </c>
       <c r="B49" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,39 +5745,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437091</v>
+        <v>437202</v>
       </c>
       <c r="R49" t="n">
-        <v>6763822</v>
+        <v>6764007</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,10 +5841,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127294741</v>
+        <v>127291031</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,17 +5872,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437209</v>
+        <v>437097</v>
       </c>
       <c r="R50" t="n">
-        <v>6764061</v>
+        <v>6763850</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5916,7 +5911,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5926,7 +5921,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5941,22 +5936,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127292980</v>
+        <v>127290803</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,37 +5959,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437068</v>
+        <v>437091</v>
       </c>
       <c r="R51" t="n">
-        <v>6763858</v>
+        <v>6763822</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6048,44 +6048,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127295897</v>
+        <v>127290540</v>
       </c>
       <c r="B52" t="n">
-        <v>91339</v>
+        <v>8447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437244</v>
+        <v>437113</v>
       </c>
       <c r="R52" t="n">
-        <v>6763890</v>
+        <v>6763817</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6274,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127293209</v>
+        <v>127291397</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437116</v>
+        <v>437058</v>
       </c>
       <c r="R54" t="n">
-        <v>6763949</v>
+        <v>6763796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127291397</v>
+        <v>127290094</v>
       </c>
       <c r="B55" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437058</v>
+        <v>437239</v>
       </c>
       <c r="R55" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,6 +6462,11 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6491,7 +6496,7 @@
         <v>127290996</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6595,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127290094</v>
+        <v>127293209</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6630,13 +6635,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437239</v>
+        <v>437116</v>
       </c>
       <c r="R57" t="n">
-        <v>6763818</v>
+        <v>6763949</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6676,11 +6681,6 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6710,7 +6710,7 @@
         <v>127291537</v>
       </c>
       <c r="B58" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6814,48 +6814,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127293858</v>
+        <v>127294772</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437201</v>
+        <v>437255</v>
       </c>
       <c r="R59" t="n">
-        <v>6763976</v>
+        <v>6764049</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6909,22 +6909,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127293072</v>
+        <v>127294736</v>
       </c>
       <c r="B60" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6932,37 +6932,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437081</v>
+        <v>437212</v>
       </c>
       <c r="R60" t="n">
-        <v>6763901</v>
+        <v>6764065</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7016,22 +7016,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294416</v>
+        <v>127294985</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7059,17 +7059,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437158</v>
+        <v>437293</v>
       </c>
       <c r="R61" t="n">
-        <v>6764069</v>
+        <v>6763965</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7123,22 +7123,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294772</v>
+        <v>127294411</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437255</v>
+        <v>437202</v>
       </c>
       <c r="R62" t="n">
-        <v>6764049</v>
+        <v>6764041</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7242,10 +7242,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127294736</v>
+        <v>127294416</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7273,17 +7273,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437212</v>
+        <v>437158</v>
       </c>
       <c r="R63" t="n">
-        <v>6764065</v>
+        <v>6764069</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7337,62 +7337,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127290454</v>
+        <v>127295806</v>
       </c>
       <c r="B64" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437078</v>
+        <v>437212</v>
       </c>
       <c r="R64" t="n">
-        <v>6763737</v>
+        <v>6763955</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -7424,7 +7419,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7429,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7461,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127294985</v>
+        <v>127293072</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7472,37 +7467,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437293</v>
+        <v>437081</v>
       </c>
       <c r="R65" t="n">
-        <v>6763965</v>
+        <v>6763901</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7531,7 +7526,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7536,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7556,60 +7551,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127294411</v>
+        <v>127293858</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437202</v>
+        <v>437201</v>
       </c>
       <c r="R66" t="n">
-        <v>6764041</v>
+        <v>6763976</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7638,7 +7633,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7643,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7663,57 +7658,62 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127295806</v>
+        <v>127290454</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437212</v>
+        <v>437078</v>
       </c>
       <c r="R67" t="n">
-        <v>6763955</v>
+        <v>6763737</v>
       </c>
       <c r="S67" t="n">
         <v>9</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,32 +7782,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290959</v>
+        <v>127290713</v>
       </c>
       <c r="B68" t="n">
-        <v>91339</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437097</v>
+        <v>437108</v>
       </c>
       <c r="R68" t="n">
-        <v>6763868</v>
+        <v>6763809</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8103,32 +8103,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290713</v>
+        <v>127290826</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R71" t="n">
-        <v>6763809</v>
+        <v>6763837</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127290826</v>
+        <v>127290751</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8241,17 +8241,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437081</v>
+        <v>437062</v>
       </c>
       <c r="R72" t="n">
-        <v>6763837</v>
+        <v>6763738</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,22 +8305,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127290751</v>
+        <v>127290959</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437062</v>
+        <v>437097</v>
       </c>
       <c r="R73" t="n">
-        <v>6763738</v>
+        <v>6763868</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8412,12 +8412,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
         <v>127294334</v>
       </c>
       <c r="B74" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127294842</v>
+        <v>127295799</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437280</v>
+        <v>437234</v>
       </c>
       <c r="R75" t="n">
-        <v>6764030</v>
+        <v>6763858</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127295799</v>
+        <v>127294842</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437234</v>
+        <v>437280</v>
       </c>
       <c r="R76" t="n">
-        <v>6763858</v>
+        <v>6764030</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8857,10 +8857,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293897</v>
+        <v>127290717</v>
       </c>
       <c r="B78" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,34 +8868,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437180</v>
+        <v>437108</v>
       </c>
       <c r="R78" t="n">
-        <v>6763986</v>
+        <v>6763809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8964,32 +8969,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293677</v>
+        <v>127293090</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8999,10 +9004,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437148</v>
+        <v>437081</v>
       </c>
       <c r="R79" t="n">
-        <v>6764001</v>
+        <v>6763901</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9071,10 +9076,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293789</v>
+        <v>127293897</v>
       </c>
       <c r="B80" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9106,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437218</v>
+        <v>437180</v>
       </c>
       <c r="R80" t="n">
-        <v>6763950</v>
+        <v>6763986</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9178,10 +9183,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127293504</v>
+        <v>127293677</v>
       </c>
       <c r="B81" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9213,10 +9218,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437136</v>
+        <v>437148</v>
       </c>
       <c r="R81" t="n">
-        <v>6763963</v>
+        <v>6764001</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9285,32 +9290,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293090</v>
+        <v>127293789</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9320,10 +9325,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437081</v>
+        <v>437218</v>
       </c>
       <c r="R82" t="n">
-        <v>6763901</v>
+        <v>6763950</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9392,10 +9397,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127290717</v>
+        <v>127294716</v>
       </c>
       <c r="B83" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9403,42 +9408,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437108</v>
+        <v>437199</v>
       </c>
       <c r="R83" t="n">
-        <v>6763809</v>
+        <v>6764063</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,22 +9492,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127294716</v>
+        <v>127293504</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9535,17 +9535,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437199</v>
+        <v>437136</v>
       </c>
       <c r="R84" t="n">
-        <v>6764063</v>
+        <v>6763963</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,12 +9599,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9614,7 +9614,7 @@
         <v>127294433</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9718,10 +9718,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127293022</v>
+        <v>127290757</v>
       </c>
       <c r="B86" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9749,17 +9749,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437081</v>
+        <v>437058</v>
       </c>
       <c r="R86" t="n">
-        <v>6763901</v>
+        <v>6763741</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,44 +9813,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127292999</v>
+        <v>127295596</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437093</v>
+        <v>437169</v>
       </c>
       <c r="R87" t="n">
-        <v>6763880</v>
+        <v>6763904</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9932,10 +9932,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127291960</v>
+        <v>127295863</v>
       </c>
       <c r="B88" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,17 +9963,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437015</v>
+        <v>437221</v>
       </c>
       <c r="R88" t="n">
-        <v>6763762</v>
+        <v>6763950</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,60 +10027,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127292822</v>
+        <v>127292924</v>
       </c>
       <c r="B89" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436992</v>
+        <v>437037</v>
       </c>
       <c r="R89" t="n">
-        <v>6763834</v>
+        <v>6763860</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10134,22 +10134,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127290757</v>
+        <v>127291960</v>
       </c>
       <c r="B90" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10177,17 +10177,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437058</v>
+        <v>437015</v>
       </c>
       <c r="R90" t="n">
-        <v>6763741</v>
+        <v>6763762</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10241,22 +10241,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127295596</v>
+        <v>127295035</v>
       </c>
       <c r="B91" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10284,17 +10284,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437169</v>
+        <v>437297</v>
       </c>
       <c r="R91" t="n">
-        <v>6763904</v>
+        <v>6763951</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,22 +10348,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127295863</v>
+        <v>127293022</v>
       </c>
       <c r="B92" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10391,17 +10391,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437221</v>
+        <v>437081</v>
       </c>
       <c r="R92" t="n">
-        <v>6763950</v>
+        <v>6763901</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10455,60 +10455,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127292924</v>
+        <v>127292822</v>
       </c>
       <c r="B93" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437037</v>
+        <v>436992</v>
       </c>
       <c r="R93" t="n">
-        <v>6763860</v>
+        <v>6763834</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10562,60 +10562,60 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127295035</v>
+        <v>127292999</v>
       </c>
       <c r="B94" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437297</v>
+        <v>437093</v>
       </c>
       <c r="R94" t="n">
-        <v>6763951</v>
+        <v>6763880</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,12 +10669,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293029</v>
+        <v>127293586</v>
       </c>
       <c r="B96" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10819,17 +10819,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437074</v>
+        <v>437163</v>
       </c>
       <c r="R96" t="n">
-        <v>6763890</v>
+        <v>6763902</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10883,22 +10883,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293586</v>
+        <v>127293953</v>
       </c>
       <c r="B97" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10906,34 +10906,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437163</v>
+        <v>437190</v>
       </c>
       <c r="R97" t="n">
-        <v>6763902</v>
+        <v>6763937</v>
       </c>
       <c r="S97" t="n">
         <v>9</v>
@@ -10965,7 +10974,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10975,7 +10984,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11002,53 +11011,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127295309</v>
+        <v>127293371</v>
       </c>
       <c r="B98" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437289</v>
+        <v>437140</v>
       </c>
       <c r="R98" t="n">
-        <v>6763874</v>
+        <v>6763931</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11114,10 +11118,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293953</v>
+        <v>127293249</v>
       </c>
       <c r="B99" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11125,43 +11129,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437190</v>
+        <v>437134</v>
       </c>
       <c r="R99" t="n">
-        <v>6763937</v>
+        <v>6763889</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -11193,7 +11188,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11203,7 +11198,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11230,10 +11225,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293249</v>
+        <v>127293029</v>
       </c>
       <c r="B100" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11261,17 +11256,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437134</v>
+        <v>437074</v>
       </c>
       <c r="R100" t="n">
-        <v>6763889</v>
+        <v>6763890</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11300,7 +11295,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11310,7 +11305,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11325,22 +11320,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293348</v>
+        <v>127290978</v>
       </c>
       <c r="B101" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11348,39 +11343,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437154</v>
+        <v>437098</v>
       </c>
       <c r="R101" t="n">
-        <v>6763925</v>
+        <v>6763850</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11449,10 +11439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293371</v>
+        <v>127293348</v>
       </c>
       <c r="B102" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11460,34 +11450,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437140</v>
+        <v>437154</v>
       </c>
       <c r="R102" t="n">
-        <v>6763931</v>
+        <v>6763925</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11556,48 +11551,53 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127290978</v>
+        <v>127295309</v>
       </c>
       <c r="B103" t="n">
-        <v>79011</v>
+        <v>58027</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437098</v>
+        <v>437289</v>
       </c>
       <c r="R103" t="n">
-        <v>6763850</v>
+        <v>6763874</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11663,45 +11663,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127294008</v>
+        <v>127294074</v>
       </c>
       <c r="B104" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437190</v>
+        <v>437189</v>
       </c>
       <c r="R104" t="n">
-        <v>6763955</v>
+        <v>6763951</v>
       </c>
       <c r="S104" t="n">
         <v>9</v>
@@ -11733,7 +11738,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11743,7 +11748,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11770,7 +11775,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127294074</v>
+        <v>127293475</v>
       </c>
       <c r="B105" t="n">
         <v>8447</v>
@@ -11799,24 +11804,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>437189</v>
+        <v>437136</v>
       </c>
       <c r="R105" t="n">
-        <v>6763951</v>
+        <v>6763963</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11870,60 +11870,60 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127293475</v>
+        <v>127294008</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>437136</v>
+        <v>437190</v>
       </c>
       <c r="R106" t="n">
-        <v>6763963</v>
+        <v>6763955</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11977,12 +11977,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11992,7 +11992,7 @@
         <v>127292751</v>
       </c>
       <c r="B107" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>127291177</v>
       </c>
       <c r="B108" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12203,53 +12203,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127292727</v>
+        <v>127293290</v>
       </c>
       <c r="B109" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437043</v>
+        <v>437138</v>
       </c>
       <c r="R109" t="n">
-        <v>6763856</v>
+        <v>6763901</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12278,7 +12273,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12288,7 +12283,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12303,19 +12303,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127294388</v>
+        <v>127292727</v>
       </c>
       <c r="B110" t="n">
         <v>8447</v>
@@ -12344,16 +12344,21 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437183</v>
+        <v>437043</v>
       </c>
       <c r="R110" t="n">
-        <v>6764033</v>
+        <v>6763856</v>
       </c>
       <c r="S110" t="n">
         <v>9</v>
@@ -12385,7 +12390,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12395,7 +12400,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12422,32 +12427,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127293290</v>
+        <v>127290265</v>
       </c>
       <c r="B111" t="n">
-        <v>91339</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12457,10 +12462,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437138</v>
+        <v>437187</v>
       </c>
       <c r="R111" t="n">
-        <v>6763901</v>
+        <v>6763801</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12503,11 +12508,6 @@
       <c r="AB111" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12534,7 +12534,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127290265</v>
+        <v>127294388</v>
       </c>
       <c r="B112" t="n">
         <v>8447</v>
@@ -12565,17 +12565,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437187</v>
+        <v>437183</v>
       </c>
       <c r="R112" t="n">
-        <v>6763801</v>
+        <v>6764033</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12629,22 +12629,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293240</v>
+        <v>127293262</v>
       </c>
       <c r="B113" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12652,37 +12652,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437122</v>
+        <v>437131</v>
       </c>
       <c r="R113" t="n">
-        <v>6763905</v>
+        <v>6763892</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,60 +12736,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293766</v>
+        <v>127290747</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437187</v>
+        <v>437064</v>
       </c>
       <c r="R114" t="n">
-        <v>6763964</v>
+        <v>6763744</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12843,22 +12843,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127291635</v>
+        <v>127293240</v>
       </c>
       <c r="B115" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,21 +12866,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437032</v>
+        <v>437122</v>
       </c>
       <c r="R115" t="n">
-        <v>6763776</v>
+        <v>6763905</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12962,10 +12962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127293262</v>
+        <v>127294788</v>
       </c>
       <c r="B116" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12997,10 +12997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437131</v>
+        <v>437274</v>
       </c>
       <c r="R116" t="n">
-        <v>6763892</v>
+        <v>6764023</v>
       </c>
       <c r="S116" t="n">
         <v>9</v>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13069,10 +13069,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127290747</v>
+        <v>127291635</v>
       </c>
       <c r="B117" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437064</v>
+        <v>437032</v>
       </c>
       <c r="R117" t="n">
-        <v>6763744</v>
+        <v>6763776</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,60 +13164,60 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127294788</v>
+        <v>127293766</v>
       </c>
       <c r="B118" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437274</v>
+        <v>437187</v>
       </c>
       <c r="R118" t="n">
-        <v>6764023</v>
+        <v>6763964</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13271,22 +13271,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127290001</v>
+        <v>127291536</v>
       </c>
       <c r="B119" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13294,42 +13294,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>437239</v>
+        <v>436972</v>
       </c>
       <c r="R119" t="n">
-        <v>6763818</v>
+        <v>6763733</v>
       </c>
       <c r="S119" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13358,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13368,7 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13383,44 +13378,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127290203</v>
+        <v>127293427</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13430,10 +13425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437188</v>
+        <v>437147</v>
       </c>
       <c r="R120" t="n">
-        <v>6763793</v>
+        <v>6763942</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13476,11 +13471,6 @@
       <c r="AB120" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13507,32 +13497,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127290773</v>
+        <v>127293635</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13542,10 +13532,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437081</v>
+        <v>437130</v>
       </c>
       <c r="R121" t="n">
-        <v>6763812</v>
+        <v>6763988</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13614,10 +13604,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127291536</v>
+        <v>127290001</v>
       </c>
       <c r="B122" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13625,37 +13615,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436972</v>
+        <v>437239</v>
       </c>
       <c r="R122" t="n">
-        <v>6763733</v>
+        <v>6763818</v>
       </c>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13684,7 +13679,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13694,7 +13689,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13709,44 +13704,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127293427</v>
+        <v>127290203</v>
       </c>
       <c r="B123" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13756,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437147</v>
+        <v>437188</v>
       </c>
       <c r="R123" t="n">
-        <v>6763942</v>
+        <v>6763793</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13802,6 +13797,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13828,32 +13828,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127293635</v>
+        <v>127290773</v>
       </c>
       <c r="B124" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437130</v>
+        <v>437081</v>
       </c>
       <c r="R124" t="n">
-        <v>6763988</v>
+        <v>6763812</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13935,7 +13935,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127292816</v>
+        <v>127295889</v>
       </c>
       <c r="B125" t="n">
         <v>57654</v>
@@ -13966,7 +13966,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436992</v>
+        <v>437244</v>
       </c>
       <c r="R125" t="n">
-        <v>6763834</v>
+        <v>6763890</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14047,45 +14047,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127290736</v>
+        <v>127292816</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>437102</v>
+        <v>436992</v>
       </c>
       <c r="R126" t="n">
-        <v>6763801</v>
+        <v>6763834</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14271,50 +14276,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127295889</v>
+        <v>127290736</v>
       </c>
       <c r="B128" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437244</v>
+        <v>437102</v>
       </c>
       <c r="R128" t="n">
-        <v>6763890</v>
+        <v>6763801</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14495,10 +14495,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127292761</v>
+        <v>127293305</v>
       </c>
       <c r="B130" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14526,17 +14526,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436992</v>
+        <v>437137</v>
       </c>
       <c r="R130" t="n">
-        <v>6763834</v>
+        <v>6763885</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,44 +14590,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127295217</v>
+        <v>127292761</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437312</v>
+        <v>436992</v>
       </c>
       <c r="R131" t="n">
-        <v>6763984</v>
+        <v>6763834</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14712,7 +14712,7 @@
         <v>127294311</v>
       </c>
       <c r="B132" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15035,48 +15035,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127293305</v>
+        <v>127295217</v>
       </c>
       <c r="B135" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437137</v>
+        <v>437312</v>
       </c>
       <c r="R135" t="n">
-        <v>6763885</v>
+        <v>6763984</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15130,12 +15130,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295019</v>
+        <v>127295759</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437299</v>
+        <v>437218</v>
       </c>
       <c r="R2" t="n">
-        <v>6763962</v>
+        <v>6763878</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127293337</v>
+        <v>127295923</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437130</v>
+        <v>437244</v>
       </c>
       <c r="R3" t="n">
-        <v>6763889</v>
+        <v>6763901</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295759</v>
+        <v>127294146</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437218</v>
+        <v>437131</v>
       </c>
       <c r="R4" t="n">
-        <v>6763878</v>
+        <v>6764010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127293774</v>
+        <v>127294422</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1037,17 +1027,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437187</v>
+        <v>437193</v>
       </c>
       <c r="R5" t="n">
-        <v>6763964</v>
+        <v>6764064</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295923</v>
+        <v>127290437</v>
       </c>
       <c r="B6" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437244</v>
+        <v>437157</v>
       </c>
       <c r="R6" t="n">
-        <v>6763901</v>
+        <v>6763806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127294146</v>
+        <v>127295045</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1251,17 +1241,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437131</v>
+        <v>437295</v>
       </c>
       <c r="R7" t="n">
-        <v>6764010</v>
+        <v>6763947</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,57 +1305,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294422</v>
+        <v>127295019</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437193</v>
+        <v>437299</v>
       </c>
       <c r="R8" t="n">
-        <v>6764064</v>
+        <v>6763962</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127291489</v>
+        <v>127293774</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437044</v>
+        <v>437187</v>
       </c>
       <c r="R9" t="n">
-        <v>6763790</v>
+        <v>6763964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127290437</v>
+        <v>127291489</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437157</v>
+        <v>437044</v>
       </c>
       <c r="R10" t="n">
-        <v>6763806</v>
+        <v>6763790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,45 +1643,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295045</v>
+        <v>127293337</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437295</v>
+        <v>437130</v>
       </c>
       <c r="R11" t="n">
-        <v>6763947</v>
+        <v>6763889</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294354</v>
+        <v>127294721</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437188</v>
+        <v>437204</v>
       </c>
       <c r="R12" t="n">
-        <v>6764029</v>
+        <v>6764046</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,19 +1850,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294721</v>
+        <v>127294354</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437204</v>
+        <v>437188</v>
       </c>
       <c r="R13" t="n">
-        <v>6764046</v>
+        <v>6764029</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,12 +1957,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127293263</v>
+        <v>127293099</v>
       </c>
       <c r="B17" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437138</v>
+        <v>437109</v>
       </c>
       <c r="R17" t="n">
-        <v>6763887</v>
+        <v>6763908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293099</v>
+        <v>127291525</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437109</v>
+        <v>437044</v>
       </c>
       <c r="R18" t="n">
-        <v>6763908</v>
+        <v>6763790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127291525</v>
+        <v>127293263</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>91345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437044</v>
+        <v>437138</v>
       </c>
       <c r="R19" t="n">
-        <v>6763790</v>
+        <v>6763887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293735</v>
+        <v>127293820</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,34 +3050,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437156</v>
+        <v>437201</v>
       </c>
       <c r="R24" t="n">
-        <v>6763978</v>
+        <v>6763976</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295078</v>
+        <v>127295384</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,37 +3162,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437293</v>
+        <v>437233</v>
       </c>
       <c r="R25" t="n">
-        <v>6763940</v>
+        <v>6763867</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,12 +3251,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3360,10 +3370,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293820</v>
+        <v>127293735</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,39 +3381,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437201</v>
+        <v>437156</v>
       </c>
       <c r="R27" t="n">
-        <v>6763976</v>
+        <v>6763978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,10 +3477,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295384</v>
+        <v>127295078</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3483,42 +3488,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437233</v>
+        <v>437293</v>
       </c>
       <c r="R28" t="n">
-        <v>6763867</v>
+        <v>6763940</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,12 +3572,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127293914</v>
+        <v>127293203</v>
       </c>
       <c r="B32" t="n">
         <v>79014</v>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437190</v>
+        <v>437116</v>
       </c>
       <c r="R32" t="n">
-        <v>6763999</v>
+        <v>6763949</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293203</v>
+        <v>127293914</v>
       </c>
       <c r="B33" t="n">
         <v>79014</v>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437116</v>
+        <v>437190</v>
       </c>
       <c r="R33" t="n">
-        <v>6763949</v>
+        <v>6763999</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127292669</v>
+        <v>127293212</v>
       </c>
       <c r="B38" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437023</v>
+        <v>437120</v>
       </c>
       <c r="R38" t="n">
-        <v>6763818</v>
+        <v>6763919</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,48 +4664,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295245</v>
+        <v>127294037</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437308</v>
+        <v>437188</v>
       </c>
       <c r="R39" t="n">
-        <v>6763966</v>
+        <v>6763952</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,19 +4759,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127292954</v>
+        <v>127295245</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4802,17 +4802,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437050</v>
+        <v>437308</v>
       </c>
       <c r="R40" t="n">
-        <v>6763860</v>
+        <v>6763966</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,22 +4866,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127290586</v>
+        <v>127292669</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,37 +4889,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437065</v>
+        <v>437023</v>
       </c>
       <c r="R41" t="n">
-        <v>6763754</v>
+        <v>6763818</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,12 +4973,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5092,48 +5092,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127293212</v>
+        <v>127292954</v>
       </c>
       <c r="B43" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437120</v>
+        <v>437050</v>
       </c>
       <c r="R43" t="n">
-        <v>6763919</v>
+        <v>6763860</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,44 +5187,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127294037</v>
+        <v>127290586</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437188</v>
+        <v>437065</v>
       </c>
       <c r="R44" t="n">
-        <v>6763952</v>
+        <v>6763754</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5306,7 +5306,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127292927</v>
+        <v>127294741</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5337,17 +5337,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437032</v>
+        <v>437209</v>
       </c>
       <c r="R45" t="n">
-        <v>6763858</v>
+        <v>6764061</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5401,19 +5401,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127294741</v>
+        <v>127292980</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437209</v>
+        <v>437068</v>
       </c>
       <c r="R46" t="n">
-        <v>6764061</v>
+        <v>6763858</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292980</v>
+        <v>127295897</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,37 +5531,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437068</v>
+        <v>437244</v>
       </c>
       <c r="R47" t="n">
-        <v>6763858</v>
+        <v>6763890</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295897</v>
+        <v>127291031</v>
       </c>
       <c r="B48" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437244</v>
+        <v>437097</v>
       </c>
       <c r="R48" t="n">
-        <v>6763890</v>
+        <v>6763850</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127293956</v>
+        <v>127292927</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437202</v>
+        <v>437032</v>
       </c>
       <c r="R49" t="n">
-        <v>6764007</v>
+        <v>6763858</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127291031</v>
+        <v>127293956</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437097</v>
+        <v>437202</v>
       </c>
       <c r="R50" t="n">
-        <v>6763850</v>
+        <v>6764007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127291397</v>
+        <v>127290094</v>
       </c>
       <c r="B54" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437058</v>
+        <v>437239</v>
       </c>
       <c r="R54" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6355,6 +6355,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,10 +6386,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127290094</v>
+        <v>127291397</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6397,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6421,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437239</v>
+        <v>437058</v>
       </c>
       <c r="R55" t="n">
-        <v>6763818</v>
+        <v>6763796</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,11 +6467,6 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6707,32 +6707,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127291537</v>
+        <v>127293858</v>
       </c>
       <c r="B58" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437044</v>
+        <v>437201</v>
       </c>
       <c r="R58" t="n">
-        <v>6763790</v>
+        <v>6763976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,45 +6814,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294772</v>
+        <v>127290454</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437255</v>
+        <v>437078</v>
       </c>
       <c r="R59" t="n">
-        <v>6764049</v>
+        <v>6763737</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6884,7 +6889,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6899,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6921,7 +6926,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294736</v>
+        <v>127294772</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6956,10 +6961,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437212</v>
+        <v>437255</v>
       </c>
       <c r="R60" t="n">
-        <v>6764065</v>
+        <v>6764049</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -6991,7 +6996,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7006,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7028,7 +7033,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294985</v>
+        <v>127294736</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -7063,10 +7068,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437293</v>
+        <v>437212</v>
       </c>
       <c r="R61" t="n">
-        <v>6763965</v>
+        <v>6764065</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7098,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7135,7 +7140,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294411</v>
+        <v>127294985</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -7170,10 +7175,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437202</v>
+        <v>437293</v>
       </c>
       <c r="R62" t="n">
-        <v>6764041</v>
+        <v>6763965</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7205,7 +7210,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7215,7 +7220,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7242,7 +7247,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127294416</v>
+        <v>127294411</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -7273,17 +7278,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437158</v>
+        <v>437202</v>
       </c>
       <c r="R63" t="n">
-        <v>6764069</v>
+        <v>6764041</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,7 +7317,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7322,7 +7327,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7337,19 +7342,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127295806</v>
+        <v>127294416</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7380,17 +7385,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437212</v>
+        <v>437158</v>
       </c>
       <c r="R64" t="n">
-        <v>6763955</v>
+        <v>6764069</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7419,7 +7424,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7429,7 +7434,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7444,22 +7449,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127293072</v>
+        <v>127295806</v>
       </c>
       <c r="B65" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,37 +7472,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437081</v>
+        <v>437212</v>
       </c>
       <c r="R65" t="n">
-        <v>6763901</v>
+        <v>6763955</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7526,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7536,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7551,44 +7556,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127293858</v>
+        <v>127293072</v>
       </c>
       <c r="B66" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7598,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437201</v>
+        <v>437081</v>
       </c>
       <c r="R66" t="n">
-        <v>6763976</v>
+        <v>6763901</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7670,53 +7675,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127290454</v>
+        <v>127291537</v>
       </c>
       <c r="B67" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437078</v>
+        <v>437044</v>
       </c>
       <c r="R67" t="n">
-        <v>6763737</v>
+        <v>6763790</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,44 +7770,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290713</v>
+        <v>127290826</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R68" t="n">
-        <v>6763809</v>
+        <v>6763837</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127292742</v>
+        <v>127290713</v>
       </c>
       <c r="B69" t="n">
         <v>8447</v>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437089</v>
+        <v>437108</v>
       </c>
       <c r="R69" t="n">
-        <v>6763838</v>
+        <v>6763809</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7996,7 +7996,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127294714</v>
+        <v>127292742</v>
       </c>
       <c r="B70" t="n">
         <v>8447</v>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437204</v>
+        <v>437089</v>
       </c>
       <c r="R70" t="n">
-        <v>6764046</v>
+        <v>6763838</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,32 +8103,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290826</v>
+        <v>127294714</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437081</v>
+        <v>437204</v>
       </c>
       <c r="R71" t="n">
-        <v>6763837</v>
+        <v>6764046</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8638,48 +8638,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R76" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8708,7 +8713,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8723,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8733,65 +8738,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B77" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R77" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127290717</v>
+        <v>127293897</v>
       </c>
       <c r="B78" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,39 +8868,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437108</v>
+        <v>437180</v>
       </c>
       <c r="R78" t="n">
-        <v>6763809</v>
+        <v>6763986</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8969,48 +8964,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293090</v>
+        <v>127294716</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437081</v>
+        <v>437199</v>
       </c>
       <c r="R79" t="n">
-        <v>6763901</v>
+        <v>6764063</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9049,7 +9044,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9064,19 +9059,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293897</v>
+        <v>127293677</v>
       </c>
       <c r="B80" t="n">
         <v>79014</v>
@@ -9111,10 +9106,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437180</v>
+        <v>437148</v>
       </c>
       <c r="R80" t="n">
-        <v>6763986</v>
+        <v>6764001</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9183,7 +9178,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127293677</v>
+        <v>127293789</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -9218,10 +9213,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437148</v>
+        <v>437218</v>
       </c>
       <c r="R81" t="n">
-        <v>6764001</v>
+        <v>6763950</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9290,7 +9285,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293789</v>
+        <v>127293504</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -9325,10 +9320,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437218</v>
+        <v>437136</v>
       </c>
       <c r="R82" t="n">
-        <v>6763950</v>
+        <v>6763963</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9397,7 +9392,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294716</v>
+        <v>127294433</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -9432,10 +9427,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437199</v>
+        <v>437180</v>
       </c>
       <c r="R83" t="n">
-        <v>6764063</v>
+        <v>6764047</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -9467,7 +9462,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9477,7 +9472,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9504,10 +9499,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127293504</v>
+        <v>127290717</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9515,34 +9510,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437136</v>
+        <v>437108</v>
       </c>
       <c r="R84" t="n">
-        <v>6763963</v>
+        <v>6763809</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9611,48 +9611,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127294433</v>
+        <v>127293090</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437180</v>
+        <v>437081</v>
       </c>
       <c r="R85" t="n">
-        <v>6764047</v>
+        <v>6763901</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,12 +9706,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127295863</v>
+        <v>127291960</v>
       </c>
       <c r="B88" t="n">
         <v>79014</v>
@@ -9963,17 +9963,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437221</v>
+        <v>437015</v>
       </c>
       <c r="R88" t="n">
-        <v>6763950</v>
+        <v>6763762</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,19 +10027,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127292924</v>
+        <v>127293022</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -10070,17 +10070,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437037</v>
+        <v>437081</v>
       </c>
       <c r="R89" t="n">
-        <v>6763860</v>
+        <v>6763901</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10134,19 +10134,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127291960</v>
+        <v>127295863</v>
       </c>
       <c r="B90" t="n">
         <v>79014</v>
@@ -10177,17 +10177,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437015</v>
+        <v>437221</v>
       </c>
       <c r="R90" t="n">
-        <v>6763762</v>
+        <v>6763950</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10241,19 +10241,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127295035</v>
+        <v>127292924</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437297</v>
+        <v>437037</v>
       </c>
       <c r="R91" t="n">
-        <v>6763951</v>
+        <v>6763860</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10360,7 +10360,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127293022</v>
+        <v>127295035</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -10391,17 +10391,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437081</v>
+        <v>437297</v>
       </c>
       <c r="R92" t="n">
-        <v>6763901</v>
+        <v>6763951</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10455,12 +10455,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293586</v>
+        <v>127293348</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,37 +10799,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437163</v>
+        <v>437154</v>
       </c>
       <c r="R96" t="n">
-        <v>6763902</v>
+        <v>6763925</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10858,7 +10863,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10868,7 +10873,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10883,69 +10888,65 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293953</v>
+        <v>127295309</v>
       </c>
       <c r="B97" t="n">
-        <v>91345</v>
+        <v>58027</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437190</v>
+        <v>437289</v>
       </c>
       <c r="R97" t="n">
-        <v>6763937</v>
+        <v>6763874</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10974,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10984,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10999,19 +11000,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293371</v>
+        <v>127293586</v>
       </c>
       <c r="B98" t="n">
         <v>79014</v>
@@ -11042,17 +11043,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437140</v>
+        <v>437163</v>
       </c>
       <c r="R98" t="n">
-        <v>6763931</v>
+        <v>6763902</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11081,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11091,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11106,22 +11107,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293249</v>
+        <v>127293953</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11129,34 +11130,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437134</v>
+        <v>437190</v>
       </c>
       <c r="R99" t="n">
-        <v>6763889</v>
+        <v>6763937</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -11188,7 +11198,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11198,7 +11208,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11225,7 +11235,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293029</v>
+        <v>127293371</v>
       </c>
       <c r="B100" t="n">
         <v>79014</v>
@@ -11260,10 +11270,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437074</v>
+        <v>437140</v>
       </c>
       <c r="R100" t="n">
-        <v>6763890</v>
+        <v>6763931</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11332,7 +11342,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127290978</v>
+        <v>127293249</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11363,17 +11373,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437098</v>
+        <v>437134</v>
       </c>
       <c r="R101" t="n">
-        <v>6763850</v>
+        <v>6763889</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11402,7 +11412,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11412,7 +11422,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11427,22 +11437,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293348</v>
+        <v>127293029</v>
       </c>
       <c r="B102" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11450,39 +11460,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437154</v>
+        <v>437074</v>
       </c>
       <c r="R102" t="n">
-        <v>6763925</v>
+        <v>6763890</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11551,53 +11556,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127295309</v>
+        <v>127290978</v>
       </c>
       <c r="B103" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437289</v>
+        <v>437098</v>
       </c>
       <c r="R103" t="n">
-        <v>6763874</v>
+        <v>6763850</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11663,50 +11663,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127294074</v>
+        <v>127294008</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437189</v>
+        <v>437190</v>
       </c>
       <c r="R104" t="n">
-        <v>6763951</v>
+        <v>6763955</v>
       </c>
       <c r="S104" t="n">
         <v>9</v>
@@ -11738,7 +11733,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11748,7 +11743,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11775,32 +11770,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127293475</v>
+        <v>127292751</v>
       </c>
       <c r="B105" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11810,10 +11805,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>437136</v>
+        <v>436974</v>
       </c>
       <c r="R105" t="n">
-        <v>6763963</v>
+        <v>6763823</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11882,45 +11877,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127294008</v>
+        <v>127294074</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>437190</v>
+        <v>437189</v>
       </c>
       <c r="R106" t="n">
-        <v>6763955</v>
+        <v>6763951</v>
       </c>
       <c r="S106" t="n">
         <v>9</v>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11989,32 +11989,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127292751</v>
+        <v>127293475</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436974</v>
+        <v>437136</v>
       </c>
       <c r="R107" t="n">
-        <v>6763823</v>
+        <v>6763963</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12427,7 +12427,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127290265</v>
+        <v>127294388</v>
       </c>
       <c r="B111" t="n">
         <v>8447</v>
@@ -12458,17 +12458,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437187</v>
+        <v>437183</v>
       </c>
       <c r="R111" t="n">
-        <v>6763801</v>
+        <v>6764033</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12522,19 +12522,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127294388</v>
+        <v>127290265</v>
       </c>
       <c r="B112" t="n">
         <v>8447</v>
@@ -12565,17 +12565,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437183</v>
+        <v>437187</v>
       </c>
       <c r="R112" t="n">
-        <v>6764033</v>
+        <v>6763801</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12629,19 +12629,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293262</v>
+        <v>127291635</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12672,17 +12672,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437131</v>
+        <v>437032</v>
       </c>
       <c r="R113" t="n">
-        <v>6763892</v>
+        <v>6763776</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,19 +12736,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127290747</v>
+        <v>127293262</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437064</v>
+        <v>437131</v>
       </c>
       <c r="R114" t="n">
-        <v>6763744</v>
+        <v>6763892</v>
       </c>
       <c r="S114" t="n">
         <v>9</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12855,10 +12855,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127293240</v>
+        <v>127290747</v>
       </c>
       <c r="B115" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437122</v>
+        <v>437064</v>
       </c>
       <c r="R115" t="n">
-        <v>6763905</v>
+        <v>6763744</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127294788</v>
+        <v>127293240</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437274</v>
+        <v>437122</v>
       </c>
       <c r="R116" t="n">
-        <v>6764023</v>
+        <v>6763905</v>
       </c>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,19 +13057,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127291635</v>
+        <v>127294788</v>
       </c>
       <c r="B117" t="n">
         <v>79014</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437032</v>
+        <v>437274</v>
       </c>
       <c r="R117" t="n">
-        <v>6763776</v>
+        <v>6764023</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,12 +13164,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13283,7 +13283,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127291536</v>
+        <v>127293427</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -13314,17 +13314,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436972</v>
+        <v>437147</v>
       </c>
       <c r="R119" t="n">
-        <v>6763733</v>
+        <v>6763942</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13378,19 +13378,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127293427</v>
+        <v>127291536</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13421,17 +13421,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437147</v>
+        <v>436972</v>
       </c>
       <c r="R120" t="n">
-        <v>6763942</v>
+        <v>6763733</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13485,12 +13485,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13604,53 +13604,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290001</v>
+        <v>127290203</v>
       </c>
       <c r="B122" t="n">
-        <v>57817</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437239</v>
+        <v>437188</v>
       </c>
       <c r="R122" t="n">
-        <v>6763818</v>
+        <v>6763793</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13690,6 +13685,11 @@
       <c r="AB122" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13716,7 +13716,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290203</v>
+        <v>127290773</v>
       </c>
       <c r="B123" t="n">
         <v>8447</v>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437188</v>
+        <v>437081</v>
       </c>
       <c r="R123" t="n">
-        <v>6763793</v>
+        <v>6763812</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,11 +13797,6 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13828,48 +13823,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290773</v>
+        <v>127290001</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57817</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437081</v>
+        <v>437239</v>
       </c>
       <c r="R124" t="n">
-        <v>6763812</v>
+        <v>6763818</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127293305</v>
+        <v>127292761</v>
       </c>
       <c r="B130" t="n">
         <v>79014</v>
@@ -14526,17 +14526,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437137</v>
+        <v>436992</v>
       </c>
       <c r="R130" t="n">
-        <v>6763885</v>
+        <v>6763834</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,44 +14590,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127292761</v>
+        <v>127295386</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436992</v>
+        <v>437233</v>
       </c>
       <c r="R131" t="n">
-        <v>6763834</v>
+        <v>6763867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14709,48 +14709,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127294311</v>
+        <v>127294021</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437170</v>
+        <v>437191</v>
       </c>
       <c r="R132" t="n">
-        <v>6764043</v>
+        <v>6763952</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14789,12 +14789,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14809,19 +14804,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295386</v>
+        <v>127295217</v>
       </c>
       <c r="B133" t="n">
         <v>8447</v>
@@ -14856,10 +14851,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437233</v>
+        <v>437312</v>
       </c>
       <c r="R133" t="n">
-        <v>6763867</v>
+        <v>6763984</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14928,7 +14923,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127294021</v>
+        <v>127293270</v>
       </c>
       <c r="B134" t="n">
         <v>8447</v>
@@ -14963,10 +14958,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437191</v>
+        <v>437124</v>
       </c>
       <c r="R134" t="n">
-        <v>6763952</v>
+        <v>6763885</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14998,7 +14993,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15008,7 +15003,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15035,48 +15030,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127295217</v>
+        <v>127293305</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437312</v>
+        <v>437137</v>
       </c>
       <c r="R135" t="n">
-        <v>6763984</v>
+        <v>6763885</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15105,7 +15100,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15115,7 +15110,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15130,60 +15125,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127293270</v>
+        <v>127294311</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437124</v>
+        <v>437170</v>
       </c>
       <c r="R136" t="n">
-        <v>6763885</v>
+        <v>6764043</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15212,7 +15207,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15222,7 +15217,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -4017,48 +4017,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293914</v>
+        <v>127294136</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437190</v>
+        <v>437182</v>
       </c>
       <c r="R33" t="n">
-        <v>6763999</v>
+        <v>6763976</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4087,7 +4092,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4102,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,19 +4117,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295057</v>
+        <v>127293914</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4155,17 +4160,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437295</v>
+        <v>437190</v>
       </c>
       <c r="R34" t="n">
-        <v>6763942</v>
+        <v>6763999</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,19 +4224,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127293696</v>
+        <v>127295057</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -4262,17 +4267,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437156</v>
+        <v>437295</v>
       </c>
       <c r="R35" t="n">
-        <v>6763982</v>
+        <v>6763942</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4301,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,19 +4331,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293981</v>
+        <v>127293696</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4373,10 +4378,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437177</v>
+        <v>437156</v>
       </c>
       <c r="R36" t="n">
-        <v>6764017</v>
+        <v>6763982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4445,53 +4450,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294136</v>
+        <v>127293981</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437182</v>
+        <v>437177</v>
       </c>
       <c r="R37" t="n">
-        <v>6763976</v>
+        <v>6764017</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,44 +4545,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127293212</v>
+        <v>127295245</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437120</v>
+        <v>437308</v>
       </c>
       <c r="R38" t="n">
-        <v>6763919</v>
+        <v>6763966</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,48 +4664,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294037</v>
+        <v>127292669</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437188</v>
+        <v>437023</v>
       </c>
       <c r="R39" t="n">
-        <v>6763952</v>
+        <v>6763818</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,22 +4759,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295245</v>
+        <v>127291424</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437308</v>
+        <v>437058</v>
       </c>
       <c r="R40" t="n">
-        <v>6763966</v>
+        <v>6763796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127292669</v>
+        <v>127293212</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437023</v>
+        <v>437120</v>
       </c>
       <c r="R41" t="n">
-        <v>6763818</v>
+        <v>6763919</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,48 +4985,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127291424</v>
+        <v>127294037</v>
       </c>
       <c r="B42" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437058</v>
+        <v>437188</v>
       </c>
       <c r="R42" t="n">
-        <v>6763796</v>
+        <v>6763952</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,12 +5080,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5306,7 +5306,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127294741</v>
+        <v>127292927</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5337,17 +5337,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437209</v>
+        <v>437032</v>
       </c>
       <c r="R45" t="n">
-        <v>6764061</v>
+        <v>6763858</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5401,19 +5401,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127292980</v>
+        <v>127293956</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5444,17 +5444,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437068</v>
+        <v>437202</v>
       </c>
       <c r="R46" t="n">
-        <v>6763858</v>
+        <v>6764007</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5508,22 +5508,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295897</v>
+        <v>127294741</v>
       </c>
       <c r="B47" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,37 +5531,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437244</v>
+        <v>437209</v>
       </c>
       <c r="R47" t="n">
-        <v>6763890</v>
+        <v>6764061</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,19 +5615,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127291031</v>
+        <v>127292980</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5658,17 +5658,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437097</v>
+        <v>437068</v>
       </c>
       <c r="R48" t="n">
-        <v>6763850</v>
+        <v>6763858</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,22 +5722,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127292927</v>
+        <v>127295897</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437032</v>
+        <v>437244</v>
       </c>
       <c r="R49" t="n">
-        <v>6763858</v>
+        <v>6763890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127293956</v>
+        <v>127291031</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437202</v>
+        <v>437097</v>
       </c>
       <c r="R50" t="n">
-        <v>6764007</v>
+        <v>6763850</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7889,48 +7889,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127290713</v>
+        <v>127290751</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437108</v>
+        <v>437062</v>
       </c>
       <c r="R69" t="n">
-        <v>6763809</v>
+        <v>6763738</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,44 +7984,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127292742</v>
+        <v>127290959</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437089</v>
+        <v>437097</v>
       </c>
       <c r="R70" t="n">
-        <v>6763838</v>
+        <v>6763868</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,7 +8103,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127294714</v>
+        <v>127290713</v>
       </c>
       <c r="B71" t="n">
         <v>8447</v>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437204</v>
+        <v>437108</v>
       </c>
       <c r="R71" t="n">
-        <v>6764046</v>
+        <v>6763809</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,48 +8210,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127290751</v>
+        <v>127292742</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437062</v>
+        <v>437089</v>
       </c>
       <c r="R72" t="n">
-        <v>6763738</v>
+        <v>6763838</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,44 +8305,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B73" t="n">
-        <v>91345</v>
+        <v>8447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R73" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -12096,48 +12096,53 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127291177</v>
+        <v>127292727</v>
       </c>
       <c r="B108" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437081</v>
+        <v>437043</v>
       </c>
       <c r="R108" t="n">
-        <v>6763837</v>
+        <v>6763856</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12166,7 +12171,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12176,7 +12181,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12191,44 +12196,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127293290</v>
+        <v>127290265</v>
       </c>
       <c r="B109" t="n">
-        <v>91345</v>
+        <v>8447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437138</v>
+        <v>437187</v>
       </c>
       <c r="R109" t="n">
-        <v>6763901</v>
+        <v>6763801</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12284,11 +12289,6 @@
       <c r="AB109" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12315,7 +12315,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127292727</v>
+        <v>127294388</v>
       </c>
       <c r="B110" t="n">
         <v>8447</v>
@@ -12344,21 +12344,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437043</v>
+        <v>437183</v>
       </c>
       <c r="R110" t="n">
-        <v>6763856</v>
+        <v>6764033</v>
       </c>
       <c r="S110" t="n">
         <v>9</v>
@@ -12390,7 +12385,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12400,7 +12395,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12427,48 +12422,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127294388</v>
+        <v>127291177</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437183</v>
+        <v>437081</v>
       </c>
       <c r="R111" t="n">
-        <v>6764033</v>
+        <v>6763837</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12497,7 +12492,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12507,7 +12502,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12522,44 +12517,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127290265</v>
+        <v>127293290</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>91345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12569,10 +12564,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437187</v>
+        <v>437138</v>
       </c>
       <c r="R112" t="n">
-        <v>6763801</v>
+        <v>6763901</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12615,6 +12610,11 @@
       <c r="AB112" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12641,32 +12641,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127291635</v>
+        <v>127293766</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437032</v>
+        <v>437187</v>
       </c>
       <c r="R113" t="n">
-        <v>6763776</v>
+        <v>6763964</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12748,7 +12748,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293262</v>
+        <v>127291635</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12779,17 +12779,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437131</v>
+        <v>437032</v>
       </c>
       <c r="R114" t="n">
-        <v>6763892</v>
+        <v>6763776</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12843,19 +12843,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127290747</v>
+        <v>127293262</v>
       </c>
       <c r="B115" t="n">
         <v>79014</v>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437064</v>
+        <v>437131</v>
       </c>
       <c r="R115" t="n">
-        <v>6763744</v>
+        <v>6763892</v>
       </c>
       <c r="S115" t="n">
         <v>9</v>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12962,10 +12962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127293240</v>
+        <v>127290747</v>
       </c>
       <c r="B116" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437122</v>
+        <v>437064</v>
       </c>
       <c r="R116" t="n">
-        <v>6763905</v>
+        <v>6763744</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,22 +13057,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127294788</v>
+        <v>127293240</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13080,37 +13080,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437274</v>
+        <v>437122</v>
       </c>
       <c r="R117" t="n">
-        <v>6764023</v>
+        <v>6763905</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,60 +13164,60 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127293766</v>
+        <v>127294788</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437187</v>
+        <v>437274</v>
       </c>
       <c r="R118" t="n">
-        <v>6763964</v>
+        <v>6764023</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13271,19 +13271,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127293427</v>
+        <v>127291536</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -13314,17 +13314,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>437147</v>
+        <v>436972</v>
       </c>
       <c r="R119" t="n">
-        <v>6763942</v>
+        <v>6763733</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13378,19 +13378,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127291536</v>
+        <v>127293635</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13421,17 +13421,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436972</v>
+        <v>437130</v>
       </c>
       <c r="R120" t="n">
-        <v>6763733</v>
+        <v>6763988</v>
       </c>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13485,19 +13485,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127293635</v>
+        <v>127293427</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13532,10 +13532,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437130</v>
+        <v>437147</v>
       </c>
       <c r="R121" t="n">
-        <v>6763988</v>
+        <v>6763942</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13604,48 +13604,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290203</v>
+        <v>127290001</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>57817</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437188</v>
+        <v>437239</v>
       </c>
       <c r="R122" t="n">
-        <v>6763793</v>
+        <v>6763818</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13685,11 +13690,6 @@
       <c r="AB122" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13716,7 +13716,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290773</v>
+        <v>127290203</v>
       </c>
       <c r="B123" t="n">
         <v>8447</v>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437081</v>
+        <v>437188</v>
       </c>
       <c r="R123" t="n">
-        <v>6763812</v>
+        <v>6763793</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,6 +13797,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13823,53 +13828,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290001</v>
+        <v>127290773</v>
       </c>
       <c r="B124" t="n">
-        <v>57817</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437239</v>
+        <v>437081</v>
       </c>
       <c r="R124" t="n">
-        <v>6763818</v>
+        <v>6763812</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14602,48 +14602,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127295386</v>
+        <v>127293305</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437233</v>
+        <v>437137</v>
       </c>
       <c r="R131" t="n">
-        <v>6763867</v>
+        <v>6763885</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14697,60 +14697,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127294021</v>
+        <v>127294311</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437191</v>
+        <v>437170</v>
       </c>
       <c r="R132" t="n">
-        <v>6763952</v>
+        <v>6764043</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14789,7 +14789,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14804,19 +14809,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295217</v>
+        <v>127295386</v>
       </c>
       <c r="B133" t="n">
         <v>8447</v>
@@ -14851,10 +14856,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437312</v>
+        <v>437233</v>
       </c>
       <c r="R133" t="n">
-        <v>6763984</v>
+        <v>6763867</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14923,7 +14928,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127293270</v>
+        <v>127294021</v>
       </c>
       <c r="B134" t="n">
         <v>8447</v>
@@ -14958,10 +14963,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437124</v>
+        <v>437191</v>
       </c>
       <c r="R134" t="n">
-        <v>6763885</v>
+        <v>6763952</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14993,7 +14998,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15003,7 +15008,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15030,48 +15035,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127293305</v>
+        <v>127295217</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437137</v>
+        <v>437312</v>
       </c>
       <c r="R135" t="n">
-        <v>6763885</v>
+        <v>6763984</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15100,7 +15105,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15110,7 +15115,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15125,60 +15130,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127294311</v>
+        <v>127293270</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437170</v>
+        <v>437124</v>
       </c>
       <c r="R136" t="n">
-        <v>6764043</v>
+        <v>6763885</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15207,7 +15212,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15217,12 +15222,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295759</v>
+        <v>127293774</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437218</v>
+        <v>437187</v>
       </c>
       <c r="R2" t="n">
-        <v>6763878</v>
+        <v>6763964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295923</v>
+        <v>127295759</v>
       </c>
       <c r="B3" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437244</v>
+        <v>437218</v>
       </c>
       <c r="R3" t="n">
-        <v>6763901</v>
+        <v>6763878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127294146</v>
+        <v>127295923</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437131</v>
+        <v>437244</v>
       </c>
       <c r="R4" t="n">
-        <v>6764010</v>
+        <v>6763901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294422</v>
+        <v>127294146</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1027,17 +1027,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437193</v>
+        <v>437131</v>
       </c>
       <c r="R5" t="n">
-        <v>6764064</v>
+        <v>6764010</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127290437</v>
+        <v>127294422</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1134,17 +1134,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437157</v>
+        <v>437193</v>
       </c>
       <c r="R6" t="n">
-        <v>6763806</v>
+        <v>6764064</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,19 +1198,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295045</v>
+        <v>127291489</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1241,17 +1241,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437295</v>
+        <v>437044</v>
       </c>
       <c r="R7" t="n">
-        <v>6763947</v>
+        <v>6763790</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,65 +1305,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295019</v>
+        <v>127290437</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437299</v>
+        <v>437157</v>
       </c>
       <c r="R8" t="n">
-        <v>6763962</v>
+        <v>6763806</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,19 +1412,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127293774</v>
+        <v>127295045</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1460,17 +1455,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437187</v>
+        <v>437295</v>
       </c>
       <c r="R9" t="n">
-        <v>6763964</v>
+        <v>6763947</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,60 +1519,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291489</v>
+        <v>127295019</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437044</v>
+        <v>437299</v>
       </c>
       <c r="R10" t="n">
-        <v>6763790</v>
+        <v>6763962</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,12 +1631,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294721</v>
+        <v>127294354</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437204</v>
+        <v>437188</v>
       </c>
       <c r="R12" t="n">
-        <v>6764046</v>
+        <v>6764029</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,19 +1850,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294354</v>
+        <v>127294041</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437188</v>
+        <v>437152</v>
       </c>
       <c r="R13" t="n">
-        <v>6764029</v>
+        <v>6764014</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127291056</v>
+        <v>127294738</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437040</v>
+        <v>437220</v>
       </c>
       <c r="R14" t="n">
-        <v>6763751</v>
+        <v>6764061</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,19 +2064,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127294041</v>
+        <v>127294721</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437152</v>
+        <v>437204</v>
       </c>
       <c r="R15" t="n">
-        <v>6764014</v>
+        <v>6764046</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127294738</v>
+        <v>127291056</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2214,17 +2214,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437220</v>
+        <v>437040</v>
       </c>
       <c r="R16" t="n">
-        <v>6764061</v>
+        <v>6763751</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,22 +2278,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127293099</v>
+        <v>127293263</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437109</v>
+        <v>437138</v>
       </c>
       <c r="R17" t="n">
-        <v>6763908</v>
+        <v>6763887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127291525</v>
+        <v>127295941</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,37 +2408,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437044</v>
+        <v>437223</v>
       </c>
       <c r="R18" t="n">
-        <v>6763790</v>
+        <v>6763922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,22 +2492,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127293263</v>
+        <v>127293099</v>
       </c>
       <c r="B19" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437138</v>
+        <v>437109</v>
       </c>
       <c r="R19" t="n">
-        <v>6763887</v>
+        <v>6763908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127294351</v>
+        <v>127291525</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437151</v>
+        <v>437044</v>
       </c>
       <c r="R20" t="n">
-        <v>6764039</v>
+        <v>6763790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295941</v>
+        <v>127294351</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2749,17 +2749,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437223</v>
+        <v>437151</v>
       </c>
       <c r="R21" t="n">
-        <v>6763922</v>
+        <v>6764039</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3039,53 +3039,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293820</v>
+        <v>127293241</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437201</v>
+        <v>437135</v>
       </c>
       <c r="R24" t="n">
-        <v>6763976</v>
+        <v>6763885</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,62 +3139,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295384</v>
+        <v>127293161</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437233</v>
+        <v>437098</v>
       </c>
       <c r="R25" t="n">
-        <v>6763867</v>
+        <v>6763941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,48 +3258,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294346</v>
+        <v>127292736</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437187</v>
+        <v>436991</v>
       </c>
       <c r="R26" t="n">
-        <v>6764029</v>
+        <v>6763816</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3333,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3358,19 +3353,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293735</v>
+        <v>127295078</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3401,17 +3396,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437156</v>
+        <v>437293</v>
       </c>
       <c r="R27" t="n">
-        <v>6763978</v>
+        <v>6763940</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3450,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,19 +3460,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295078</v>
+        <v>127294346</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3512,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437293</v>
+        <v>437187</v>
       </c>
       <c r="R28" t="n">
-        <v>6763940</v>
+        <v>6764029</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3547,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,53 +3579,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127293241</v>
+        <v>127295384</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437135</v>
+        <v>437233</v>
       </c>
       <c r="R29" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,57 +3679,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293161</v>
+        <v>127293820</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437098</v>
+        <v>437201</v>
       </c>
       <c r="R30" t="n">
-        <v>6763941</v>
+        <v>6763976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3803,32 +3803,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127292736</v>
+        <v>127293735</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436991</v>
+        <v>437156</v>
       </c>
       <c r="R31" t="n">
-        <v>6763816</v>
+        <v>6763978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127293203</v>
+        <v>127295057</v>
       </c>
       <c r="B32" t="n">
         <v>79014</v>
@@ -3941,17 +3941,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437116</v>
+        <v>437295</v>
       </c>
       <c r="R32" t="n">
-        <v>6763949</v>
+        <v>6763942</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,65 +4005,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294136</v>
+        <v>127293696</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437182</v>
+        <v>437156</v>
       </c>
       <c r="R33" t="n">
-        <v>6763976</v>
+        <v>6763982</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4092,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4102,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,12 +4112,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4236,7 +4231,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295057</v>
+        <v>127293203</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -4267,17 +4262,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437295</v>
+        <v>437116</v>
       </c>
       <c r="R35" t="n">
-        <v>6763942</v>
+        <v>6763949</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4331,19 +4326,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293696</v>
+        <v>127293981</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4378,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437156</v>
+        <v>437177</v>
       </c>
       <c r="R36" t="n">
-        <v>6763982</v>
+        <v>6764017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,48 +4445,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127293981</v>
+        <v>127294136</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437177</v>
+        <v>437182</v>
       </c>
       <c r="R37" t="n">
-        <v>6764017</v>
+        <v>6763976</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,44 +4545,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295245</v>
+        <v>127293212</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437308</v>
+        <v>437120</v>
       </c>
       <c r="R38" t="n">
-        <v>6763966</v>
+        <v>6763919</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,48 +4664,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127292669</v>
+        <v>127294037</v>
       </c>
       <c r="B39" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437023</v>
+        <v>437188</v>
       </c>
       <c r="R39" t="n">
-        <v>6763818</v>
+        <v>6763952</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,19 +4759,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127291424</v>
+        <v>127292669</v>
       </c>
       <c r="B40" t="n">
         <v>79632</v>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437058</v>
+        <v>437023</v>
       </c>
       <c r="R40" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,48 +4878,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127293212</v>
+        <v>127290586</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437120</v>
+        <v>437065</v>
       </c>
       <c r="R41" t="n">
-        <v>6763919</v>
+        <v>6763754</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,60 +4973,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127294037</v>
+        <v>127291424</v>
       </c>
       <c r="B42" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437188</v>
+        <v>437058</v>
       </c>
       <c r="R42" t="n">
-        <v>6763952</v>
+        <v>6763796</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,19 +5080,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127292954</v>
+        <v>127295245</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -5123,17 +5123,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437050</v>
+        <v>437308</v>
       </c>
       <c r="R43" t="n">
-        <v>6763860</v>
+        <v>6763966</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,19 +5187,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127290586</v>
+        <v>127292954</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437065</v>
+        <v>437050</v>
       </c>
       <c r="R44" t="n">
-        <v>6763754</v>
+        <v>6763860</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5306,7 +5306,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127292927</v>
+        <v>127291031</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437032</v>
+        <v>437097</v>
       </c>
       <c r="R45" t="n">
-        <v>6763858</v>
+        <v>6763850</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127293956</v>
+        <v>127292927</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437202</v>
+        <v>437032</v>
       </c>
       <c r="R46" t="n">
-        <v>6764007</v>
+        <v>6763858</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
         <v>127295897</v>
       </c>
       <c r="B49" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127291031</v>
+        <v>127293956</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437097</v>
+        <v>437202</v>
       </c>
       <c r="R50" t="n">
-        <v>6763850</v>
+        <v>6764007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,50 +5948,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290803</v>
+        <v>127290540</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437091</v>
+        <v>437113</v>
       </c>
       <c r="R51" t="n">
-        <v>6763822</v>
+        <v>6763817</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127290540</v>
+        <v>127294782</v>
       </c>
       <c r="B52" t="n">
         <v>8447</v>
@@ -6091,17 +6086,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437113</v>
+        <v>437273</v>
       </c>
       <c r="R52" t="n">
-        <v>6763817</v>
+        <v>6764025</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6130,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6140,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6155,60 +6150,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127294782</v>
+        <v>127290803</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437273</v>
+        <v>437091</v>
       </c>
       <c r="R53" t="n">
-        <v>6764025</v>
+        <v>6763822</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,22 +6262,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127290094</v>
+        <v>127291397</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437239</v>
+        <v>437058</v>
       </c>
       <c r="R54" t="n">
-        <v>6763818</v>
+        <v>6763796</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6355,11 +6355,6 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6386,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127291397</v>
+        <v>127290094</v>
       </c>
       <c r="B55" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6397,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6421,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437058</v>
+        <v>437239</v>
       </c>
       <c r="R55" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6467,6 +6462,11 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6707,48 +6707,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127293858</v>
+        <v>127294772</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437201</v>
+        <v>437255</v>
       </c>
       <c r="R58" t="n">
-        <v>6763976</v>
+        <v>6764049</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,62 +6802,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127290454</v>
+        <v>127294411</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437078</v>
+        <v>437202</v>
       </c>
       <c r="R59" t="n">
-        <v>6763737</v>
+        <v>6764041</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6889,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6899,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6926,7 +6921,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294772</v>
+        <v>127294416</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6957,17 +6952,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437255</v>
+        <v>437158</v>
       </c>
       <c r="R60" t="n">
-        <v>6764049</v>
+        <v>6764069</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6996,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7006,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,19 +7016,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294736</v>
+        <v>127295806</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -7071,7 +7066,7 @@
         <v>437212</v>
       </c>
       <c r="R61" t="n">
-        <v>6764065</v>
+        <v>6763955</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7103,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,10 +7135,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294985</v>
+        <v>127293072</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7151,37 +7146,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437293</v>
+        <v>437081</v>
       </c>
       <c r="R62" t="n">
-        <v>6763965</v>
+        <v>6763901</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7205,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7215,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,22 +7230,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127294411</v>
+        <v>127291537</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7258,37 +7253,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437202</v>
+        <v>437044</v>
       </c>
       <c r="R63" t="n">
-        <v>6764041</v>
+        <v>6763790</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7317,7 +7312,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7327,7 +7322,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,19 +7337,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127294416</v>
+        <v>127294736</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7385,17 +7380,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437158</v>
+        <v>437212</v>
       </c>
       <c r="R64" t="n">
-        <v>6764069</v>
+        <v>6764065</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7424,7 +7419,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7429,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,19 +7444,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127295806</v>
+        <v>127294985</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -7496,10 +7491,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437212</v>
+        <v>437293</v>
       </c>
       <c r="R65" t="n">
-        <v>6763955</v>
+        <v>6763965</v>
       </c>
       <c r="S65" t="n">
         <v>9</v>
@@ -7531,7 +7526,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7536,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,32 +7563,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127293072</v>
+        <v>127293858</v>
       </c>
       <c r="B66" t="n">
-        <v>91345</v>
+        <v>8447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437081</v>
+        <v>437201</v>
       </c>
       <c r="R66" t="n">
-        <v>6763901</v>
+        <v>6763976</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7675,48 +7670,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127291537</v>
+        <v>127290454</v>
       </c>
       <c r="B67" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437044</v>
+        <v>437078</v>
       </c>
       <c r="R67" t="n">
-        <v>6763790</v>
+        <v>6763737</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,12 +7770,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7999,7 +7999,7 @@
         <v>127290959</v>
       </c>
       <c r="B70" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>127294334</v>
       </c>
       <c r="B74" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8638,53 +8638,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B76" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R76" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8713,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8723,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8738,60 +8733,65 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R77" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293897</v>
+        <v>127290717</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,34 +8868,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437180</v>
+        <v>437108</v>
       </c>
       <c r="R78" t="n">
-        <v>6763986</v>
+        <v>6763809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8964,7 +8969,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127294716</v>
+        <v>127293897</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8995,17 +9000,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437199</v>
+        <v>437180</v>
       </c>
       <c r="R79" t="n">
-        <v>6764063</v>
+        <v>6763986</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9034,7 +9039,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9044,7 +9049,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9059,12 +9064,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9285,7 +9290,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293504</v>
+        <v>127294716</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -9316,17 +9321,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437136</v>
+        <v>437199</v>
       </c>
       <c r="R82" t="n">
-        <v>6763963</v>
+        <v>6764063</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9355,7 +9360,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9365,7 +9370,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,19 +9385,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294433</v>
+        <v>127293504</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -9423,17 +9428,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437180</v>
+        <v>437136</v>
       </c>
       <c r="R83" t="n">
-        <v>6764047</v>
+        <v>6763963</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9472,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,22 +9492,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127290717</v>
+        <v>127294433</v>
       </c>
       <c r="B84" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9510,42 +9515,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437108</v>
+        <v>437180</v>
       </c>
       <c r="R84" t="n">
-        <v>6763809</v>
+        <v>6764047</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,12 +9599,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9718,7 +9718,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127290757</v>
+        <v>127295863</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9753,10 +9753,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437058</v>
+        <v>437221</v>
       </c>
       <c r="R86" t="n">
-        <v>6763741</v>
+        <v>6763950</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9825,7 +9825,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127295596</v>
+        <v>127291960</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437169</v>
+        <v>437015</v>
       </c>
       <c r="R87" t="n">
-        <v>6763904</v>
+        <v>6763762</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127291960</v>
+        <v>127293022</v>
       </c>
       <c r="B88" t="n">
         <v>79014</v>
@@ -9967,10 +9967,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437015</v>
+        <v>437081</v>
       </c>
       <c r="R88" t="n">
-        <v>6763762</v>
+        <v>6763901</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10039,32 +10039,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127293022</v>
+        <v>127292822</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437081</v>
+        <v>436992</v>
       </c>
       <c r="R89" t="n">
-        <v>6763901</v>
+        <v>6763834</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10146,48 +10146,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127295863</v>
+        <v>127295269</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437221</v>
+        <v>437297</v>
       </c>
       <c r="R90" t="n">
-        <v>6763950</v>
+        <v>6763935</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10241,19 +10241,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127292924</v>
+        <v>127290757</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437037</v>
+        <v>437058</v>
       </c>
       <c r="R91" t="n">
-        <v>6763860</v>
+        <v>6763741</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10360,7 +10360,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127295035</v>
+        <v>127295596</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -10391,17 +10391,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437297</v>
+        <v>437169</v>
       </c>
       <c r="R92" t="n">
-        <v>6763951</v>
+        <v>6763904</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10455,60 +10455,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127292822</v>
+        <v>127292924</v>
       </c>
       <c r="B93" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436992</v>
+        <v>437037</v>
       </c>
       <c r="R93" t="n">
-        <v>6763834</v>
+        <v>6763860</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10562,60 +10562,60 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127292999</v>
+        <v>127295035</v>
       </c>
       <c r="B94" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437093</v>
+        <v>437297</v>
       </c>
       <c r="R94" t="n">
-        <v>6763880</v>
+        <v>6763951</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,19 +10669,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127295269</v>
+        <v>127292999</v>
       </c>
       <c r="B95" t="n">
         <v>8447</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437297</v>
+        <v>437093</v>
       </c>
       <c r="R95" t="n">
-        <v>6763935</v>
+        <v>6763880</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293348</v>
+        <v>127293029</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,39 +10799,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437154</v>
+        <v>437074</v>
       </c>
       <c r="R96" t="n">
-        <v>6763925</v>
+        <v>6763890</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10900,53 +10895,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127295309</v>
+        <v>127293586</v>
       </c>
       <c r="B97" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437289</v>
+        <v>437163</v>
       </c>
       <c r="R97" t="n">
-        <v>6763874</v>
+        <v>6763902</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10975,7 +10965,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10975,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11000,22 +10990,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293586</v>
+        <v>127293953</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11023,34 +11013,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437163</v>
+        <v>437190</v>
       </c>
       <c r="R98" t="n">
-        <v>6763902</v>
+        <v>6763937</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -11082,7 +11081,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11091,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11118,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293953</v>
+        <v>127293371</v>
       </c>
       <c r="B99" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,46 +11129,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437190</v>
+        <v>437140</v>
       </c>
       <c r="R99" t="n">
-        <v>6763937</v>
+        <v>6763931</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11198,7 +11188,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11208,7 +11198,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11223,19 +11213,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293371</v>
+        <v>127293249</v>
       </c>
       <c r="B100" t="n">
         <v>79014</v>
@@ -11266,17 +11256,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437140</v>
+        <v>437134</v>
       </c>
       <c r="R100" t="n">
-        <v>6763931</v>
+        <v>6763889</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11305,7 +11295,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11315,7 +11305,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11330,19 +11320,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293249</v>
+        <v>127290978</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11373,17 +11363,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437134</v>
+        <v>437098</v>
       </c>
       <c r="R101" t="n">
-        <v>6763889</v>
+        <v>6763850</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11412,7 +11402,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11422,7 +11412,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11437,60 +11427,65 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293029</v>
+        <v>127295309</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437074</v>
+        <v>437289</v>
       </c>
       <c r="R102" t="n">
-        <v>6763890</v>
+        <v>6763874</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11556,10 +11551,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127290978</v>
+        <v>127293348</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11567,34 +11562,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437098</v>
+        <v>437154</v>
       </c>
       <c r="R103" t="n">
-        <v>6763850</v>
+        <v>6763925</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12096,53 +12096,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127292727</v>
+        <v>127291177</v>
       </c>
       <c r="B108" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437043</v>
+        <v>437081</v>
       </c>
       <c r="R108" t="n">
-        <v>6763856</v>
+        <v>6763837</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12171,7 +12166,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12181,7 +12176,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12196,44 +12191,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127290265</v>
+        <v>127293290</v>
       </c>
       <c r="B109" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12243,10 +12238,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437187</v>
+        <v>437138</v>
       </c>
       <c r="R109" t="n">
-        <v>6763801</v>
+        <v>6763901</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12289,6 +12284,11 @@
       <c r="AB109" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12315,7 +12315,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127294388</v>
+        <v>127292727</v>
       </c>
       <c r="B110" t="n">
         <v>8447</v>
@@ -12344,16 +12344,21 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437183</v>
+        <v>437043</v>
       </c>
       <c r="R110" t="n">
-        <v>6764033</v>
+        <v>6763856</v>
       </c>
       <c r="S110" t="n">
         <v>9</v>
@@ -12385,7 +12390,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12395,7 +12400,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12422,32 +12427,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127291177</v>
+        <v>127290265</v>
       </c>
       <c r="B111" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12457,10 +12462,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437081</v>
+        <v>437187</v>
       </c>
       <c r="R111" t="n">
-        <v>6763837</v>
+        <v>6763801</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12529,48 +12534,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127293290</v>
+        <v>127294388</v>
       </c>
       <c r="B112" t="n">
-        <v>91345</v>
+        <v>8447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437138</v>
+        <v>437183</v>
       </c>
       <c r="R112" t="n">
-        <v>6763901</v>
+        <v>6764033</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12599,7 +12604,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12609,12 +12614,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12629,60 +12629,60 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293766</v>
+        <v>127293262</v>
       </c>
       <c r="B113" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437187</v>
+        <v>437131</v>
       </c>
       <c r="R113" t="n">
-        <v>6763964</v>
+        <v>6763892</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,22 +12736,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127291635</v>
+        <v>127293240</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12759,21 +12759,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437032</v>
+        <v>437122</v>
       </c>
       <c r="R114" t="n">
-        <v>6763776</v>
+        <v>6763905</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12855,7 +12855,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127293262</v>
+        <v>127294788</v>
       </c>
       <c r="B115" t="n">
         <v>79014</v>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437131</v>
+        <v>437274</v>
       </c>
       <c r="R115" t="n">
-        <v>6763892</v>
+        <v>6764023</v>
       </c>
       <c r="S115" t="n">
         <v>9</v>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12962,7 +12962,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127290747</v>
+        <v>127291635</v>
       </c>
       <c r="B116" t="n">
         <v>79014</v>
@@ -12993,17 +12993,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437064</v>
+        <v>437032</v>
       </c>
       <c r="R116" t="n">
-        <v>6763744</v>
+        <v>6763776</v>
       </c>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,44 +13057,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127293240</v>
+        <v>127293766</v>
       </c>
       <c r="B117" t="n">
-        <v>91345</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13104,10 +13104,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437122</v>
+        <v>437187</v>
       </c>
       <c r="R117" t="n">
-        <v>6763905</v>
+        <v>6763964</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13176,7 +13176,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127294788</v>
+        <v>127290747</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437274</v>
+        <v>437064</v>
       </c>
       <c r="R118" t="n">
-        <v>6764023</v>
+        <v>6763744</v>
       </c>
       <c r="S118" t="n">
         <v>9</v>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13390,7 +13390,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127293635</v>
+        <v>127293427</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13425,10 +13425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437130</v>
+        <v>437147</v>
       </c>
       <c r="R120" t="n">
-        <v>6763988</v>
+        <v>6763942</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13497,7 +13497,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127293427</v>
+        <v>127293635</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13532,10 +13532,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437147</v>
+        <v>437130</v>
       </c>
       <c r="R121" t="n">
-        <v>6763942</v>
+        <v>6763988</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13935,7 +13935,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127295889</v>
+        <v>127292816</v>
       </c>
       <c r="B125" t="n">
         <v>57654</v>
@@ -13966,7 +13966,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437244</v>
+        <v>436992</v>
       </c>
       <c r="R125" t="n">
-        <v>6763890</v>
+        <v>6763834</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14047,7 +14047,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127292816</v>
+        <v>127295889</v>
       </c>
       <c r="B126" t="n">
         <v>57654</v>
@@ -14078,7 +14078,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14087,10 +14087,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436992</v>
+        <v>437244</v>
       </c>
       <c r="R126" t="n">
-        <v>6763834</v>
+        <v>6763890</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14495,32 +14495,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127292761</v>
+        <v>127295386</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436992</v>
+        <v>437233</v>
       </c>
       <c r="R130" t="n">
-        <v>6763834</v>
+        <v>6763867</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14602,32 +14602,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127293305</v>
+        <v>127294021</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437137</v>
+        <v>437191</v>
       </c>
       <c r="R131" t="n">
-        <v>6763885</v>
+        <v>6763952</v>
       </c>
       <c r="S131" t="n">
         <v>9</v>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14709,32 +14709,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127294311</v>
+        <v>127295217</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14744,10 +14744,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437170</v>
+        <v>437312</v>
       </c>
       <c r="R132" t="n">
-        <v>6764043</v>
+        <v>6763984</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14790,11 +14790,6 @@
       <c r="AB132" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14821,7 +14816,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295386</v>
+        <v>127293270</v>
       </c>
       <c r="B133" t="n">
         <v>8447</v>
@@ -14852,17 +14847,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437233</v>
+        <v>437124</v>
       </c>
       <c r="R133" t="n">
-        <v>6763867</v>
+        <v>6763885</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14891,7 +14886,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14901,7 +14896,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14916,44 +14911,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127294021</v>
+        <v>127293305</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14963,10 +14958,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437191</v>
+        <v>437137</v>
       </c>
       <c r="R134" t="n">
-        <v>6763952</v>
+        <v>6763885</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14998,7 +14993,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15008,7 +15003,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15035,32 +15030,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127295217</v>
+        <v>127292761</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15070,10 +15065,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437312</v>
+        <v>436992</v>
       </c>
       <c r="R135" t="n">
-        <v>6763984</v>
+        <v>6763834</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15142,48 +15137,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127293270</v>
+        <v>127294311</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437124</v>
+        <v>437170</v>
       </c>
       <c r="R136" t="n">
-        <v>6763885</v>
+        <v>6764043</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15212,7 +15207,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15222,7 +15217,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294354</v>
+        <v>127294721</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437188</v>
+        <v>437204</v>
       </c>
       <c r="R12" t="n">
-        <v>6764029</v>
+        <v>6764046</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,19 +1850,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294041</v>
+        <v>127291056</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437152</v>
+        <v>437040</v>
       </c>
       <c r="R13" t="n">
-        <v>6764014</v>
+        <v>6763751</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294738</v>
+        <v>127294354</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437220</v>
+        <v>437188</v>
       </c>
       <c r="R14" t="n">
-        <v>6764061</v>
+        <v>6764029</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,19 +2064,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127294721</v>
+        <v>127294041</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437204</v>
+        <v>437152</v>
       </c>
       <c r="R15" t="n">
-        <v>6764046</v>
+        <v>6764014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127291056</v>
+        <v>127294738</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2214,17 +2214,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437040</v>
+        <v>437220</v>
       </c>
       <c r="R16" t="n">
-        <v>6763751</v>
+        <v>6764061</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,12 +2278,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3039,50 +3039,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293241</v>
+        <v>127295078</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437135</v>
+        <v>437293</v>
       </c>
       <c r="R24" t="n">
-        <v>6763885</v>
+        <v>6763940</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3114,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,48 +3146,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127293161</v>
+        <v>127294346</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437098</v>
+        <v>437187</v>
       </c>
       <c r="R25" t="n">
-        <v>6763941</v>
+        <v>6764029</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,44 +3241,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127292736</v>
+        <v>127293735</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436991</v>
+        <v>437156</v>
       </c>
       <c r="R26" t="n">
-        <v>6763816</v>
+        <v>6763978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,45 +3360,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295078</v>
+        <v>127293241</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437293</v>
+        <v>437135</v>
       </c>
       <c r="R27" t="n">
-        <v>6763940</v>
+        <v>6763885</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,48 +3472,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127294346</v>
+        <v>127293161</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437187</v>
+        <v>437098</v>
       </c>
       <c r="R28" t="n">
-        <v>6764029</v>
+        <v>6763941</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,62 +3567,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295384</v>
+        <v>127292736</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437233</v>
+        <v>436991</v>
       </c>
       <c r="R29" t="n">
-        <v>6763867</v>
+        <v>6763816</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293820</v>
+        <v>127295384</v>
       </c>
       <c r="B30" t="n">
         <v>57654</v>
@@ -3722,7 +3717,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3731,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437201</v>
+        <v>437233</v>
       </c>
       <c r="R30" t="n">
-        <v>6763976</v>
+        <v>6763867</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3803,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127293735</v>
+        <v>127293820</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,34 +3809,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437156</v>
+        <v>437201</v>
       </c>
       <c r="R31" t="n">
-        <v>6763978</v>
+        <v>6763976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295057</v>
+        <v>127293914</v>
       </c>
       <c r="B32" t="n">
         <v>79014</v>
@@ -3941,17 +3941,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437295</v>
+        <v>437190</v>
       </c>
       <c r="R32" t="n">
-        <v>6763942</v>
+        <v>6763999</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,19 +4005,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293696</v>
+        <v>127293203</v>
       </c>
       <c r="B33" t="n">
         <v>79014</v>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437156</v>
+        <v>437116</v>
       </c>
       <c r="R33" t="n">
-        <v>6763982</v>
+        <v>6763949</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293914</v>
+        <v>127293981</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437190</v>
+        <v>437177</v>
       </c>
       <c r="R34" t="n">
-        <v>6763999</v>
+        <v>6764017</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4231,48 +4231,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127293203</v>
+        <v>127294136</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437116</v>
+        <v>437182</v>
       </c>
       <c r="R35" t="n">
-        <v>6763949</v>
+        <v>6763976</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4301,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,19 +4331,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293981</v>
+        <v>127295057</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4369,17 +4374,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437177</v>
+        <v>437295</v>
       </c>
       <c r="R36" t="n">
-        <v>6764017</v>
+        <v>6763942</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4418,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,65 +4438,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294136</v>
+        <v>127293696</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437182</v>
+        <v>437156</v>
       </c>
       <c r="R37" t="n">
-        <v>6763976</v>
+        <v>6763982</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,12 +4545,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127294772</v>
+        <v>127294736</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437255</v>
+        <v>437212</v>
       </c>
       <c r="R58" t="n">
-        <v>6764049</v>
+        <v>6764065</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6814,7 +6814,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294411</v>
+        <v>127294985</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437202</v>
+        <v>437293</v>
       </c>
       <c r="R59" t="n">
-        <v>6764041</v>
+        <v>6763965</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6921,32 +6921,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294416</v>
+        <v>127293858</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437158</v>
+        <v>437201</v>
       </c>
       <c r="R60" t="n">
-        <v>6764069</v>
+        <v>6763976</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7028,45 +7028,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127295806</v>
+        <v>127290454</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437212</v>
+        <v>437078</v>
       </c>
       <c r="R61" t="n">
-        <v>6763955</v>
+        <v>6763737</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7098,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7135,10 +7140,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127293072</v>
+        <v>127291537</v>
       </c>
       <c r="B62" t="n">
-        <v>91346</v>
+        <v>79603</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7146,21 +7151,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7170,10 +7175,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437081</v>
+        <v>437044</v>
       </c>
       <c r="R62" t="n">
-        <v>6763901</v>
+        <v>6763790</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7242,10 +7247,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127291537</v>
+        <v>127294772</v>
       </c>
       <c r="B63" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7253,37 +7258,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437044</v>
+        <v>437255</v>
       </c>
       <c r="R63" t="n">
-        <v>6763790</v>
+        <v>6764049</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,7 +7317,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7322,7 +7327,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7337,19 +7342,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127294736</v>
+        <v>127294411</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7384,10 +7389,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437212</v>
+        <v>437202</v>
       </c>
       <c r="R64" t="n">
-        <v>6764065</v>
+        <v>6764041</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -7419,7 +7424,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7429,7 +7434,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7456,7 +7461,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127294985</v>
+        <v>127294416</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -7487,17 +7492,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437293</v>
+        <v>437158</v>
       </c>
       <c r="R65" t="n">
-        <v>6763965</v>
+        <v>6764069</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7526,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7536,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7551,60 +7556,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127293858</v>
+        <v>127295806</v>
       </c>
       <c r="B66" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437201</v>
+        <v>437212</v>
       </c>
       <c r="R66" t="n">
-        <v>6763976</v>
+        <v>6763955</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7633,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7643,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7658,65 +7663,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127290454</v>
+        <v>127293072</v>
       </c>
       <c r="B67" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437078</v>
+        <v>437081</v>
       </c>
       <c r="R67" t="n">
-        <v>6763737</v>
+        <v>6763901</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,44 +7770,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290826</v>
+        <v>127290713</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437081</v>
+        <v>437108</v>
       </c>
       <c r="R68" t="n">
-        <v>6763837</v>
+        <v>6763809</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,48 +7889,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127290751</v>
+        <v>127292742</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437062</v>
+        <v>437089</v>
       </c>
       <c r="R69" t="n">
-        <v>6763738</v>
+        <v>6763838</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,44 +7984,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B70" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R70" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,32 +8103,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290713</v>
+        <v>127290826</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R71" t="n">
-        <v>6763809</v>
+        <v>6763837</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,48 +8210,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127292742</v>
+        <v>127290751</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437089</v>
+        <v>437062</v>
       </c>
       <c r="R72" t="n">
-        <v>6763838</v>
+        <v>6763738</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,44 +8305,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127294714</v>
+        <v>127290959</v>
       </c>
       <c r="B73" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437204</v>
+        <v>437097</v>
       </c>
       <c r="R73" t="n">
-        <v>6764046</v>
+        <v>6763868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,48 +8424,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127294334</v>
+        <v>127292676</v>
       </c>
       <c r="B74" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437170</v>
+        <v>437043</v>
       </c>
       <c r="R74" t="n">
-        <v>6764043</v>
+        <v>6763840</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8519,22 +8524,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127295799</v>
+        <v>127294334</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8547,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,10 +8571,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437234</v>
+        <v>437170</v>
       </c>
       <c r="R75" t="n">
-        <v>6763858</v>
+        <v>6764043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8638,7 +8643,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127294842</v>
+        <v>127295799</v>
       </c>
       <c r="B76" t="n">
         <v>79014</v>
@@ -8673,10 +8678,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437280</v>
+        <v>437234</v>
       </c>
       <c r="R76" t="n">
-        <v>6764030</v>
+        <v>6763858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8745,53 +8750,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B77" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R77" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,12 +8845,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293586</v>
+        <v>127293348</v>
       </c>
       <c r="B97" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10906,37 +10906,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437163</v>
+        <v>437154</v>
       </c>
       <c r="R97" t="n">
-        <v>6763902</v>
+        <v>6763925</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10965,7 +10970,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10975,7 +10980,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10990,22 +10995,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293953</v>
+        <v>127293586</v>
       </c>
       <c r="B98" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11013,43 +11018,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437190</v>
+        <v>437163</v>
       </c>
       <c r="R98" t="n">
-        <v>6763937</v>
+        <v>6763902</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -11081,7 +11077,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11091,7 +11087,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11118,10 +11114,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293371</v>
+        <v>127293953</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11129,37 +11125,46 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437140</v>
+        <v>437190</v>
       </c>
       <c r="R99" t="n">
-        <v>6763931</v>
+        <v>6763937</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11188,7 +11193,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11198,7 +11203,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11213,19 +11218,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293249</v>
+        <v>127293371</v>
       </c>
       <c r="B100" t="n">
         <v>79014</v>
@@ -11256,17 +11261,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437134</v>
+        <v>437140</v>
       </c>
       <c r="R100" t="n">
-        <v>6763889</v>
+        <v>6763931</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11295,7 +11300,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11305,7 +11310,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11320,19 +11325,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127290978</v>
+        <v>127293249</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11363,17 +11368,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437098</v>
+        <v>437134</v>
       </c>
       <c r="R101" t="n">
-        <v>6763850</v>
+        <v>6763889</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11402,7 +11407,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11412,7 +11417,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11427,65 +11432,60 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127295309</v>
+        <v>127290978</v>
       </c>
       <c r="B102" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437289</v>
+        <v>437098</v>
       </c>
       <c r="R102" t="n">
-        <v>6763874</v>
+        <v>6763850</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11551,27 +11551,27 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127293348</v>
+        <v>127295309</v>
       </c>
       <c r="B103" t="n">
-        <v>57654</v>
+        <v>58027</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11582,7 +11582,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437154</v>
+        <v>437289</v>
       </c>
       <c r="R103" t="n">
-        <v>6763925</v>
+        <v>6763874</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13069,48 +13069,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127293766</v>
+        <v>127290747</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437187</v>
+        <v>437064</v>
       </c>
       <c r="R117" t="n">
-        <v>6763964</v>
+        <v>6763744</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,60 +13164,60 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127290747</v>
+        <v>127293766</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437064</v>
+        <v>437187</v>
       </c>
       <c r="R118" t="n">
-        <v>6763744</v>
+        <v>6763964</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13271,12 +13271,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127293774</v>
+        <v>127295759</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437187</v>
+        <v>437218</v>
       </c>
       <c r="R2" t="n">
-        <v>6763964</v>
+        <v>6763878</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295759</v>
+        <v>127293774</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437218</v>
+        <v>437187</v>
       </c>
       <c r="R3" t="n">
-        <v>6763878</v>
+        <v>6763964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294721</v>
+        <v>127294354</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437204</v>
+        <v>437188</v>
       </c>
       <c r="R12" t="n">
-        <v>6764046</v>
+        <v>6764029</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,19 +1850,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127291056</v>
+        <v>127294721</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437040</v>
+        <v>437204</v>
       </c>
       <c r="R13" t="n">
-        <v>6763751</v>
+        <v>6764046</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294354</v>
+        <v>127291056</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437188</v>
+        <v>437040</v>
       </c>
       <c r="R14" t="n">
-        <v>6764029</v>
+        <v>6763751</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295941</v>
+        <v>127293099</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2428,17 +2428,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437223</v>
+        <v>437109</v>
       </c>
       <c r="R18" t="n">
-        <v>6763922</v>
+        <v>6763908</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,19 +2492,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127293099</v>
+        <v>127294351</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437109</v>
+        <v>437151</v>
       </c>
       <c r="R19" t="n">
-        <v>6763908</v>
+        <v>6764039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127291525</v>
+        <v>127295941</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437044</v>
+        <v>437223</v>
       </c>
       <c r="R20" t="n">
-        <v>6763790</v>
+        <v>6763922</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127294351</v>
+        <v>127291525</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437151</v>
+        <v>437044</v>
       </c>
       <c r="R21" t="n">
-        <v>6764039</v>
+        <v>6763790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295078</v>
+        <v>127293735</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -3070,17 +3070,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437293</v>
+        <v>437156</v>
       </c>
       <c r="R24" t="n">
-        <v>6763940</v>
+        <v>6763978</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,19 +3134,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294346</v>
+        <v>127295078</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437187</v>
+        <v>437293</v>
       </c>
       <c r="R25" t="n">
-        <v>6764029</v>
+        <v>6763940</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127293735</v>
+        <v>127294346</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3284,17 +3284,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437156</v>
+        <v>437187</v>
       </c>
       <c r="R26" t="n">
-        <v>6763978</v>
+        <v>6764029</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,65 +3348,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293241</v>
+        <v>127293820</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437135</v>
+        <v>437201</v>
       </c>
       <c r="R27" t="n">
-        <v>6763885</v>
+        <v>6763976</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,57 +3460,62 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127293161</v>
+        <v>127295384</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437098</v>
+        <v>437233</v>
       </c>
       <c r="R28" t="n">
-        <v>6763941</v>
+        <v>6763867</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3579,7 +3584,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127292736</v>
+        <v>127293241</v>
       </c>
       <c r="B29" t="n">
         <v>8447</v>
@@ -3608,19 +3613,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436991</v>
+        <v>437135</v>
       </c>
       <c r="R29" t="n">
-        <v>6763816</v>
+        <v>6763885</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3649,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,62 +3684,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295384</v>
+        <v>127293161</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437233</v>
+        <v>437098</v>
       </c>
       <c r="R30" t="n">
-        <v>6763867</v>
+        <v>6763941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,50 +3803,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127293820</v>
+        <v>127292736</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437201</v>
+        <v>436991</v>
       </c>
       <c r="R31" t="n">
-        <v>6763976</v>
+        <v>6763816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,48 +3910,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127293914</v>
+        <v>127294136</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437190</v>
+        <v>437182</v>
       </c>
       <c r="R32" t="n">
-        <v>6763999</v>
+        <v>6763976</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,19 +4010,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293203</v>
+        <v>127293914</v>
       </c>
       <c r="B33" t="n">
         <v>79014</v>
@@ -4052,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437116</v>
+        <v>437190</v>
       </c>
       <c r="R33" t="n">
-        <v>6763949</v>
+        <v>6763999</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,7 +4129,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293981</v>
+        <v>127293203</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4159,10 +4164,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437177</v>
+        <v>437116</v>
       </c>
       <c r="R34" t="n">
-        <v>6764017</v>
+        <v>6763949</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4231,50 +4236,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127294136</v>
+        <v>127295057</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437182</v>
+        <v>437295</v>
       </c>
       <c r="R35" t="n">
-        <v>6763976</v>
+        <v>6763942</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,7 +4343,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295057</v>
+        <v>127293696</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4374,17 +4374,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437295</v>
+        <v>437156</v>
       </c>
       <c r="R36" t="n">
-        <v>6763942</v>
+        <v>6763982</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,19 +4438,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127293696</v>
+        <v>127293981</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437156</v>
+        <v>437177</v>
       </c>
       <c r="R37" t="n">
-        <v>6763982</v>
+        <v>6764017</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127293212</v>
+        <v>127295245</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437120</v>
+        <v>437308</v>
       </c>
       <c r="R38" t="n">
-        <v>6763919</v>
+        <v>6763966</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294037</v>
+        <v>127292954</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437188</v>
+        <v>437050</v>
       </c>
       <c r="R39" t="n">
-        <v>6763952</v>
+        <v>6763860</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127292669</v>
+        <v>127290586</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,37 +4782,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437023</v>
+        <v>437065</v>
       </c>
       <c r="R40" t="n">
-        <v>6763818</v>
+        <v>6763754</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,22 +4866,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127290586</v>
+        <v>127292669</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,37 +4889,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437065</v>
+        <v>437023</v>
       </c>
       <c r="R41" t="n">
-        <v>6763754</v>
+        <v>6763818</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,12 +4973,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5092,32 +5092,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295245</v>
+        <v>127293212</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437308</v>
+        <v>437120</v>
       </c>
       <c r="R43" t="n">
-        <v>6763966</v>
+        <v>6763919</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,32 +5199,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127292954</v>
+        <v>127294037</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437050</v>
+        <v>437188</v>
       </c>
       <c r="R44" t="n">
-        <v>6763860</v>
+        <v>6763952</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5306,32 +5306,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127291031</v>
+        <v>127290540</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437097</v>
+        <v>437113</v>
       </c>
       <c r="R45" t="n">
-        <v>6763850</v>
+        <v>6763817</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,48 +5413,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127292927</v>
+        <v>127294782</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437032</v>
+        <v>437273</v>
       </c>
       <c r="R46" t="n">
-        <v>6763858</v>
+        <v>6764025</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5508,19 +5508,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127294741</v>
+        <v>127292927</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5551,17 +5551,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437209</v>
+        <v>437032</v>
       </c>
       <c r="R47" t="n">
-        <v>6764061</v>
+        <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,19 +5615,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127292980</v>
+        <v>127294741</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437068</v>
+        <v>437209</v>
       </c>
       <c r="R48" t="n">
-        <v>6763858</v>
+        <v>6764061</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295897</v>
+        <v>127292980</v>
       </c>
       <c r="B49" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,37 +5745,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437244</v>
+        <v>437068</v>
       </c>
       <c r="R49" t="n">
-        <v>6763890</v>
+        <v>6763858</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5829,22 +5829,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127293956</v>
+        <v>127295897</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437202</v>
+        <v>437244</v>
       </c>
       <c r="R50" t="n">
-        <v>6764007</v>
+        <v>6763890</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,32 +5948,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290540</v>
+        <v>127293956</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437113</v>
+        <v>437202</v>
       </c>
       <c r="R51" t="n">
-        <v>6763817</v>
+        <v>6764007</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,48 +6055,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127294782</v>
+        <v>127291031</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437273</v>
+        <v>437097</v>
       </c>
       <c r="R52" t="n">
-        <v>6764025</v>
+        <v>6763850</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6150,12 +6150,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6274,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127291397</v>
+        <v>127293209</v>
       </c>
       <c r="B54" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437058</v>
+        <v>437116</v>
       </c>
       <c r="R54" t="n">
-        <v>6763796</v>
+        <v>6763949</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127290094</v>
+        <v>127291397</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437239</v>
+        <v>437058</v>
       </c>
       <c r="R55" t="n">
-        <v>6763818</v>
+        <v>6763796</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,11 +6462,6 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6493,7 +6488,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127290996</v>
+        <v>127290094</v>
       </c>
       <c r="B56" t="n">
         <v>79014</v>
@@ -6528,13 +6523,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437108</v>
+        <v>437239</v>
       </c>
       <c r="R56" t="n">
-        <v>6763849</v>
+        <v>6763818</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6574,6 +6569,11 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6600,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127293209</v>
+        <v>127290996</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437116</v>
+        <v>437108</v>
       </c>
       <c r="R57" t="n">
-        <v>6763949</v>
+        <v>6763849</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6707,48 +6707,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127294736</v>
+        <v>127293858</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437212</v>
+        <v>437201</v>
       </c>
       <c r="R58" t="n">
-        <v>6764065</v>
+        <v>6763976</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,57 +6802,62 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294985</v>
+        <v>127290454</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437293</v>
+        <v>437078</v>
       </c>
       <c r="R59" t="n">
-        <v>6763965</v>
+        <v>6763737</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6884,7 +6889,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6899,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6921,32 +6926,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127293858</v>
+        <v>127291537</v>
       </c>
       <c r="B60" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6956,10 +6961,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437201</v>
+        <v>437044</v>
       </c>
       <c r="R60" t="n">
-        <v>6763976</v>
+        <v>6763790</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7028,50 +7033,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127290454</v>
+        <v>127294772</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437078</v>
+        <v>437255</v>
       </c>
       <c r="R61" t="n">
-        <v>6763737</v>
+        <v>6764049</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127291537</v>
+        <v>127294736</v>
       </c>
       <c r="B62" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7151,37 +7151,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437044</v>
+        <v>437212</v>
       </c>
       <c r="R62" t="n">
-        <v>6763790</v>
+        <v>6764065</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,19 +7235,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127294772</v>
+        <v>127294985</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437255</v>
+        <v>437293</v>
       </c>
       <c r="R63" t="n">
-        <v>6764049</v>
+        <v>6763965</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7782,32 +7782,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290713</v>
+        <v>127290826</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R68" t="n">
-        <v>6763809</v>
+        <v>6763837</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,48 +7889,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127292742</v>
+        <v>127290751</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437089</v>
+        <v>437062</v>
       </c>
       <c r="R69" t="n">
-        <v>6763838</v>
+        <v>6763738</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,44 +7984,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127294714</v>
+        <v>127290959</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437204</v>
+        <v>437097</v>
       </c>
       <c r="R70" t="n">
-        <v>6764046</v>
+        <v>6763868</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,32 +8103,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290826</v>
+        <v>127290713</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437081</v>
+        <v>437108</v>
       </c>
       <c r="R71" t="n">
-        <v>6763837</v>
+        <v>6763809</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,48 +8210,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127290751</v>
+        <v>127292742</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437062</v>
+        <v>437089</v>
       </c>
       <c r="R72" t="n">
-        <v>6763738</v>
+        <v>6763838</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,44 +8305,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B73" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R73" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,53 +8424,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127292676</v>
+        <v>127294334</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437043</v>
+        <v>437170</v>
       </c>
       <c r="R74" t="n">
-        <v>6763840</v>
+        <v>6764043</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8524,22 +8519,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127294334</v>
+        <v>127295799</v>
       </c>
       <c r="B75" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8547,21 +8542,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437170</v>
+        <v>437234</v>
       </c>
       <c r="R75" t="n">
-        <v>6764043</v>
+        <v>6763858</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8643,7 +8638,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127295799</v>
+        <v>127294842</v>
       </c>
       <c r="B76" t="n">
         <v>79014</v>
@@ -8678,10 +8673,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437234</v>
+        <v>437280</v>
       </c>
       <c r="R76" t="n">
-        <v>6763858</v>
+        <v>6764030</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8750,48 +8745,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R77" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127290717</v>
+        <v>127293897</v>
       </c>
       <c r="B78" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,39 +8868,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437108</v>
+        <v>437180</v>
       </c>
       <c r="R78" t="n">
-        <v>6763809</v>
+        <v>6763986</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8969,7 +8964,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293897</v>
+        <v>127293677</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -9004,10 +8999,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437180</v>
+        <v>437148</v>
       </c>
       <c r="R79" t="n">
-        <v>6763986</v>
+        <v>6764001</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9076,7 +9071,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293677</v>
+        <v>127293789</v>
       </c>
       <c r="B80" t="n">
         <v>79014</v>
@@ -9111,10 +9106,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437148</v>
+        <v>437218</v>
       </c>
       <c r="R80" t="n">
-        <v>6764001</v>
+        <v>6763950</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9183,7 +9178,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127293789</v>
+        <v>127294716</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -9214,17 +9209,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437218</v>
+        <v>437199</v>
       </c>
       <c r="R81" t="n">
-        <v>6763950</v>
+        <v>6764063</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9253,7 +9248,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9263,7 +9258,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9278,19 +9273,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127294716</v>
+        <v>127293504</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -9321,17 +9316,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437199</v>
+        <v>437136</v>
       </c>
       <c r="R82" t="n">
-        <v>6764063</v>
+        <v>6763963</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9360,7 +9355,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9370,7 +9365,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9385,19 +9380,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127293504</v>
+        <v>127294433</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -9428,17 +9423,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437136</v>
+        <v>437180</v>
       </c>
       <c r="R83" t="n">
-        <v>6763963</v>
+        <v>6764047</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9477,7 +9472,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,22 +9487,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127294433</v>
+        <v>127290717</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9515,37 +9510,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437180</v>
+        <v>437108</v>
       </c>
       <c r="R84" t="n">
-        <v>6764047</v>
+        <v>6763809</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,12 +9599,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9718,7 +9718,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127295863</v>
+        <v>127290757</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9753,10 +9753,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437221</v>
+        <v>437058</v>
       </c>
       <c r="R86" t="n">
-        <v>6763950</v>
+        <v>6763741</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9825,7 +9825,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127291960</v>
+        <v>127295596</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437015</v>
+        <v>437169</v>
       </c>
       <c r="R87" t="n">
-        <v>6763762</v>
+        <v>6763904</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127293022</v>
+        <v>127295863</v>
       </c>
       <c r="B88" t="n">
         <v>79014</v>
@@ -9963,17 +9963,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437081</v>
+        <v>437221</v>
       </c>
       <c r="R88" t="n">
-        <v>6763901</v>
+        <v>6763950</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,60 +10027,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127292822</v>
+        <v>127292924</v>
       </c>
       <c r="B89" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436992</v>
+        <v>437037</v>
       </c>
       <c r="R89" t="n">
-        <v>6763834</v>
+        <v>6763860</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10134,44 +10134,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127295269</v>
+        <v>127291960</v>
       </c>
       <c r="B90" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437297</v>
+        <v>437015</v>
       </c>
       <c r="R90" t="n">
-        <v>6763935</v>
+        <v>6763762</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10253,7 +10253,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127290757</v>
+        <v>127295035</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437058</v>
+        <v>437297</v>
       </c>
       <c r="R91" t="n">
-        <v>6763741</v>
+        <v>6763951</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10360,7 +10360,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127295596</v>
+        <v>127293022</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437169</v>
+        <v>437081</v>
       </c>
       <c r="R92" t="n">
-        <v>6763904</v>
+        <v>6763901</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10467,48 +10467,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127292924</v>
+        <v>127292822</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437037</v>
+        <v>436992</v>
       </c>
       <c r="R93" t="n">
-        <v>6763860</v>
+        <v>6763834</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10562,60 +10562,60 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127295035</v>
+        <v>127292999</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437297</v>
+        <v>437093</v>
       </c>
       <c r="R94" t="n">
-        <v>6763951</v>
+        <v>6763880</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,19 +10669,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127292999</v>
+        <v>127295269</v>
       </c>
       <c r="B95" t="n">
         <v>8447</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437093</v>
+        <v>437297</v>
       </c>
       <c r="R95" t="n">
-        <v>6763880</v>
+        <v>6763935</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293029</v>
+        <v>127293348</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,34 +10799,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437074</v>
+        <v>437154</v>
       </c>
       <c r="R96" t="n">
-        <v>6763890</v>
+        <v>6763925</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10895,27 +10900,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293348</v>
+        <v>127295309</v>
       </c>
       <c r="B97" t="n">
-        <v>57654</v>
+        <v>58027</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10926,7 +10931,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10935,13 +10940,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437154</v>
+        <v>437289</v>
       </c>
       <c r="R97" t="n">
-        <v>6763925</v>
+        <v>6763874</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11444,7 +11449,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127290978</v>
+        <v>127293029</v>
       </c>
       <c r="B102" t="n">
         <v>79014</v>
@@ -11479,10 +11484,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437098</v>
+        <v>437074</v>
       </c>
       <c r="R102" t="n">
-        <v>6763850</v>
+        <v>6763890</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11551,53 +11556,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127295309</v>
+        <v>127290978</v>
       </c>
       <c r="B103" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437289</v>
+        <v>437098</v>
       </c>
       <c r="R103" t="n">
-        <v>6763874</v>
+        <v>6763850</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12096,10 +12096,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127291177</v>
+        <v>127293290</v>
       </c>
       <c r="B108" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12107,21 +12107,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437081</v>
+        <v>437138</v>
       </c>
       <c r="R108" t="n">
-        <v>6763837</v>
+        <v>6763901</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12177,6 +12177,11 @@
       <c r="AB108" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12203,10 +12208,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127293290</v>
+        <v>127291177</v>
       </c>
       <c r="B109" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12214,21 +12219,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437138</v>
+        <v>437081</v>
       </c>
       <c r="R109" t="n">
-        <v>6763901</v>
+        <v>6763837</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12284,11 +12289,6 @@
       <c r="AB109" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12748,10 +12748,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293240</v>
+        <v>127290747</v>
       </c>
       <c r="B114" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12759,37 +12759,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437122</v>
+        <v>437064</v>
       </c>
       <c r="R114" t="n">
-        <v>6763905</v>
+        <v>6763744</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12843,22 +12843,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127294788</v>
+        <v>127293240</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437274</v>
+        <v>437122</v>
       </c>
       <c r="R115" t="n">
-        <v>6764023</v>
+        <v>6763905</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,19 +12950,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127291635</v>
+        <v>127294788</v>
       </c>
       <c r="B116" t="n">
         <v>79014</v>
@@ -12993,17 +12993,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437032</v>
+        <v>437274</v>
       </c>
       <c r="R116" t="n">
-        <v>6763776</v>
+        <v>6764023</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,19 +13057,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127290747</v>
+        <v>127291635</v>
       </c>
       <c r="B117" t="n">
         <v>79014</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437064</v>
+        <v>437032</v>
       </c>
       <c r="R117" t="n">
-        <v>6763744</v>
+        <v>6763776</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,12 +13164,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13935,53 +13935,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127292816</v>
+        <v>127293007</v>
       </c>
       <c r="B125" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436992</v>
+        <v>437076</v>
       </c>
       <c r="R125" t="n">
-        <v>6763834</v>
+        <v>6763849</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14020,7 +14020,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Två torrtallar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14035,62 +14040,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127295889</v>
+        <v>127290736</v>
       </c>
       <c r="B126" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>437244</v>
+        <v>437102</v>
       </c>
       <c r="R126" t="n">
-        <v>6763890</v>
+        <v>6763801</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127293007</v>
+        <v>127292627</v>
       </c>
       <c r="B127" t="n">
         <v>8447</v>
@@ -14199,10 +14199,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>437076</v>
+        <v>437059</v>
       </c>
       <c r="R127" t="n">
-        <v>6763849</v>
+        <v>6763861</v>
       </c>
       <c r="S127" t="n">
         <v>9</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14244,12 +14244,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Två torrtallar</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14276,45 +14271,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127290736</v>
+        <v>127295889</v>
       </c>
       <c r="B128" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437102</v>
+        <v>437244</v>
       </c>
       <c r="R128" t="n">
-        <v>6763801</v>
+        <v>6763890</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14383,53 +14383,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127292627</v>
+        <v>127292816</v>
       </c>
       <c r="B129" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>437059</v>
+        <v>436992</v>
       </c>
       <c r="R129" t="n">
-        <v>6763861</v>
+        <v>6763834</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14483,60 +14483,60 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127295386</v>
+        <v>127293305</v>
       </c>
       <c r="B130" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437233</v>
+        <v>437137</v>
       </c>
       <c r="R130" t="n">
-        <v>6763867</v>
+        <v>6763885</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,60 +14590,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127294021</v>
+        <v>127292761</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437191</v>
+        <v>436992</v>
       </c>
       <c r="R131" t="n">
-        <v>6763952</v>
+        <v>6763834</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14697,44 +14697,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127295217</v>
+        <v>127294311</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14744,10 +14744,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437312</v>
+        <v>437170</v>
       </c>
       <c r="R132" t="n">
-        <v>6763984</v>
+        <v>6764043</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14790,6 +14790,11 @@
       <c r="AB132" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14816,7 +14821,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127293270</v>
+        <v>127295386</v>
       </c>
       <c r="B133" t="n">
         <v>8447</v>
@@ -14847,17 +14852,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437124</v>
+        <v>437233</v>
       </c>
       <c r="R133" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14886,7 +14891,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14896,7 +14901,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14911,44 +14916,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127293305</v>
+        <v>127294021</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14958,10 +14963,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437137</v>
+        <v>437191</v>
       </c>
       <c r="R134" t="n">
-        <v>6763885</v>
+        <v>6763952</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14993,7 +14998,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15003,7 +15008,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15030,32 +15035,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127292761</v>
+        <v>127295217</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15065,10 +15070,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436992</v>
+        <v>437312</v>
       </c>
       <c r="R135" t="n">
-        <v>6763834</v>
+        <v>6763984</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15137,48 +15142,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127294311</v>
+        <v>127293270</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437170</v>
+        <v>437124</v>
       </c>
       <c r="R136" t="n">
-        <v>6764043</v>
+        <v>6763885</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15207,7 +15212,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15217,12 +15222,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127293263</v>
+        <v>127291525</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437138</v>
+        <v>437044</v>
       </c>
       <c r="R17" t="n">
-        <v>6763887</v>
+        <v>6763790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,32 +2397,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293099</v>
+        <v>127290331</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437109</v>
+        <v>437173</v>
       </c>
       <c r="R18" t="n">
-        <v>6763908</v>
+        <v>6763816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127294351</v>
+        <v>127295240</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437151</v>
+        <v>437308</v>
       </c>
       <c r="R19" t="n">
-        <v>6764039</v>
+        <v>6763966</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295941</v>
+        <v>127293263</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437223</v>
+        <v>437138</v>
       </c>
       <c r="R20" t="n">
-        <v>6763922</v>
+        <v>6763887</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127291525</v>
+        <v>127293099</v>
       </c>
       <c r="B21" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437044</v>
+        <v>437109</v>
       </c>
       <c r="R21" t="n">
-        <v>6763790</v>
+        <v>6763908</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290331</v>
+        <v>127294351</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437173</v>
+        <v>437151</v>
       </c>
       <c r="R22" t="n">
-        <v>6763816</v>
+        <v>6764039</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,48 +2932,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295240</v>
+        <v>127295941</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437308</v>
+        <v>437223</v>
       </c>
       <c r="R23" t="n">
-        <v>6763966</v>
+        <v>6763922</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,12 +3027,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6707,48 +6707,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127293858</v>
+        <v>127294772</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437201</v>
+        <v>437255</v>
       </c>
       <c r="R58" t="n">
-        <v>6763976</v>
+        <v>6764049</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,62 +6802,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127290454</v>
+        <v>127294736</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437078</v>
+        <v>437212</v>
       </c>
       <c r="R59" t="n">
-        <v>6763737</v>
+        <v>6764065</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6889,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6899,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6926,10 +6921,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127291537</v>
+        <v>127294985</v>
       </c>
       <c r="B60" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6937,37 +6932,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437044</v>
+        <v>437293</v>
       </c>
       <c r="R60" t="n">
-        <v>6763790</v>
+        <v>6763965</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6996,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7006,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,19 +7016,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294772</v>
+        <v>127294411</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -7068,10 +7063,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437255</v>
+        <v>437202</v>
       </c>
       <c r="R61" t="n">
-        <v>6764049</v>
+        <v>6764041</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7103,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,7 +7135,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294736</v>
+        <v>127294416</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -7171,17 +7166,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437212</v>
+        <v>437158</v>
       </c>
       <c r="R62" t="n">
-        <v>6764065</v>
+        <v>6764069</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7205,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7215,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,19 +7230,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127294985</v>
+        <v>127295806</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -7282,10 +7277,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437293</v>
+        <v>437212</v>
       </c>
       <c r="R63" t="n">
-        <v>6763965</v>
+        <v>6763955</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7317,7 +7312,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7327,7 +7322,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7354,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127294411</v>
+        <v>127293072</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7365,37 +7360,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437202</v>
+        <v>437081</v>
       </c>
       <c r="R64" t="n">
-        <v>6764041</v>
+        <v>6763901</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7424,7 +7419,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7429,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,22 +7444,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127294416</v>
+        <v>127291537</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7472,21 +7467,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7496,10 +7491,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437158</v>
+        <v>437044</v>
       </c>
       <c r="R65" t="n">
-        <v>6764069</v>
+        <v>6763790</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7568,48 +7563,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127295806</v>
+        <v>127293858</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437212</v>
+        <v>437201</v>
       </c>
       <c r="R66" t="n">
-        <v>6763955</v>
+        <v>6763976</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7638,7 +7633,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7643,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7663,60 +7658,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127293072</v>
+        <v>127290454</v>
       </c>
       <c r="B67" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437081</v>
+        <v>437078</v>
       </c>
       <c r="R67" t="n">
-        <v>6763901</v>
+        <v>6763737</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,44 +7770,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290826</v>
+        <v>127290713</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437081</v>
+        <v>437108</v>
       </c>
       <c r="R68" t="n">
-        <v>6763837</v>
+        <v>6763809</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,48 +7889,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127290751</v>
+        <v>127292742</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437062</v>
+        <v>437089</v>
       </c>
       <c r="R69" t="n">
-        <v>6763738</v>
+        <v>6763838</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,44 +7984,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B70" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R70" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,32 +8103,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290713</v>
+        <v>127290826</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R71" t="n">
-        <v>6763809</v>
+        <v>6763837</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,48 +8210,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127292742</v>
+        <v>127290751</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437089</v>
+        <v>437062</v>
       </c>
       <c r="R72" t="n">
-        <v>6763838</v>
+        <v>6763738</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,44 +8305,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127294714</v>
+        <v>127290959</v>
       </c>
       <c r="B73" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437204</v>
+        <v>437097</v>
       </c>
       <c r="R73" t="n">
-        <v>6764046</v>
+        <v>6763868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -11663,45 +11663,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127294008</v>
+        <v>127294074</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437190</v>
+        <v>437189</v>
       </c>
       <c r="R104" t="n">
-        <v>6763955</v>
+        <v>6763951</v>
       </c>
       <c r="S104" t="n">
         <v>9</v>
@@ -11733,7 +11738,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11743,7 +11748,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11770,32 +11775,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127292751</v>
+        <v>127293475</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11805,10 +11810,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436974</v>
+        <v>437136</v>
       </c>
       <c r="R105" t="n">
-        <v>6763823</v>
+        <v>6763963</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11877,50 +11882,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127294074</v>
+        <v>127294008</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>437189</v>
+        <v>437190</v>
       </c>
       <c r="R106" t="n">
-        <v>6763951</v>
+        <v>6763955</v>
       </c>
       <c r="S106" t="n">
         <v>9</v>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11989,32 +11989,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127293475</v>
+        <v>127292751</v>
       </c>
       <c r="B107" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>437136</v>
+        <v>436974</v>
       </c>
       <c r="R107" t="n">
-        <v>6763963</v>
+        <v>6763823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13283,48 +13283,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127291536</v>
+        <v>127290203</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436972</v>
+        <v>437188</v>
       </c>
       <c r="R119" t="n">
-        <v>6763733</v>
+        <v>6763793</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,7 +13363,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13378,44 +13383,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127293427</v>
+        <v>127290773</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13425,10 +13430,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437147</v>
+        <v>437081</v>
       </c>
       <c r="R120" t="n">
-        <v>6763942</v>
+        <v>6763812</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13497,7 +13502,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127293635</v>
+        <v>127291536</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13528,17 +13533,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437130</v>
+        <v>436972</v>
       </c>
       <c r="R121" t="n">
-        <v>6763988</v>
+        <v>6763733</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13567,7 +13572,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13577,7 +13582,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13592,22 +13597,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290001</v>
+        <v>127293427</v>
       </c>
       <c r="B122" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13615,42 +13620,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437239</v>
+        <v>437147</v>
       </c>
       <c r="R122" t="n">
-        <v>6763818</v>
+        <v>6763942</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290203</v>
+        <v>127293635</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437188</v>
+        <v>437130</v>
       </c>
       <c r="R123" t="n">
-        <v>6763793</v>
+        <v>6763988</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,11 +13797,6 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13828,48 +13823,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290773</v>
+        <v>127290001</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57817</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437081</v>
+        <v>437239</v>
       </c>
       <c r="R124" t="n">
-        <v>6763812</v>
+        <v>6763818</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127291525</v>
+        <v>127293263</v>
       </c>
       <c r="B17" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437044</v>
+        <v>437138</v>
       </c>
       <c r="R17" t="n">
-        <v>6763790</v>
+        <v>6763887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,32 +2397,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127290331</v>
+        <v>127293099</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437173</v>
+        <v>437109</v>
       </c>
       <c r="R18" t="n">
-        <v>6763816</v>
+        <v>6763908</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295240</v>
+        <v>127294351</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437308</v>
+        <v>437151</v>
       </c>
       <c r="R19" t="n">
-        <v>6763966</v>
+        <v>6764039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127293263</v>
+        <v>127295941</v>
       </c>
       <c r="B20" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437138</v>
+        <v>437223</v>
       </c>
       <c r="R20" t="n">
-        <v>6763887</v>
+        <v>6763922</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127293099</v>
+        <v>127291525</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437109</v>
+        <v>437044</v>
       </c>
       <c r="R21" t="n">
-        <v>6763908</v>
+        <v>6763790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127294351</v>
+        <v>127290331</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437151</v>
+        <v>437173</v>
       </c>
       <c r="R22" t="n">
-        <v>6764039</v>
+        <v>6763816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,48 +2932,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295941</v>
+        <v>127295240</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437223</v>
+        <v>437308</v>
       </c>
       <c r="R23" t="n">
-        <v>6763922</v>
+        <v>6763966</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,60 +3027,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293735</v>
+        <v>127293241</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437156</v>
+        <v>437135</v>
       </c>
       <c r="R24" t="n">
-        <v>6763978</v>
+        <v>6763885</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3109,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,60 +3139,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295078</v>
+        <v>127293161</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437293</v>
+        <v>437098</v>
       </c>
       <c r="R25" t="n">
-        <v>6763940</v>
+        <v>6763941</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,60 +3246,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294346</v>
+        <v>127292736</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437187</v>
+        <v>436991</v>
       </c>
       <c r="R26" t="n">
-        <v>6764029</v>
+        <v>6763816</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3323,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,22 +3353,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293820</v>
+        <v>127293735</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,39 +3376,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437201</v>
+        <v>437156</v>
       </c>
       <c r="R27" t="n">
-        <v>6763976</v>
+        <v>6763978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295384</v>
+        <v>127295078</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3483,42 +3483,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437233</v>
+        <v>437293</v>
       </c>
       <c r="R28" t="n">
-        <v>6763867</v>
+        <v>6763940</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3547,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,62 +3567,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127293241</v>
+        <v>127294346</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437135</v>
+        <v>437187</v>
       </c>
       <c r="R29" t="n">
-        <v>6763885</v>
+        <v>6764029</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3659,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,45 +3686,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293161</v>
+        <v>127293820</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437098</v>
+        <v>437201</v>
       </c>
       <c r="R30" t="n">
-        <v>6763941</v>
+        <v>6763976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3803,45 +3798,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127292736</v>
+        <v>127295384</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436991</v>
+        <v>437233</v>
       </c>
       <c r="R31" t="n">
-        <v>6763816</v>
+        <v>6763867</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -5306,32 +5306,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127290540</v>
+        <v>127292927</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437113</v>
+        <v>437032</v>
       </c>
       <c r="R45" t="n">
-        <v>6763817</v>
+        <v>6763858</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,32 +5413,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127294782</v>
+        <v>127294741</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437273</v>
+        <v>437209</v>
       </c>
       <c r="R46" t="n">
-        <v>6764025</v>
+        <v>6764061</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,7 +5520,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292927</v>
+        <v>127292980</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5551,17 +5551,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437032</v>
+        <v>437068</v>
       </c>
       <c r="R47" t="n">
         <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127294741</v>
+        <v>127295897</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,37 +5638,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437209</v>
+        <v>437244</v>
       </c>
       <c r="R48" t="n">
-        <v>6764061</v>
+        <v>6763890</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127292980</v>
+        <v>127293956</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5765,17 +5765,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437068</v>
+        <v>437202</v>
       </c>
       <c r="R49" t="n">
-        <v>6763858</v>
+        <v>6764007</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5829,22 +5829,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295897</v>
+        <v>127291031</v>
       </c>
       <c r="B50" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437244</v>
+        <v>437097</v>
       </c>
       <c r="R50" t="n">
-        <v>6763890</v>
+        <v>6763850</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,10 +5948,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127293956</v>
+        <v>127290803</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5959,34 +5959,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437202</v>
+        <v>437091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764007</v>
+        <v>6763822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,32 +6060,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127291031</v>
+        <v>127290540</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6090,10 +6095,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437097</v>
+        <v>437113</v>
       </c>
       <c r="R52" t="n">
-        <v>6763850</v>
+        <v>6763817</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6162,53 +6167,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127290803</v>
+        <v>127294782</v>
       </c>
       <c r="B53" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437091</v>
+        <v>437273</v>
       </c>
       <c r="R53" t="n">
-        <v>6763822</v>
+        <v>6764025</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,44 +6262,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127293209</v>
+        <v>127291397</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>91346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437116</v>
+        <v>437058</v>
       </c>
       <c r="R54" t="n">
-        <v>6763949</v>
+        <v>6763796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127291397</v>
+        <v>127290094</v>
       </c>
       <c r="B55" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437058</v>
+        <v>437239</v>
       </c>
       <c r="R55" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,6 +6462,11 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6488,7 +6493,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127290094</v>
+        <v>127290996</v>
       </c>
       <c r="B56" t="n">
         <v>79014</v>
@@ -6523,13 +6528,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437239</v>
+        <v>437108</v>
       </c>
       <c r="R56" t="n">
-        <v>6763818</v>
+        <v>6763849</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6569,11 +6574,6 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6600,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127290996</v>
+        <v>127293209</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437108</v>
+        <v>437116</v>
       </c>
       <c r="R57" t="n">
-        <v>6763849</v>
+        <v>6763949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8424,48 +8424,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127294334</v>
+        <v>127292676</v>
       </c>
       <c r="B74" t="n">
-        <v>91346</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437170</v>
+        <v>437043</v>
       </c>
       <c r="R74" t="n">
-        <v>6764043</v>
+        <v>6763840</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8519,22 +8524,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127295799</v>
+        <v>127294334</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8547,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,10 +8571,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437234</v>
+        <v>437170</v>
       </c>
       <c r="R75" t="n">
-        <v>6763858</v>
+        <v>6764043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8638,7 +8643,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127294842</v>
+        <v>127295799</v>
       </c>
       <c r="B76" t="n">
         <v>79014</v>
@@ -8673,10 +8678,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437280</v>
+        <v>437234</v>
       </c>
       <c r="R76" t="n">
-        <v>6764030</v>
+        <v>6763858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8745,53 +8750,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B77" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R77" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293897</v>
+        <v>127290717</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,34 +8868,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437180</v>
+        <v>437108</v>
       </c>
       <c r="R78" t="n">
-        <v>6763986</v>
+        <v>6763809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8964,32 +8969,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293677</v>
+        <v>127293090</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8999,10 +9004,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437148</v>
+        <v>437081</v>
       </c>
       <c r="R79" t="n">
-        <v>6764001</v>
+        <v>6763901</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9071,7 +9076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293789</v>
+        <v>127293897</v>
       </c>
       <c r="B80" t="n">
         <v>79014</v>
@@ -9106,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437218</v>
+        <v>437180</v>
       </c>
       <c r="R80" t="n">
-        <v>6763950</v>
+        <v>6763986</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9178,7 +9183,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127294716</v>
+        <v>127293677</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -9209,17 +9214,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437199</v>
+        <v>437148</v>
       </c>
       <c r="R81" t="n">
-        <v>6764063</v>
+        <v>6764001</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9248,7 +9253,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9258,7 +9263,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,19 +9278,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293504</v>
+        <v>127293789</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -9320,10 +9325,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437136</v>
+        <v>437218</v>
       </c>
       <c r="R82" t="n">
-        <v>6763963</v>
+        <v>6763950</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9392,7 +9397,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294433</v>
+        <v>127294716</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -9427,10 +9432,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437180</v>
+        <v>437199</v>
       </c>
       <c r="R83" t="n">
-        <v>6764047</v>
+        <v>6764063</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -9462,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9472,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9499,10 +9504,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127290717</v>
+        <v>127293504</v>
       </c>
       <c r="B84" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9510,39 +9515,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437108</v>
+        <v>437136</v>
       </c>
       <c r="R84" t="n">
-        <v>6763809</v>
+        <v>6763963</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9611,48 +9611,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127293090</v>
+        <v>127294433</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437081</v>
+        <v>437180</v>
       </c>
       <c r="R85" t="n">
-        <v>6763901</v>
+        <v>6764047</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,12 +9706,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293348</v>
+        <v>127293586</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,42 +10799,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437154</v>
+        <v>437163</v>
       </c>
       <c r="R96" t="n">
-        <v>6763925</v>
+        <v>6763902</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10863,7 +10858,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10873,7 +10868,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10888,65 +10883,69 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127295309</v>
+        <v>127293953</v>
       </c>
       <c r="B97" t="n">
-        <v>58027</v>
+        <v>91346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437289</v>
+        <v>437190</v>
       </c>
       <c r="R97" t="n">
-        <v>6763874</v>
+        <v>6763937</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10975,7 +10974,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10984,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11000,19 +10999,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293586</v>
+        <v>127293371</v>
       </c>
       <c r="B98" t="n">
         <v>79014</v>
@@ -11043,17 +11042,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437163</v>
+        <v>437140</v>
       </c>
       <c r="R98" t="n">
-        <v>6763902</v>
+        <v>6763931</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11082,7 +11081,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11091,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,22 +11106,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293953</v>
+        <v>127293249</v>
       </c>
       <c r="B99" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,43 +11129,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437190</v>
+        <v>437134</v>
       </c>
       <c r="R99" t="n">
-        <v>6763937</v>
+        <v>6763889</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -11198,7 +11188,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11208,7 +11198,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11235,7 +11225,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293371</v>
+        <v>127293029</v>
       </c>
       <c r="B100" t="n">
         <v>79014</v>
@@ -11270,10 +11260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437140</v>
+        <v>437074</v>
       </c>
       <c r="R100" t="n">
-        <v>6763931</v>
+        <v>6763890</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11342,7 +11332,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293249</v>
+        <v>127290978</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11373,17 +11363,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437134</v>
+        <v>437098</v>
       </c>
       <c r="R101" t="n">
-        <v>6763889</v>
+        <v>6763850</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11412,7 +11402,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11422,7 +11412,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11437,22 +11427,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293029</v>
+        <v>127293348</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11460,34 +11450,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437074</v>
+        <v>437154</v>
       </c>
       <c r="R102" t="n">
-        <v>6763890</v>
+        <v>6763925</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11556,48 +11551,53 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127290978</v>
+        <v>127295309</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437098</v>
+        <v>437289</v>
       </c>
       <c r="R103" t="n">
-        <v>6763850</v>
+        <v>6763874</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13283,48 +13283,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127290203</v>
+        <v>127291536</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>437188</v>
+        <v>436972</v>
       </c>
       <c r="R119" t="n">
-        <v>6763793</v>
+        <v>6763733</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,12 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13383,44 +13378,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127290773</v>
+        <v>127293427</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13430,10 +13425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437081</v>
+        <v>437147</v>
       </c>
       <c r="R120" t="n">
-        <v>6763812</v>
+        <v>6763942</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13502,7 +13497,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127291536</v>
+        <v>127293635</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13533,17 +13528,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436972</v>
+        <v>437130</v>
       </c>
       <c r="R121" t="n">
-        <v>6763733</v>
+        <v>6763988</v>
       </c>
       <c r="S121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13572,7 +13567,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13582,7 +13577,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13597,22 +13592,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127293427</v>
+        <v>127290001</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13620,37 +13615,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437147</v>
+        <v>437239</v>
       </c>
       <c r="R122" t="n">
-        <v>6763942</v>
+        <v>6763818</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127293635</v>
+        <v>127290203</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437130</v>
+        <v>437188</v>
       </c>
       <c r="R123" t="n">
-        <v>6763988</v>
+        <v>6763793</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,6 +13797,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13823,53 +13828,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290001</v>
+        <v>127290773</v>
       </c>
       <c r="B124" t="n">
-        <v>57817</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437239</v>
+        <v>437081</v>
       </c>
       <c r="R124" t="n">
-        <v>6763818</v>
+        <v>6763812</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295759</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127293774</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295923</v>
+        <v>127294146</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437244</v>
+        <v>437131</v>
       </c>
       <c r="R4" t="n">
-        <v>6763901</v>
+        <v>6764010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294146</v>
+        <v>127294422</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,17 +1027,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437131</v>
+        <v>437193</v>
       </c>
       <c r="R5" t="n">
-        <v>6764010</v>
+        <v>6764064</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294422</v>
+        <v>127291489</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,17 +1134,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437193</v>
+        <v>437044</v>
       </c>
       <c r="R6" t="n">
-        <v>6764064</v>
+        <v>6763790</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127291489</v>
+        <v>127290437</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437044</v>
+        <v>437157</v>
       </c>
       <c r="R7" t="n">
-        <v>6763790</v>
+        <v>6763806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127290437</v>
+        <v>127295045</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,17 +1348,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437157</v>
+        <v>437295</v>
       </c>
       <c r="R8" t="n">
-        <v>6763806</v>
+        <v>6763947</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295045</v>
+        <v>127295923</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,37 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437295</v>
+        <v>437244</v>
       </c>
       <c r="R9" t="n">
-        <v>6763947</v>
+        <v>6763901</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,12 +1519,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>127295019</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>127293337</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127294354</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127294721</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127291056</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>127294041</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>127294738</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127293263</v>
+        <v>127290331</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437138</v>
+        <v>437173</v>
       </c>
       <c r="R17" t="n">
-        <v>6763887</v>
+        <v>6763816</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,32 +2397,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293099</v>
+        <v>127295240</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437109</v>
+        <v>437308</v>
       </c>
       <c r="R18" t="n">
-        <v>6763908</v>
+        <v>6763966</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127294351</v>
+        <v>127293099</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437151</v>
+        <v>437109</v>
       </c>
       <c r="R19" t="n">
-        <v>6764039</v>
+        <v>6763908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295941</v>
+        <v>127291525</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437223</v>
+        <v>437044</v>
       </c>
       <c r="R20" t="n">
-        <v>6763922</v>
+        <v>6763790</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127291525</v>
+        <v>127294351</v>
       </c>
       <c r="B21" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437044</v>
+        <v>437151</v>
       </c>
       <c r="R21" t="n">
-        <v>6763790</v>
+        <v>6764039</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,48 +2825,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127290331</v>
+        <v>127295941</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437173</v>
+        <v>437223</v>
       </c>
       <c r="R22" t="n">
-        <v>6763816</v>
+        <v>6763922</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,44 +2920,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295240</v>
+        <v>127293263</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437308</v>
+        <v>437138</v>
       </c>
       <c r="R23" t="n">
-        <v>6763966</v>
+        <v>6763887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,53 +3039,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293241</v>
+        <v>127293735</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437135</v>
+        <v>437156</v>
       </c>
       <c r="R24" t="n">
-        <v>6763885</v>
+        <v>6763978</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,60 +3134,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127293161</v>
+        <v>127295078</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437098</v>
+        <v>437293</v>
       </c>
       <c r="R25" t="n">
-        <v>6763941</v>
+        <v>6763940</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,60 +3241,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127292736</v>
+        <v>127294346</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436991</v>
+        <v>437187</v>
       </c>
       <c r="R26" t="n">
-        <v>6763816</v>
+        <v>6764029</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3328,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,22 +3348,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293735</v>
+        <v>127293820</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,34 +3371,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437156</v>
+        <v>437201</v>
       </c>
       <c r="R27" t="n">
-        <v>6763978</v>
+        <v>6763976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295078</v>
+        <v>127295384</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3483,37 +3483,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437293</v>
+        <v>437233</v>
       </c>
       <c r="R28" t="n">
-        <v>6763940</v>
+        <v>6763867</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,57 +3572,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127294346</v>
+        <v>127293241</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437187</v>
+        <v>437135</v>
       </c>
       <c r="R29" t="n">
-        <v>6764029</v>
+        <v>6763885</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3649,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,50 +3696,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293820</v>
+        <v>127293161</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437201</v>
+        <v>437098</v>
       </c>
       <c r="R30" t="n">
-        <v>6763976</v>
+        <v>6763941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,50 +3803,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295384</v>
+        <v>127292736</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437233</v>
+        <v>436991</v>
       </c>
       <c r="R31" t="n">
-        <v>6763867</v>
+        <v>6763816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
         <v>127294136</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>127293914</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>127293203</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>127295057</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>127293696</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>127293981</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295245</v>
+        <v>127293212</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437308</v>
+        <v>437120</v>
       </c>
       <c r="R38" t="n">
-        <v>6763966</v>
+        <v>6763919</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127292954</v>
+        <v>127294037</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437050</v>
+        <v>437188</v>
       </c>
       <c r="R39" t="n">
-        <v>6763860</v>
+        <v>6763952</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127290586</v>
+        <v>127295245</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4802,17 +4802,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437065</v>
+        <v>437308</v>
       </c>
       <c r="R40" t="n">
-        <v>6763754</v>
+        <v>6763966</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,22 +4866,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127292669</v>
+        <v>127292954</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,37 +4889,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437023</v>
+        <v>437050</v>
       </c>
       <c r="R41" t="n">
-        <v>6763818</v>
+        <v>6763860</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,22 +4973,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127291424</v>
+        <v>127292669</v>
       </c>
       <c r="B42" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437058</v>
+        <v>437023</v>
       </c>
       <c r="R42" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,48 +5092,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127293212</v>
+        <v>127290586</v>
       </c>
       <c r="B43" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437120</v>
+        <v>437065</v>
       </c>
       <c r="R43" t="n">
-        <v>6763919</v>
+        <v>6763754</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,60 +5187,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127294037</v>
+        <v>127291424</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437188</v>
+        <v>437058</v>
       </c>
       <c r="R44" t="n">
-        <v>6763952</v>
+        <v>6763796</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,12 +5294,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
         <v>127292927</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>127294741</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>127292980</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295897</v>
+        <v>127293956</v>
       </c>
       <c r="B48" t="n">
-        <v>91346</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437244</v>
+        <v>437202</v>
       </c>
       <c r="R48" t="n">
-        <v>6763890</v>
+        <v>6764007</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127293956</v>
+        <v>127291031</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437202</v>
+        <v>437097</v>
       </c>
       <c r="R49" t="n">
-        <v>6764007</v>
+        <v>6763850</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127291031</v>
+        <v>127295897</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>91350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437097</v>
+        <v>437244</v>
       </c>
       <c r="R50" t="n">
-        <v>6763850</v>
+        <v>6763890</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
         <v>127290803</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>127290540</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>127294782</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6274,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127291397</v>
+        <v>127293209</v>
       </c>
       <c r="B54" t="n">
-        <v>91346</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437058</v>
+        <v>437116</v>
       </c>
       <c r="R54" t="n">
-        <v>6763796</v>
+        <v>6763949</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
         <v>127290094</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>127290996</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127293209</v>
+        <v>127291397</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>91350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437116</v>
+        <v>437058</v>
       </c>
       <c r="R57" t="n">
-        <v>6763949</v>
+        <v>6763796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6710,7 +6710,7 @@
         <v>127294772</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>127294736</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127294985</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>127294411</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>127294416</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>127295806</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>127293072</v>
       </c>
       <c r="B64" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>127291537</v>
       </c>
       <c r="B65" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>127293858</v>
       </c>
       <c r="B66" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>127290454</v>
       </c>
       <c r="B67" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290713</v>
+        <v>127290959</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>91350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437108</v>
+        <v>437097</v>
       </c>
       <c r="R68" t="n">
-        <v>6763809</v>
+        <v>6763868</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,32 +7889,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127292742</v>
+        <v>127290826</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437089</v>
+        <v>437081</v>
       </c>
       <c r="R69" t="n">
-        <v>6763838</v>
+        <v>6763837</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7996,48 +7996,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127294714</v>
+        <v>127290751</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437204</v>
+        <v>437062</v>
       </c>
       <c r="R70" t="n">
-        <v>6764046</v>
+        <v>6763738</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8091,44 +8091,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290826</v>
+        <v>127290713</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437081</v>
+        <v>437108</v>
       </c>
       <c r="R71" t="n">
-        <v>6763837</v>
+        <v>6763809</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,48 +8210,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127290751</v>
+        <v>127292742</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437062</v>
+        <v>437089</v>
       </c>
       <c r="R72" t="n">
-        <v>6763738</v>
+        <v>6763838</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,44 +8305,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B73" t="n">
-        <v>91346</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R73" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,53 +8424,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127292676</v>
+        <v>127295799</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437043</v>
+        <v>437234</v>
       </c>
       <c r="R74" t="n">
-        <v>6763840</v>
+        <v>6763858</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8524,22 +8519,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127294334</v>
+        <v>127294842</v>
       </c>
       <c r="B75" t="n">
-        <v>91346</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8547,21 +8542,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437170</v>
+        <v>437280</v>
       </c>
       <c r="R75" t="n">
-        <v>6764043</v>
+        <v>6764030</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8643,10 +8638,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127295799</v>
+        <v>127294334</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>91350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8654,21 +8649,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8678,10 +8673,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437234</v>
+        <v>437170</v>
       </c>
       <c r="R76" t="n">
-        <v>6763858</v>
+        <v>6764043</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8750,48 +8745,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R77" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127290717</v>
+        <v>127293897</v>
       </c>
       <c r="B78" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,39 +8868,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437108</v>
+        <v>437180</v>
       </c>
       <c r="R78" t="n">
-        <v>6763809</v>
+        <v>6763986</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8969,32 +8964,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293090</v>
+        <v>127293677</v>
       </c>
       <c r="B79" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9004,10 +8999,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437081</v>
+        <v>437148</v>
       </c>
       <c r="R79" t="n">
-        <v>6763901</v>
+        <v>6764001</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9076,10 +9071,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293897</v>
+        <v>127293789</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9111,10 +9106,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437180</v>
+        <v>437218</v>
       </c>
       <c r="R80" t="n">
-        <v>6763986</v>
+        <v>6763950</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9183,10 +9178,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127293677</v>
+        <v>127294716</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9214,17 +9209,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437148</v>
+        <v>437199</v>
       </c>
       <c r="R81" t="n">
-        <v>6764001</v>
+        <v>6764063</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9253,7 +9248,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9263,7 +9258,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9278,22 +9273,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293789</v>
+        <v>127293504</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9325,10 +9320,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437218</v>
+        <v>437136</v>
       </c>
       <c r="R82" t="n">
-        <v>6763950</v>
+        <v>6763963</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9397,10 +9392,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294716</v>
+        <v>127294433</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9432,10 +9427,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437199</v>
+        <v>437180</v>
       </c>
       <c r="R83" t="n">
-        <v>6764063</v>
+        <v>6764047</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -9467,7 +9462,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9477,7 +9472,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9504,32 +9499,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127293504</v>
+        <v>127293090</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9539,10 +9534,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437136</v>
+        <v>437081</v>
       </c>
       <c r="R84" t="n">
-        <v>6763963</v>
+        <v>6763901</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9611,10 +9606,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127294433</v>
+        <v>127290717</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9622,37 +9617,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437180</v>
+        <v>437108</v>
       </c>
       <c r="R85" t="n">
-        <v>6764047</v>
+        <v>6763809</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,12 +9706,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9721,7 +9721,7 @@
         <v>127290757</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>127295596</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>127295863</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>127292924</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>127291960</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>127295035</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>127293022</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>127292822</v>
       </c>
       <c r="B93" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>127292999</v>
       </c>
       <c r="B94" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>127295269</v>
       </c>
       <c r="B95" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>127293586</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293953</v>
+        <v>127293371</v>
       </c>
       <c r="B97" t="n">
-        <v>91346</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10906,46 +10906,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437190</v>
+        <v>437140</v>
       </c>
       <c r="R97" t="n">
-        <v>6763937</v>
+        <v>6763931</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10974,7 +10965,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10984,7 +10975,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10999,22 +10990,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293371</v>
+        <v>127293249</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11042,17 +11033,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437140</v>
+        <v>437134</v>
       </c>
       <c r="R98" t="n">
-        <v>6763931</v>
+        <v>6763889</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11081,7 +11072,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11091,7 +11082,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11106,22 +11097,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293249</v>
+        <v>127293029</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11149,17 +11140,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437134</v>
+        <v>437074</v>
       </c>
       <c r="R99" t="n">
-        <v>6763889</v>
+        <v>6763890</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11188,7 +11179,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11198,7 +11189,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11213,22 +11204,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293029</v>
+        <v>127290978</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11260,10 +11251,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437074</v>
+        <v>437098</v>
       </c>
       <c r="R100" t="n">
-        <v>6763890</v>
+        <v>6763850</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11332,10 +11323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127290978</v>
+        <v>127293953</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>91350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11343,37 +11334,46 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437098</v>
+        <v>437190</v>
       </c>
       <c r="R101" t="n">
-        <v>6763850</v>
+        <v>6763937</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11427,12 +11427,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11442,7 +11442,7 @@
         <v>127293348</v>
       </c>
       <c r="B102" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>127295309</v>
       </c>
       <c r="B103" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11663,50 +11663,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127294074</v>
+        <v>127294008</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437189</v>
+        <v>437190</v>
       </c>
       <c r="R104" t="n">
-        <v>6763951</v>
+        <v>6763955</v>
       </c>
       <c r="S104" t="n">
         <v>9</v>
@@ -11738,7 +11733,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11748,7 +11743,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11775,32 +11770,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127293475</v>
+        <v>127292751</v>
       </c>
       <c r="B105" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11810,10 +11805,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>437136</v>
+        <v>436974</v>
       </c>
       <c r="R105" t="n">
-        <v>6763963</v>
+        <v>6763823</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11882,45 +11877,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127294008</v>
+        <v>127294074</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>437190</v>
+        <v>437189</v>
       </c>
       <c r="R106" t="n">
-        <v>6763955</v>
+        <v>6763951</v>
       </c>
       <c r="S106" t="n">
         <v>9</v>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11989,32 +11989,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127292751</v>
+        <v>127293475</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436974</v>
+        <v>437136</v>
       </c>
       <c r="R107" t="n">
-        <v>6763823</v>
+        <v>6763963</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12096,10 +12096,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127293290</v>
+        <v>127291177</v>
       </c>
       <c r="B108" t="n">
-        <v>91346</v>
+        <v>79636</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12107,21 +12107,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437138</v>
+        <v>437081</v>
       </c>
       <c r="R108" t="n">
-        <v>6763901</v>
+        <v>6763837</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12177,11 +12177,6 @@
       <c r="AB108" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12208,48 +12203,53 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127291177</v>
+        <v>127292727</v>
       </c>
       <c r="B109" t="n">
-        <v>79632</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437081</v>
+        <v>437043</v>
       </c>
       <c r="R109" t="n">
-        <v>6763837</v>
+        <v>6763856</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12303,22 +12303,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127292727</v>
+        <v>127290265</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,24 +12344,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437043</v>
+        <v>437187</v>
       </c>
       <c r="R110" t="n">
-        <v>6763856</v>
+        <v>6763801</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12390,7 +12385,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12400,7 +12395,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12415,22 +12410,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127290265</v>
+        <v>127294388</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12458,17 +12453,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437187</v>
+        <v>437183</v>
       </c>
       <c r="R111" t="n">
-        <v>6763801</v>
+        <v>6764033</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12497,7 +12492,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12507,7 +12502,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12522,60 +12517,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127294388</v>
+        <v>127293290</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>91350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437183</v>
+        <v>437138</v>
       </c>
       <c r="R112" t="n">
-        <v>6764033</v>
+        <v>6763901</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12604,7 +12599,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12614,7 +12609,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12629,12 +12629,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12644,7 +12644,7 @@
         <v>127293262</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>127290747</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12855,10 +12855,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127293240</v>
+        <v>127294788</v>
       </c>
       <c r="B115" t="n">
-        <v>91346</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437122</v>
+        <v>437274</v>
       </c>
       <c r="R115" t="n">
-        <v>6763905</v>
+        <v>6764023</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127294788</v>
+        <v>127291635</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12993,17 +12993,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437274</v>
+        <v>437032</v>
       </c>
       <c r="R116" t="n">
-        <v>6764023</v>
+        <v>6763776</v>
       </c>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,22 +13057,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127291635</v>
+        <v>127293240</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>91350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13080,21 +13080,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13104,10 +13104,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437032</v>
+        <v>437122</v>
       </c>
       <c r="R117" t="n">
-        <v>6763776</v>
+        <v>6763905</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13179,7 +13179,7 @@
         <v>127293766</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>127291536</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>127293427</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>127293635</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13604,53 +13604,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290001</v>
+        <v>127290203</v>
       </c>
       <c r="B122" t="n">
-        <v>57817</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437239</v>
+        <v>437188</v>
       </c>
       <c r="R122" t="n">
-        <v>6763818</v>
+        <v>6763793</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13690,6 +13685,11 @@
       <c r="AB122" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13716,10 +13716,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290203</v>
+        <v>127290773</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437188</v>
+        <v>437081</v>
       </c>
       <c r="R123" t="n">
-        <v>6763793</v>
+        <v>6763812</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,11 +13797,6 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13828,48 +13823,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290773</v>
+        <v>127290001</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57821</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437081</v>
+        <v>437239</v>
       </c>
       <c r="R124" t="n">
-        <v>6763812</v>
+        <v>6763818</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>127293007</v>
       </c>
       <c r="B125" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>127290736</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>127292627</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>127295889</v>
       </c>
       <c r="B128" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>127292816</v>
       </c>
       <c r="B129" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14495,48 +14495,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127293305</v>
+        <v>127295386</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437137</v>
+        <v>437233</v>
       </c>
       <c r="R130" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,60 +14590,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127292761</v>
+        <v>127294021</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436992</v>
+        <v>437191</v>
       </c>
       <c r="R131" t="n">
-        <v>6763834</v>
+        <v>6763952</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14697,44 +14697,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127294311</v>
+        <v>127295217</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14744,10 +14744,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437170</v>
+        <v>437312</v>
       </c>
       <c r="R132" t="n">
-        <v>6764043</v>
+        <v>6763984</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14790,11 +14790,6 @@
       <c r="AB132" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14821,10 +14816,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295386</v>
+        <v>127293270</v>
       </c>
       <c r="B133" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14852,17 +14847,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437233</v>
+        <v>437124</v>
       </c>
       <c r="R133" t="n">
-        <v>6763867</v>
+        <v>6763885</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14891,7 +14886,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14901,7 +14896,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14916,44 +14911,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127294021</v>
+        <v>127293305</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14963,10 +14958,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437191</v>
+        <v>437137</v>
       </c>
       <c r="R134" t="n">
-        <v>6763952</v>
+        <v>6763885</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14998,7 +14993,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15008,7 +15003,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15035,32 +15030,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127295217</v>
+        <v>127292761</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15070,10 +15065,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437312</v>
+        <v>436992</v>
       </c>
       <c r="R135" t="n">
-        <v>6763984</v>
+        <v>6763834</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15142,48 +15137,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127293270</v>
+        <v>127294311</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437124</v>
+        <v>437170</v>
       </c>
       <c r="R136" t="n">
-        <v>6763885</v>
+        <v>6764043</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15212,7 +15207,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15222,7 +15217,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295759</v>
+        <v>127295019</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437218</v>
+        <v>437299</v>
       </c>
       <c r="R2" t="n">
-        <v>6763878</v>
+        <v>6763962</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,60 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127293774</v>
+        <v>127293337</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437187</v>
+        <v>437130</v>
       </c>
       <c r="R3" t="n">
-        <v>6763964</v>
+        <v>6763889</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127294146</v>
+        <v>127294422</v>
       </c>
       <c r="B4" t="n">
         <v>79018</v>
@@ -920,17 +930,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437131</v>
+        <v>437193</v>
       </c>
       <c r="R4" t="n">
-        <v>6764010</v>
+        <v>6764064</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +994,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294422</v>
+        <v>127295759</v>
       </c>
       <c r="B5" t="n">
         <v>79018</v>
@@ -1027,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437193</v>
+        <v>437218</v>
       </c>
       <c r="R5" t="n">
-        <v>6764064</v>
+        <v>6763878</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1101,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127291489</v>
+        <v>127293774</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1138,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437044</v>
+        <v>437187</v>
       </c>
       <c r="R6" t="n">
-        <v>6763790</v>
+        <v>6763964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127290437</v>
+        <v>127295923</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437157</v>
+        <v>437244</v>
       </c>
       <c r="R7" t="n">
-        <v>6763806</v>
+        <v>6763901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295045</v>
+        <v>127294146</v>
       </c>
       <c r="B8" t="n">
         <v>79018</v>
@@ -1348,17 +1358,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437295</v>
+        <v>437131</v>
       </c>
       <c r="R8" t="n">
-        <v>6763947</v>
+        <v>6764010</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295923</v>
+        <v>127291489</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437244</v>
+        <v>437044</v>
       </c>
       <c r="R9" t="n">
-        <v>6763901</v>
+        <v>6763790</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,53 +1541,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295019</v>
+        <v>127290437</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437299</v>
+        <v>437157</v>
       </c>
       <c r="R10" t="n">
-        <v>6763962</v>
+        <v>6763806</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,62 +1636,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127293337</v>
+        <v>127295045</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437130</v>
+        <v>437295</v>
       </c>
       <c r="R11" t="n">
-        <v>6763889</v>
+        <v>6763947</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294354</v>
+        <v>127291056</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437188</v>
+        <v>437040</v>
       </c>
       <c r="R12" t="n">
-        <v>6764029</v>
+        <v>6763751</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294721</v>
+        <v>127294354</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437204</v>
+        <v>437188</v>
       </c>
       <c r="R13" t="n">
-        <v>6764046</v>
+        <v>6764029</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127291056</v>
+        <v>127294721</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437040</v>
+        <v>437204</v>
       </c>
       <c r="R14" t="n">
-        <v>6763751</v>
+        <v>6764046</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,12 +2064,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127293099</v>
+        <v>127291525</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437109</v>
+        <v>437044</v>
       </c>
       <c r="R19" t="n">
-        <v>6763908</v>
+        <v>6763790</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127291525</v>
+        <v>127293263</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437044</v>
+        <v>437138</v>
       </c>
       <c r="R20" t="n">
-        <v>6763790</v>
+        <v>6763887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127294351</v>
+        <v>127293099</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437151</v>
+        <v>437109</v>
       </c>
       <c r="R21" t="n">
-        <v>6764039</v>
+        <v>6763908</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295941</v>
+        <v>127294351</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2856,17 +2856,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437223</v>
+        <v>437151</v>
       </c>
       <c r="R22" t="n">
-        <v>6763922</v>
+        <v>6764039</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,22 +2920,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127293263</v>
+        <v>127295941</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,37 +2943,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437138</v>
+        <v>437223</v>
       </c>
       <c r="R23" t="n">
-        <v>6763887</v>
+        <v>6763922</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,19 +3027,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293735</v>
+        <v>127294346</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -3070,17 +3070,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437156</v>
+        <v>437187</v>
       </c>
       <c r="R24" t="n">
-        <v>6763978</v>
+        <v>6764029</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,19 +3134,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295078</v>
+        <v>127293735</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3177,17 +3177,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437293</v>
+        <v>437156</v>
       </c>
       <c r="R25" t="n">
-        <v>6763940</v>
+        <v>6763978</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,19 +3241,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294346</v>
+        <v>127295078</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437187</v>
+        <v>437293</v>
       </c>
       <c r="R26" t="n">
-        <v>6764029</v>
+        <v>6763940</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3910,53 +3910,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294136</v>
+        <v>127293914</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437182</v>
+        <v>437190</v>
       </c>
       <c r="R32" t="n">
-        <v>6763976</v>
+        <v>6763999</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4010,19 +4005,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293914</v>
+        <v>127293696</v>
       </c>
       <c r="B33" t="n">
         <v>79018</v>
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437190</v>
+        <v>437156</v>
       </c>
       <c r="R33" t="n">
-        <v>6763999</v>
+        <v>6763982</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4343,7 +4338,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293696</v>
+        <v>127293981</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4378,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437156</v>
+        <v>437177</v>
       </c>
       <c r="R36" t="n">
-        <v>6763982</v>
+        <v>6764017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,48 +4445,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127293981</v>
+        <v>127294136</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437177</v>
+        <v>437182</v>
       </c>
       <c r="R37" t="n">
-        <v>6764017</v>
+        <v>6763976</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,60 +4545,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127293212</v>
+        <v>127292954</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437120</v>
+        <v>437050</v>
       </c>
       <c r="R38" t="n">
-        <v>6763919</v>
+        <v>6763860</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4652,60 +4652,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294037</v>
+        <v>127292669</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437188</v>
+        <v>437023</v>
       </c>
       <c r="R39" t="n">
-        <v>6763952</v>
+        <v>6763818</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,22 +4759,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295245</v>
+        <v>127291424</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437308</v>
+        <v>437058</v>
       </c>
       <c r="R40" t="n">
-        <v>6763966</v>
+        <v>6763796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127292954</v>
+        <v>127295245</v>
       </c>
       <c r="B41" t="n">
         <v>79018</v>
@@ -4909,17 +4909,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437050</v>
+        <v>437308</v>
       </c>
       <c r="R41" t="n">
-        <v>6763860</v>
+        <v>6763966</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,22 +4973,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127292669</v>
+        <v>127290586</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4996,37 +4996,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437023</v>
+        <v>437065</v>
       </c>
       <c r="R42" t="n">
-        <v>6763818</v>
+        <v>6763754</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,44 +5080,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127290586</v>
+        <v>127294037</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437065</v>
+        <v>437188</v>
       </c>
       <c r="R43" t="n">
-        <v>6763754</v>
+        <v>6763952</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5199,32 +5199,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127291424</v>
+        <v>127293212</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437058</v>
+        <v>437120</v>
       </c>
       <c r="R44" t="n">
-        <v>6763796</v>
+        <v>6763919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127294741</v>
+        <v>127292980</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437209</v>
+        <v>437068</v>
       </c>
       <c r="R46" t="n">
-        <v>6764061</v>
+        <v>6763858</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292980</v>
+        <v>127295897</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,37 +5531,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437068</v>
+        <v>437244</v>
       </c>
       <c r="R47" t="n">
-        <v>6763858</v>
+        <v>6763890</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,12 +5615,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127291031</v>
+        <v>127290803</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,34 +5745,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437097</v>
+        <v>437091</v>
       </c>
       <c r="R49" t="n">
-        <v>6763850</v>
+        <v>6763822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295897</v>
+        <v>127294741</v>
       </c>
       <c r="B50" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,37 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437244</v>
+        <v>437209</v>
       </c>
       <c r="R50" t="n">
-        <v>6763890</v>
+        <v>6764061</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5911,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5921,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5936,22 +5941,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290803</v>
+        <v>127291031</v>
       </c>
       <c r="B51" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5959,39 +5964,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437091</v>
+        <v>437097</v>
       </c>
       <c r="R51" t="n">
-        <v>6763822</v>
+        <v>6763850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127293209</v>
+        <v>127290094</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437116</v>
+        <v>437239</v>
       </c>
       <c r="R54" t="n">
-        <v>6763949</v>
+        <v>6763818</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6355,6 +6355,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,10 +6386,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127290094</v>
+        <v>127291397</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6397,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6421,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437239</v>
+        <v>437058</v>
       </c>
       <c r="R55" t="n">
-        <v>6763818</v>
+        <v>6763796</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,11 +6467,6 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6600,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127291397</v>
+        <v>127293209</v>
       </c>
       <c r="B57" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437058</v>
+        <v>437116</v>
       </c>
       <c r="R57" t="n">
-        <v>6763796</v>
+        <v>6763949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6707,48 +6707,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127294772</v>
+        <v>127293858</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437255</v>
+        <v>437201</v>
       </c>
       <c r="R58" t="n">
-        <v>6764049</v>
+        <v>6763976</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,57 +6802,62 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294736</v>
+        <v>127290454</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437212</v>
+        <v>437078</v>
       </c>
       <c r="R59" t="n">
-        <v>6764065</v>
+        <v>6763737</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6884,7 +6889,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6899,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6921,10 +6926,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294985</v>
+        <v>127291537</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6932,37 +6937,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437293</v>
+        <v>437044</v>
       </c>
       <c r="R60" t="n">
-        <v>6763965</v>
+        <v>6763790</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6991,7 +6996,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7006,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7016,19 +7021,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294411</v>
+        <v>127294985</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -7063,10 +7068,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437202</v>
+        <v>437293</v>
       </c>
       <c r="R61" t="n">
-        <v>6764041</v>
+        <v>6763965</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7098,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7456,10 +7461,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127291537</v>
+        <v>127294772</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,37 +7472,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437044</v>
+        <v>437255</v>
       </c>
       <c r="R65" t="n">
-        <v>6763790</v>
+        <v>6764049</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7526,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7536,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7551,60 +7556,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127293858</v>
+        <v>127294736</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437201</v>
+        <v>437212</v>
       </c>
       <c r="R66" t="n">
-        <v>6763976</v>
+        <v>6764065</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7633,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7643,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7658,62 +7663,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127290454</v>
+        <v>127294411</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437078</v>
+        <v>437202</v>
       </c>
       <c r="R67" t="n">
-        <v>6763737</v>
+        <v>6764041</v>
       </c>
       <c r="S67" t="n">
         <v>9</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290959</v>
+        <v>127290751</v>
       </c>
       <c r="B68" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7793,37 +7793,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437097</v>
+        <v>437062</v>
       </c>
       <c r="R68" t="n">
-        <v>6763868</v>
+        <v>6763738</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,12 +7877,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7996,10 +7996,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127290751</v>
+        <v>127290959</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8007,37 +8007,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437062</v>
+        <v>437097</v>
       </c>
       <c r="R70" t="n">
-        <v>6763738</v>
+        <v>6763868</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8091,12 +8091,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8424,48 +8424,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127295799</v>
+        <v>127292676</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437234</v>
+        <v>437043</v>
       </c>
       <c r="R74" t="n">
-        <v>6763858</v>
+        <v>6763840</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8519,22 +8524,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127294842</v>
+        <v>127294334</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8547,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,10 +8571,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437280</v>
+        <v>437170</v>
       </c>
       <c r="R75" t="n">
-        <v>6764030</v>
+        <v>6764043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8638,10 +8643,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127294334</v>
+        <v>127295799</v>
       </c>
       <c r="B76" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8649,21 +8654,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8673,10 +8678,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437170</v>
+        <v>437234</v>
       </c>
       <c r="R76" t="n">
-        <v>6764043</v>
+        <v>6763858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8745,53 +8750,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R77" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,19 +8845,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293897</v>
+        <v>127294433</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8888,17 +8888,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
         <v>437180</v>
       </c>
       <c r="R78" t="n">
-        <v>6763986</v>
+        <v>6764047</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8952,22 +8952,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293677</v>
+        <v>127290717</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,34 +8975,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437148</v>
+        <v>437108</v>
       </c>
       <c r="R79" t="n">
-        <v>6764001</v>
+        <v>6763809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9071,32 +9076,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293789</v>
+        <v>127293090</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9106,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437218</v>
+        <v>437081</v>
       </c>
       <c r="R80" t="n">
-        <v>6763950</v>
+        <v>6763901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9178,7 +9183,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127294716</v>
+        <v>127293897</v>
       </c>
       <c r="B81" t="n">
         <v>79018</v>
@@ -9209,17 +9214,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437199</v>
+        <v>437180</v>
       </c>
       <c r="R81" t="n">
-        <v>6764063</v>
+        <v>6763986</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9248,7 +9253,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9258,7 +9263,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,19 +9278,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293504</v>
+        <v>127293677</v>
       </c>
       <c r="B82" t="n">
         <v>79018</v>
@@ -9320,10 +9325,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437136</v>
+        <v>437148</v>
       </c>
       <c r="R82" t="n">
-        <v>6763963</v>
+        <v>6764001</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9392,7 +9397,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294433</v>
+        <v>127293789</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -9423,17 +9428,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437180</v>
+        <v>437218</v>
       </c>
       <c r="R83" t="n">
-        <v>6764047</v>
+        <v>6763950</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9472,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,60 +9492,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127293090</v>
+        <v>127294716</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437081</v>
+        <v>437199</v>
       </c>
       <c r="R84" t="n">
-        <v>6763901</v>
+        <v>6764063</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9569,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9579,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9594,22 +9599,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127290717</v>
+        <v>127293504</v>
       </c>
       <c r="B85" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9617,39 +9622,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437108</v>
+        <v>437136</v>
       </c>
       <c r="R85" t="n">
-        <v>6763809</v>
+        <v>6763963</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9825,7 +9825,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127295596</v>
+        <v>127295863</v>
       </c>
       <c r="B87" t="n">
         <v>79018</v>
@@ -9856,17 +9856,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437169</v>
+        <v>437221</v>
       </c>
       <c r="R87" t="n">
-        <v>6763904</v>
+        <v>6763950</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9920,19 +9920,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127295863</v>
+        <v>127291960</v>
       </c>
       <c r="B88" t="n">
         <v>79018</v>
@@ -9963,17 +9963,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437221</v>
+        <v>437015</v>
       </c>
       <c r="R88" t="n">
-        <v>6763950</v>
+        <v>6763762</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,19 +10027,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127292924</v>
+        <v>127295035</v>
       </c>
       <c r="B89" t="n">
         <v>79018</v>
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437037</v>
+        <v>437297</v>
       </c>
       <c r="R89" t="n">
-        <v>6763860</v>
+        <v>6763951</v>
       </c>
       <c r="S89" t="n">
         <v>9</v>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10146,32 +10146,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127291960</v>
+        <v>127292822</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437015</v>
+        <v>436992</v>
       </c>
       <c r="R90" t="n">
-        <v>6763762</v>
+        <v>6763834</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10253,48 +10253,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127295035</v>
+        <v>127292999</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437297</v>
+        <v>437093</v>
       </c>
       <c r="R91" t="n">
-        <v>6763951</v>
+        <v>6763880</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,44 +10348,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127293022</v>
+        <v>127295269</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437081</v>
+        <v>437297</v>
       </c>
       <c r="R92" t="n">
-        <v>6763901</v>
+        <v>6763935</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10467,32 +10467,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127292822</v>
+        <v>127295596</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436992</v>
+        <v>437169</v>
       </c>
       <c r="R93" t="n">
-        <v>6763834</v>
+        <v>6763904</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,48 +10574,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127292999</v>
+        <v>127292924</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437093</v>
+        <v>437037</v>
       </c>
       <c r="R94" t="n">
-        <v>6763880</v>
+        <v>6763860</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,44 +10669,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127295269</v>
+        <v>127293022</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437297</v>
+        <v>437081</v>
       </c>
       <c r="R95" t="n">
-        <v>6763935</v>
+        <v>6763901</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293586</v>
+        <v>127293348</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,37 +10799,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437163</v>
+        <v>437154</v>
       </c>
       <c r="R96" t="n">
-        <v>6763902</v>
+        <v>6763925</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10858,7 +10863,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10868,7 +10873,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10883,12 +10888,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11109,7 +11114,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293029</v>
+        <v>127293586</v>
       </c>
       <c r="B99" t="n">
         <v>79018</v>
@@ -11140,17 +11145,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437074</v>
+        <v>437163</v>
       </c>
       <c r="R99" t="n">
-        <v>6763890</v>
+        <v>6763902</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11179,7 +11184,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11189,7 +11194,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11204,22 +11209,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127290978</v>
+        <v>127293953</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11227,37 +11232,46 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437098</v>
+        <v>437190</v>
       </c>
       <c r="R100" t="n">
-        <v>6763850</v>
+        <v>6763937</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11286,7 +11300,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11296,7 +11310,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11311,22 +11325,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293953</v>
+        <v>127293029</v>
       </c>
       <c r="B101" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11334,46 +11348,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437190</v>
+        <v>437074</v>
       </c>
       <c r="R101" t="n">
-        <v>6763937</v>
+        <v>6763890</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11402,7 +11407,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11412,7 +11417,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11427,22 +11432,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293348</v>
+        <v>127290978</v>
       </c>
       <c r="B102" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11450,39 +11455,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437154</v>
+        <v>437098</v>
       </c>
       <c r="R102" t="n">
-        <v>6763925</v>
+        <v>6763850</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12096,48 +12096,53 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127291177</v>
+        <v>127292727</v>
       </c>
       <c r="B108" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437081</v>
+        <v>437043</v>
       </c>
       <c r="R108" t="n">
-        <v>6763837</v>
+        <v>6763856</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12166,7 +12171,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12176,7 +12181,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12191,19 +12196,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127292727</v>
+        <v>127290265</v>
       </c>
       <c r="B109" t="n">
         <v>8450</v>
@@ -12232,24 +12237,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437043</v>
+        <v>437187</v>
       </c>
       <c r="R109" t="n">
-        <v>6763856</v>
+        <v>6763801</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12303,19 +12303,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127290265</v>
+        <v>127294388</v>
       </c>
       <c r="B110" t="n">
         <v>8450</v>
@@ -12346,17 +12346,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437187</v>
+        <v>437183</v>
       </c>
       <c r="R110" t="n">
-        <v>6763801</v>
+        <v>6764033</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12410,60 +12410,60 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127294388</v>
+        <v>127291177</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>79636</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437183</v>
+        <v>437081</v>
       </c>
       <c r="R111" t="n">
-        <v>6764033</v>
+        <v>6763837</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12517,12 +12517,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12641,48 +12641,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293262</v>
+        <v>127293766</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437131</v>
+        <v>437187</v>
       </c>
       <c r="R113" t="n">
-        <v>6763892</v>
+        <v>6763964</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,19 +12736,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127290747</v>
+        <v>127293262</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437064</v>
+        <v>437131</v>
       </c>
       <c r="R114" t="n">
-        <v>6763744</v>
+        <v>6763892</v>
       </c>
       <c r="S114" t="n">
         <v>9</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12855,7 +12855,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127294788</v>
+        <v>127290747</v>
       </c>
       <c r="B115" t="n">
         <v>79018</v>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437274</v>
+        <v>437064</v>
       </c>
       <c r="R115" t="n">
-        <v>6764023</v>
+        <v>6763744</v>
       </c>
       <c r="S115" t="n">
         <v>9</v>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12962,10 +12962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127291635</v>
+        <v>127293240</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,21 +12973,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12997,10 +12997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437032</v>
+        <v>437122</v>
       </c>
       <c r="R116" t="n">
-        <v>6763776</v>
+        <v>6763905</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13069,10 +13069,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127293240</v>
+        <v>127294788</v>
       </c>
       <c r="B117" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13080,37 +13080,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437122</v>
+        <v>437274</v>
       </c>
       <c r="R117" t="n">
-        <v>6763905</v>
+        <v>6764023</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,44 +13164,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127293766</v>
+        <v>127291635</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437187</v>
+        <v>437032</v>
       </c>
       <c r="R118" t="n">
-        <v>6763964</v>
+        <v>6763776</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13604,48 +13604,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290203</v>
+        <v>127290001</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57821</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437188</v>
+        <v>437239</v>
       </c>
       <c r="R122" t="n">
-        <v>6763793</v>
+        <v>6763818</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13685,11 +13690,6 @@
       <c r="AB122" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13716,7 +13716,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290773</v>
+        <v>127290203</v>
       </c>
       <c r="B123" t="n">
         <v>8450</v>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437081</v>
+        <v>437188</v>
       </c>
       <c r="R123" t="n">
-        <v>6763812</v>
+        <v>6763793</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,6 +13797,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13823,53 +13828,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290001</v>
+        <v>127290773</v>
       </c>
       <c r="B124" t="n">
-        <v>57821</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437239</v>
+        <v>437081</v>
       </c>
       <c r="R124" t="n">
-        <v>6763818</v>
+        <v>6763812</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13935,53 +13935,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127293007</v>
+        <v>127295889</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437076</v>
+        <v>437244</v>
       </c>
       <c r="R125" t="n">
-        <v>6763849</v>
+        <v>6763890</v>
       </c>
       <c r="S125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14020,12 +14020,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Två torrtallar</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14040,57 +14035,62 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127290736</v>
+        <v>127292816</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>437102</v>
+        <v>436992</v>
       </c>
       <c r="R126" t="n">
-        <v>6763801</v>
+        <v>6763834</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127292627</v>
+        <v>127293007</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -14199,10 +14199,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>437059</v>
+        <v>437076</v>
       </c>
       <c r="R127" t="n">
-        <v>6763861</v>
+        <v>6763849</v>
       </c>
       <c r="S127" t="n">
         <v>9</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14244,7 +14244,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Två torrtallar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14271,50 +14276,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127295889</v>
+        <v>127290736</v>
       </c>
       <c r="B128" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437244</v>
+        <v>437102</v>
       </c>
       <c r="R128" t="n">
-        <v>6763890</v>
+        <v>6763801</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14383,53 +14383,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127292816</v>
+        <v>127292627</v>
       </c>
       <c r="B129" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436992</v>
+        <v>437059</v>
       </c>
       <c r="R129" t="n">
-        <v>6763834</v>
+        <v>6763861</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14483,44 +14483,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127295386</v>
+        <v>127292761</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437233</v>
+        <v>436992</v>
       </c>
       <c r="R130" t="n">
-        <v>6763867</v>
+        <v>6763834</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14602,48 +14602,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127294021</v>
+        <v>127294311</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437191</v>
+        <v>437170</v>
       </c>
       <c r="R131" t="n">
-        <v>6763952</v>
+        <v>6764043</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14682,7 +14682,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14697,60 +14702,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127295217</v>
+        <v>127293305</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437312</v>
+        <v>437137</v>
       </c>
       <c r="R132" t="n">
-        <v>6763984</v>
+        <v>6763885</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14779,7 +14784,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14789,7 +14794,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14804,19 +14809,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127293270</v>
+        <v>127295386</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -14847,17 +14852,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437124</v>
+        <v>437233</v>
       </c>
       <c r="R133" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14886,7 +14891,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14896,7 +14901,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14911,44 +14916,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127293305</v>
+        <v>127294021</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14958,10 +14963,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437137</v>
+        <v>437191</v>
       </c>
       <c r="R134" t="n">
-        <v>6763885</v>
+        <v>6763952</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14993,7 +14998,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15003,7 +15008,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15030,32 +15035,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127292761</v>
+        <v>127295217</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15065,10 +15070,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436992</v>
+        <v>437312</v>
       </c>
       <c r="R135" t="n">
-        <v>6763834</v>
+        <v>6763984</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15137,48 +15142,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127294311</v>
+        <v>127293270</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437170</v>
+        <v>437124</v>
       </c>
       <c r="R136" t="n">
-        <v>6764043</v>
+        <v>6763885</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15207,7 +15212,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15217,12 +15222,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127290331</v>
+        <v>127293263</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437173</v>
+        <v>437138</v>
       </c>
       <c r="R17" t="n">
-        <v>6763816</v>
+        <v>6763887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,32 +2397,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295240</v>
+        <v>127293099</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437308</v>
+        <v>437109</v>
       </c>
       <c r="R18" t="n">
-        <v>6763966</v>
+        <v>6763908</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127291525</v>
+        <v>127294351</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437044</v>
+        <v>437151</v>
       </c>
       <c r="R19" t="n">
-        <v>6763790</v>
+        <v>6764039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127293263</v>
+        <v>127295941</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437138</v>
+        <v>437223</v>
       </c>
       <c r="R20" t="n">
-        <v>6763887</v>
+        <v>6763922</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127293099</v>
+        <v>127291525</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437109</v>
+        <v>437044</v>
       </c>
       <c r="R21" t="n">
-        <v>6763908</v>
+        <v>6763790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127294351</v>
+        <v>127290331</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437151</v>
+        <v>437173</v>
       </c>
       <c r="R22" t="n">
-        <v>6764039</v>
+        <v>6763816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,48 +2932,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295941</v>
+        <v>127295240</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437223</v>
+        <v>437308</v>
       </c>
       <c r="R23" t="n">
-        <v>6763922</v>
+        <v>6763966</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,12 +3027,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4124,48 +4124,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293203</v>
+        <v>127294136</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437116</v>
+        <v>437182</v>
       </c>
       <c r="R34" t="n">
-        <v>6763949</v>
+        <v>6763976</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,19 +4224,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295057</v>
+        <v>127293203</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -4262,17 +4267,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437295</v>
+        <v>437116</v>
       </c>
       <c r="R35" t="n">
-        <v>6763942</v>
+        <v>6763949</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4301,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,19 +4331,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293981</v>
+        <v>127295057</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4369,17 +4374,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437177</v>
+        <v>437295</v>
       </c>
       <c r="R36" t="n">
-        <v>6764017</v>
+        <v>6763942</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4418,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,65 +4438,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294136</v>
+        <v>127293981</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437182</v>
+        <v>437177</v>
       </c>
       <c r="R37" t="n">
-        <v>6763976</v>
+        <v>6764017</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,12 +4545,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7782,48 +7782,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290751</v>
+        <v>127290713</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437062</v>
+        <v>437108</v>
       </c>
       <c r="R68" t="n">
-        <v>6763738</v>
+        <v>6763809</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,44 +7877,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127290826</v>
+        <v>127292742</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437081</v>
+        <v>437089</v>
       </c>
       <c r="R69" t="n">
-        <v>6763837</v>
+        <v>6763838</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7996,32 +7996,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B70" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R70" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,48 +8103,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290713</v>
+        <v>127290751</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437108</v>
+        <v>437062</v>
       </c>
       <c r="R71" t="n">
-        <v>6763809</v>
+        <v>6763738</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8198,44 +8198,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127292742</v>
+        <v>127290826</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437089</v>
+        <v>437081</v>
       </c>
       <c r="R72" t="n">
-        <v>6763838</v>
+        <v>6763837</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8317,32 +8317,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127294714</v>
+        <v>127290959</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437204</v>
+        <v>437097</v>
       </c>
       <c r="R73" t="n">
-        <v>6764046</v>
+        <v>6763868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,53 +8424,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127292676</v>
+        <v>127294334</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437043</v>
+        <v>437170</v>
       </c>
       <c r="R74" t="n">
-        <v>6763840</v>
+        <v>6764043</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8524,22 +8519,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127294334</v>
+        <v>127295799</v>
       </c>
       <c r="B75" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8547,21 +8542,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437170</v>
+        <v>437234</v>
       </c>
       <c r="R75" t="n">
-        <v>6764043</v>
+        <v>6763858</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8643,7 +8638,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127295799</v>
+        <v>127294842</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8678,10 +8673,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437234</v>
+        <v>437280</v>
       </c>
       <c r="R76" t="n">
-        <v>6763858</v>
+        <v>6764030</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8750,48 +8745,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R77" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,12 +8845,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127292822</v>
+        <v>127295596</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436992</v>
+        <v>437169</v>
       </c>
       <c r="R90" t="n">
-        <v>6763834</v>
+        <v>6763904</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10253,48 +10253,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127292999</v>
+        <v>127292924</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437093</v>
+        <v>437037</v>
       </c>
       <c r="R91" t="n">
-        <v>6763880</v>
+        <v>6763860</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,44 +10348,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127295269</v>
+        <v>127293022</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437297</v>
+        <v>437081</v>
       </c>
       <c r="R92" t="n">
-        <v>6763935</v>
+        <v>6763901</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10467,32 +10467,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127295596</v>
+        <v>127292822</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437169</v>
+        <v>436992</v>
       </c>
       <c r="R93" t="n">
-        <v>6763904</v>
+        <v>6763834</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,48 +10574,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127292924</v>
+        <v>127292999</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437037</v>
+        <v>437093</v>
       </c>
       <c r="R94" t="n">
-        <v>6763860</v>
+        <v>6763880</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,44 +10669,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127293022</v>
+        <v>127295269</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437081</v>
+        <v>437297</v>
       </c>
       <c r="R95" t="n">
-        <v>6763901</v>
+        <v>6763935</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10788,27 +10788,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293348</v>
+        <v>127295309</v>
       </c>
       <c r="B96" t="n">
-        <v>57658</v>
+        <v>58031</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10819,7 +10819,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10828,13 +10828,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437154</v>
+        <v>437289</v>
       </c>
       <c r="R96" t="n">
-        <v>6763925</v>
+        <v>6763874</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11551,27 +11551,27 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127295309</v>
+        <v>127293348</v>
       </c>
       <c r="B103" t="n">
-        <v>58031</v>
+        <v>57658</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11582,7 +11582,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437289</v>
+        <v>437154</v>
       </c>
       <c r="R103" t="n">
-        <v>6763874</v>
+        <v>6763925</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12641,48 +12641,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293766</v>
+        <v>127293262</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437187</v>
+        <v>437131</v>
       </c>
       <c r="R113" t="n">
-        <v>6763964</v>
+        <v>6763892</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,19 +12736,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293262</v>
+        <v>127290747</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437131</v>
+        <v>437064</v>
       </c>
       <c r="R114" t="n">
-        <v>6763892</v>
+        <v>6763744</v>
       </c>
       <c r="S114" t="n">
         <v>9</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12855,10 +12855,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127290747</v>
+        <v>127293240</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437064</v>
+        <v>437122</v>
       </c>
       <c r="R115" t="n">
-        <v>6763744</v>
+        <v>6763905</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127293240</v>
+        <v>127294788</v>
       </c>
       <c r="B116" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437122</v>
+        <v>437274</v>
       </c>
       <c r="R116" t="n">
-        <v>6763905</v>
+        <v>6764023</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,19 +13057,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127294788</v>
+        <v>127291635</v>
       </c>
       <c r="B117" t="n">
         <v>79018</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437274</v>
+        <v>437032</v>
       </c>
       <c r="R117" t="n">
-        <v>6764023</v>
+        <v>6763776</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,44 +13164,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127291635</v>
+        <v>127293766</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437032</v>
+        <v>437187</v>
       </c>
       <c r="R118" t="n">
-        <v>6763776</v>
+        <v>6763964</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14495,7 +14495,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127292761</v>
+        <v>127293305</v>
       </c>
       <c r="B130" t="n">
         <v>79018</v>
@@ -14526,17 +14526,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436992</v>
+        <v>437137</v>
       </c>
       <c r="R130" t="n">
-        <v>6763834</v>
+        <v>6763885</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,44 +14590,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127294311</v>
+        <v>127295386</v>
       </c>
       <c r="B131" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437170</v>
+        <v>437233</v>
       </c>
       <c r="R131" t="n">
-        <v>6764043</v>
+        <v>6763867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14683,11 +14683,6 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14714,32 +14709,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127293305</v>
+        <v>127294021</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14749,10 +14744,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437137</v>
+        <v>437191</v>
       </c>
       <c r="R132" t="n">
-        <v>6763885</v>
+        <v>6763952</v>
       </c>
       <c r="S132" t="n">
         <v>9</v>
@@ -14784,7 +14779,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14794,7 +14789,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14821,7 +14816,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295386</v>
+        <v>127295217</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -14856,10 +14851,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437233</v>
+        <v>437312</v>
       </c>
       <c r="R133" t="n">
-        <v>6763867</v>
+        <v>6763984</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14928,7 +14923,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127294021</v>
+        <v>127293270</v>
       </c>
       <c r="B134" t="n">
         <v>8450</v>
@@ -14963,10 +14958,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437191</v>
+        <v>437124</v>
       </c>
       <c r="R134" t="n">
-        <v>6763952</v>
+        <v>6763885</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14998,7 +14993,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15008,7 +15003,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15035,32 +15030,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127295217</v>
+        <v>127292761</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15070,10 +15065,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437312</v>
+        <v>436992</v>
       </c>
       <c r="R135" t="n">
-        <v>6763984</v>
+        <v>6763834</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15142,48 +15137,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127293270</v>
+        <v>127294311</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437124</v>
+        <v>437170</v>
       </c>
       <c r="R136" t="n">
-        <v>6763885</v>
+        <v>6764043</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15212,7 +15207,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15222,7 +15217,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4124,53 +4124,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294136</v>
+        <v>127293203</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437182</v>
+        <v>437116</v>
       </c>
       <c r="R34" t="n">
-        <v>6763976</v>
+        <v>6763949</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4199,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4224,19 +4219,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127293203</v>
+        <v>127295057</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -4267,17 +4262,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437116</v>
+        <v>437295</v>
       </c>
       <c r="R35" t="n">
-        <v>6763949</v>
+        <v>6763942</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4331,19 +4326,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295057</v>
+        <v>127293981</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4374,17 +4369,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437295</v>
+        <v>437177</v>
       </c>
       <c r="R36" t="n">
-        <v>6763942</v>
+        <v>6764017</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,60 +4433,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127293981</v>
+        <v>127294136</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437177</v>
+        <v>437182</v>
       </c>
       <c r="R37" t="n">
-        <v>6764017</v>
+        <v>6763976</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,12 +4545,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127294037</v>
+        <v>127293212</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5123,17 +5123,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437188</v>
+        <v>437120</v>
       </c>
       <c r="R43" t="n">
-        <v>6763952</v>
+        <v>6763919</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,19 +5187,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127293212</v>
+        <v>127294037</v>
       </c>
       <c r="B44" t="n">
         <v>8450</v>
@@ -5230,17 +5230,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437120</v>
+        <v>437188</v>
       </c>
       <c r="R44" t="n">
-        <v>6763919</v>
+        <v>6763952</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,12 +5294,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6707,48 +6707,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127293858</v>
+        <v>127294772</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437201</v>
+        <v>437255</v>
       </c>
       <c r="R58" t="n">
-        <v>6763976</v>
+        <v>6764049</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,62 +6802,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127290454</v>
+        <v>127294736</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437078</v>
+        <v>437212</v>
       </c>
       <c r="R59" t="n">
-        <v>6763737</v>
+        <v>6764065</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6889,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6899,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6926,10 +6921,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127291537</v>
+        <v>127294411</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6937,37 +6932,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437044</v>
+        <v>437202</v>
       </c>
       <c r="R60" t="n">
-        <v>6763790</v>
+        <v>6764041</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6996,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7006,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,60 +7016,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294985</v>
+        <v>127293858</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437293</v>
+        <v>437201</v>
       </c>
       <c r="R61" t="n">
-        <v>6763965</v>
+        <v>6763976</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7103,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,60 +7123,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294416</v>
+        <v>127290454</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437158</v>
+        <v>437078</v>
       </c>
       <c r="R62" t="n">
-        <v>6764069</v>
+        <v>6763737</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,22 +7235,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127295806</v>
+        <v>127291537</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7258,37 +7258,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437212</v>
+        <v>437044</v>
       </c>
       <c r="R63" t="n">
-        <v>6763955</v>
+        <v>6763790</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,22 +7342,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127293072</v>
+        <v>127294985</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7365,37 +7365,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437081</v>
+        <v>437293</v>
       </c>
       <c r="R64" t="n">
-        <v>6763901</v>
+        <v>6763965</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,19 +7449,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127294772</v>
+        <v>127294416</v>
       </c>
       <c r="B65" t="n">
         <v>79018</v>
@@ -7492,17 +7492,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437255</v>
+        <v>437158</v>
       </c>
       <c r="R65" t="n">
-        <v>6764049</v>
+        <v>6764069</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7556,19 +7556,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127294736</v>
+        <v>127295806</v>
       </c>
       <c r="B66" t="n">
         <v>79018</v>
@@ -7606,7 +7606,7 @@
         <v>437212</v>
       </c>
       <c r="R66" t="n">
-        <v>6764065</v>
+        <v>6763955</v>
       </c>
       <c r="S66" t="n">
         <v>9</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,10 +7675,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127294411</v>
+        <v>127293072</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7686,37 +7686,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437202</v>
+        <v>437081</v>
       </c>
       <c r="R67" t="n">
-        <v>6764041</v>
+        <v>6763901</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,12 +7770,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127295596</v>
+        <v>127292822</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437169</v>
+        <v>436992</v>
       </c>
       <c r="R90" t="n">
-        <v>6763904</v>
+        <v>6763834</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10253,48 +10253,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127292924</v>
+        <v>127292999</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437037</v>
+        <v>437093</v>
       </c>
       <c r="R91" t="n">
-        <v>6763860</v>
+        <v>6763880</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,44 +10348,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127293022</v>
+        <v>127295269</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437081</v>
+        <v>437297</v>
       </c>
       <c r="R92" t="n">
-        <v>6763901</v>
+        <v>6763935</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10467,32 +10467,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127292822</v>
+        <v>127295596</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436992</v>
+        <v>437169</v>
       </c>
       <c r="R93" t="n">
-        <v>6763834</v>
+        <v>6763904</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,48 +10574,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127292999</v>
+        <v>127292924</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437093</v>
+        <v>437037</v>
       </c>
       <c r="R94" t="n">
-        <v>6763880</v>
+        <v>6763860</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,44 +10669,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127295269</v>
+        <v>127293022</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437297</v>
+        <v>437081</v>
       </c>
       <c r="R95" t="n">
-        <v>6763935</v>
+        <v>6763901</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10788,27 +10788,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127295309</v>
+        <v>127293348</v>
       </c>
       <c r="B96" t="n">
-        <v>58031</v>
+        <v>57658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10819,7 +10819,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10828,13 +10828,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437289</v>
+        <v>437154</v>
       </c>
       <c r="R96" t="n">
-        <v>6763874</v>
+        <v>6763925</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11551,27 +11551,27 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127293348</v>
+        <v>127295309</v>
       </c>
       <c r="B103" t="n">
-        <v>57658</v>
+        <v>58031</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11582,7 +11582,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437154</v>
+        <v>437289</v>
       </c>
       <c r="R103" t="n">
-        <v>6763925</v>
+        <v>6763874</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13390,32 +13390,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127293427</v>
+        <v>127290203</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13425,10 +13425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437147</v>
+        <v>437188</v>
       </c>
       <c r="R120" t="n">
-        <v>6763942</v>
+        <v>6763793</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13471,6 +13471,11 @@
       <c r="AB120" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13497,32 +13502,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127293635</v>
+        <v>127290773</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13532,10 +13537,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437130</v>
+        <v>437081</v>
       </c>
       <c r="R121" t="n">
-        <v>6763988</v>
+        <v>6763812</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13604,10 +13609,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290001</v>
+        <v>127293427</v>
       </c>
       <c r="B122" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13615,42 +13620,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437239</v>
+        <v>437147</v>
       </c>
       <c r="R122" t="n">
-        <v>6763818</v>
+        <v>6763942</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290203</v>
+        <v>127293635</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437188</v>
+        <v>437130</v>
       </c>
       <c r="R123" t="n">
-        <v>6763793</v>
+        <v>6763988</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,11 +13797,6 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13828,48 +13823,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290773</v>
+        <v>127290001</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57821</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437081</v>
+        <v>437239</v>
       </c>
       <c r="R124" t="n">
-        <v>6763812</v>
+        <v>6763818</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15247,6 +15247,126 @@
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127295725</v>
+      </c>
+      <c r="B137" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Fagerlok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>437162</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6763895</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ca 5 meter upp, 5 till 6 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295019</v>
+        <v>127290437</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437299</v>
+        <v>437157</v>
       </c>
       <c r="R2" t="n">
-        <v>6763962</v>
+        <v>6763806</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127293337</v>
+        <v>127295019</v>
       </c>
       <c r="B3" t="n">
         <v>8450</v>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437130</v>
+        <v>437299</v>
       </c>
       <c r="R3" t="n">
-        <v>6763889</v>
+        <v>6763962</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127294422</v>
+        <v>127293337</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437193</v>
+        <v>437130</v>
       </c>
       <c r="R4" t="n">
-        <v>6764064</v>
+        <v>6763889</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127291489</v>
+        <v>127294422</v>
       </c>
       <c r="B9" t="n">
         <v>79018</v>
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437044</v>
+        <v>437193</v>
       </c>
       <c r="R9" t="n">
-        <v>6763790</v>
+        <v>6764064</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,19 +1529,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127290437</v>
+        <v>127291489</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437157</v>
+        <v>437044</v>
       </c>
       <c r="R10" t="n">
-        <v>6763806</v>
+        <v>6763790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127291056</v>
+        <v>127294354</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437040</v>
+        <v>437188</v>
       </c>
       <c r="R12" t="n">
-        <v>6763751</v>
+        <v>6764029</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294354</v>
+        <v>127294721</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437188</v>
+        <v>437204</v>
       </c>
       <c r="R13" t="n">
-        <v>6764029</v>
+        <v>6764046</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294721</v>
+        <v>127291056</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437204</v>
+        <v>437040</v>
       </c>
       <c r="R14" t="n">
-        <v>6764046</v>
+        <v>6763751</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,12 +2064,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127293263</v>
+        <v>127291525</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437138</v>
+        <v>437044</v>
       </c>
       <c r="R17" t="n">
-        <v>6763887</v>
+        <v>6763790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293099</v>
+        <v>127293263</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437109</v>
+        <v>437138</v>
       </c>
       <c r="R18" t="n">
-        <v>6763908</v>
+        <v>6763887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127294351</v>
+        <v>127293099</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437151</v>
+        <v>437109</v>
       </c>
       <c r="R19" t="n">
-        <v>6764039</v>
+        <v>6763908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295941</v>
+        <v>127294351</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2642,17 +2642,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437223</v>
+        <v>437151</v>
       </c>
       <c r="R20" t="n">
-        <v>6763922</v>
+        <v>6764039</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127291525</v>
+        <v>127295941</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,37 +2729,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437044</v>
+        <v>437223</v>
       </c>
       <c r="R21" t="n">
-        <v>6763790</v>
+        <v>6763922</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127294346</v>
+        <v>127293820</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,37 +3050,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437187</v>
+        <v>437201</v>
       </c>
       <c r="R24" t="n">
-        <v>6764029</v>
+        <v>6763976</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3109,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,22 +3139,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127293735</v>
+        <v>127295384</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,34 +3162,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437156</v>
+        <v>437233</v>
       </c>
       <c r="R25" t="n">
-        <v>6763978</v>
+        <v>6763867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,48 +3263,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295078</v>
+        <v>127293161</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437293</v>
+        <v>437098</v>
       </c>
       <c r="R26" t="n">
-        <v>6763940</v>
+        <v>6763941</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3323,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,62 +3358,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293820</v>
+        <v>127292736</v>
       </c>
       <c r="B27" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437201</v>
+        <v>436991</v>
       </c>
       <c r="R27" t="n">
-        <v>6763976</v>
+        <v>6763816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,10 +3477,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295384</v>
+        <v>127293735</v>
       </c>
       <c r="B28" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3483,39 +3488,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437233</v>
+        <v>437156</v>
       </c>
       <c r="R28" t="n">
-        <v>6763867</v>
+        <v>6763978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,50 +3584,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127293241</v>
+        <v>127295078</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437135</v>
+        <v>437293</v>
       </c>
       <c r="R29" t="n">
-        <v>6763885</v>
+        <v>6763940</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3659,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,48 +3691,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293161</v>
+        <v>127294346</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437098</v>
+        <v>437187</v>
       </c>
       <c r="R30" t="n">
-        <v>6763941</v>
+        <v>6764029</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,19 +3786,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127292736</v>
+        <v>127293241</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3832,19 +3827,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436991</v>
+        <v>437135</v>
       </c>
       <c r="R31" t="n">
-        <v>6763816</v>
+        <v>6763885</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,12 +3898,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293696</v>
+        <v>127293203</v>
       </c>
       <c r="B33" t="n">
         <v>79018</v>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437156</v>
+        <v>437116</v>
       </c>
       <c r="R33" t="n">
-        <v>6763982</v>
+        <v>6763949</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293203</v>
+        <v>127295057</v>
       </c>
       <c r="B34" t="n">
         <v>79018</v>
@@ -4155,17 +4155,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437116</v>
+        <v>437295</v>
       </c>
       <c r="R34" t="n">
-        <v>6763949</v>
+        <v>6763942</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,19 +4219,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295057</v>
+        <v>127293696</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -4262,17 +4262,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437295</v>
+        <v>437156</v>
       </c>
       <c r="R35" t="n">
-        <v>6763942</v>
+        <v>6763982</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,12 +4326,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127292954</v>
+        <v>127295245</v>
       </c>
       <c r="B38" t="n">
         <v>79018</v>
@@ -4588,17 +4588,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437050</v>
+        <v>437308</v>
       </c>
       <c r="R38" t="n">
-        <v>6763860</v>
+        <v>6763966</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4652,22 +4652,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127292669</v>
+        <v>127292954</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437023</v>
+        <v>437050</v>
       </c>
       <c r="R39" t="n">
-        <v>6763818</v>
+        <v>6763860</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,22 +4759,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127291424</v>
+        <v>127290586</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,37 +4782,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437058</v>
+        <v>437065</v>
       </c>
       <c r="R40" t="n">
-        <v>6763796</v>
+        <v>6763754</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,22 +4866,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295245</v>
+        <v>127292669</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437308</v>
+        <v>437023</v>
       </c>
       <c r="R41" t="n">
-        <v>6763966</v>
+        <v>6763818</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127290586</v>
+        <v>127291424</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4996,37 +4996,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437065</v>
+        <v>437058</v>
       </c>
       <c r="R42" t="n">
-        <v>6763754</v>
+        <v>6763796</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,12 +5080,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127292980</v>
+        <v>127294741</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437068</v>
+        <v>437209</v>
       </c>
       <c r="R46" t="n">
-        <v>6763858</v>
+        <v>6764061</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295897</v>
+        <v>127292980</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,37 +5531,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437244</v>
+        <v>437068</v>
       </c>
       <c r="R47" t="n">
-        <v>6763890</v>
+        <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127293956</v>
+        <v>127295897</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437202</v>
+        <v>437244</v>
       </c>
       <c r="R48" t="n">
-        <v>6764007</v>
+        <v>6763890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127290803</v>
+        <v>127293956</v>
       </c>
       <c r="B49" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,39 +5745,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437091</v>
+        <v>437202</v>
       </c>
       <c r="R49" t="n">
-        <v>6763822</v>
+        <v>6764007</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127294741</v>
+        <v>127291031</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5877,17 +5872,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437209</v>
+        <v>437097</v>
       </c>
       <c r="R50" t="n">
-        <v>6764061</v>
+        <v>6763850</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5916,7 +5911,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5926,7 +5921,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5941,44 +5936,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127291031</v>
+        <v>127290540</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5988,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437097</v>
+        <v>437113</v>
       </c>
       <c r="R51" t="n">
-        <v>6763850</v>
+        <v>6763817</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127290540</v>
+        <v>127294782</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6091,17 +6086,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437113</v>
+        <v>437273</v>
       </c>
       <c r="R52" t="n">
-        <v>6763817</v>
+        <v>6764025</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6130,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6140,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6155,60 +6150,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127294782</v>
+        <v>127290803</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437273</v>
+        <v>437091</v>
       </c>
       <c r="R53" t="n">
-        <v>6764025</v>
+        <v>6763822</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,22 +6262,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127290094</v>
+        <v>127291397</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437239</v>
+        <v>437058</v>
       </c>
       <c r="R54" t="n">
-        <v>6763818</v>
+        <v>6763796</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6355,11 +6355,6 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6386,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127291397</v>
+        <v>127290094</v>
       </c>
       <c r="B55" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6397,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6421,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437058</v>
+        <v>437239</v>
       </c>
       <c r="R55" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6467,6 +6462,11 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,7 +6921,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294411</v>
+        <v>127294985</v>
       </c>
       <c r="B60" t="n">
         <v>79018</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437202</v>
+        <v>437293</v>
       </c>
       <c r="R60" t="n">
-        <v>6764041</v>
+        <v>6763965</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7028,48 +7028,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127293858</v>
+        <v>127294411</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437201</v>
+        <v>437202</v>
       </c>
       <c r="R61" t="n">
-        <v>6763976</v>
+        <v>6764041</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7123,65 +7123,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127290454</v>
+        <v>127294416</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437078</v>
+        <v>437158</v>
       </c>
       <c r="R62" t="n">
-        <v>6763737</v>
+        <v>6764069</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7205,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7215,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,22 +7230,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127291537</v>
+        <v>127295806</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7258,37 +7253,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437044</v>
+        <v>437212</v>
       </c>
       <c r="R63" t="n">
-        <v>6763790</v>
+        <v>6763955</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7317,7 +7312,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7327,7 +7322,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,22 +7337,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127294985</v>
+        <v>127293072</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7365,37 +7360,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437293</v>
+        <v>437081</v>
       </c>
       <c r="R64" t="n">
-        <v>6763965</v>
+        <v>6763901</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7424,7 +7419,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7429,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,44 +7444,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127294416</v>
+        <v>127293858</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7496,10 +7491,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437158</v>
+        <v>437201</v>
       </c>
       <c r="R65" t="n">
-        <v>6764069</v>
+        <v>6763976</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7568,45 +7563,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127295806</v>
+        <v>127290454</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437212</v>
+        <v>437078</v>
       </c>
       <c r="R66" t="n">
-        <v>6763955</v>
+        <v>6763737</v>
       </c>
       <c r="S66" t="n">
         <v>9</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,10 +7675,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127293072</v>
+        <v>127291537</v>
       </c>
       <c r="B67" t="n">
-        <v>91350</v>
+        <v>79607</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437081</v>
+        <v>437044</v>
       </c>
       <c r="R67" t="n">
-        <v>6763901</v>
+        <v>6763790</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290713</v>
+        <v>127290826</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R68" t="n">
-        <v>6763809</v>
+        <v>6763837</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,48 +7889,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127292742</v>
+        <v>127290751</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437089</v>
+        <v>437062</v>
       </c>
       <c r="R69" t="n">
-        <v>6763838</v>
+        <v>6763738</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,44 +7984,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127294714</v>
+        <v>127290959</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437204</v>
+        <v>437097</v>
       </c>
       <c r="R70" t="n">
-        <v>6764046</v>
+        <v>6763868</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,48 +8103,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290751</v>
+        <v>127290713</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437062</v>
+        <v>437108</v>
       </c>
       <c r="R71" t="n">
-        <v>6763738</v>
+        <v>6763809</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8198,44 +8198,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127290826</v>
+        <v>127292742</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437081</v>
+        <v>437089</v>
       </c>
       <c r="R72" t="n">
-        <v>6763837</v>
+        <v>6763838</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8317,32 +8317,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127290959</v>
+        <v>127294714</v>
       </c>
       <c r="B73" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437097</v>
+        <v>437204</v>
       </c>
       <c r="R73" t="n">
-        <v>6763868</v>
+        <v>6764046</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,48 +8424,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127294334</v>
+        <v>127292676</v>
       </c>
       <c r="B74" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437170</v>
+        <v>437043</v>
       </c>
       <c r="R74" t="n">
-        <v>6764043</v>
+        <v>6763840</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8519,22 +8524,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127295799</v>
+        <v>127294334</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8547,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,10 +8571,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437234</v>
+        <v>437170</v>
       </c>
       <c r="R75" t="n">
-        <v>6763858</v>
+        <v>6764043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8638,7 +8643,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127294842</v>
+        <v>127295799</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8673,10 +8678,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437280</v>
+        <v>437234</v>
       </c>
       <c r="R76" t="n">
-        <v>6764030</v>
+        <v>6763858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8745,53 +8750,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R77" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,19 +8845,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127294433</v>
+        <v>127293897</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8888,17 +8888,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
         <v>437180</v>
       </c>
       <c r="R78" t="n">
-        <v>6764047</v>
+        <v>6763986</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8952,22 +8952,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127290717</v>
+        <v>127293677</v>
       </c>
       <c r="B79" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,39 +8975,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437108</v>
+        <v>437148</v>
       </c>
       <c r="R79" t="n">
-        <v>6763809</v>
+        <v>6764001</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9076,32 +9071,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293090</v>
+        <v>127293789</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9111,10 +9106,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437081</v>
+        <v>437218</v>
       </c>
       <c r="R80" t="n">
-        <v>6763901</v>
+        <v>6763950</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9183,7 +9178,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127293897</v>
+        <v>127294716</v>
       </c>
       <c r="B81" t="n">
         <v>79018</v>
@@ -9214,17 +9209,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437180</v>
+        <v>437199</v>
       </c>
       <c r="R81" t="n">
-        <v>6763986</v>
+        <v>6764063</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9253,7 +9248,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9263,7 +9258,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9278,19 +9273,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293677</v>
+        <v>127293504</v>
       </c>
       <c r="B82" t="n">
         <v>79018</v>
@@ -9325,10 +9320,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437148</v>
+        <v>437136</v>
       </c>
       <c r="R82" t="n">
-        <v>6764001</v>
+        <v>6763963</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9397,7 +9392,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127293789</v>
+        <v>127294433</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -9428,17 +9423,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437218</v>
+        <v>437180</v>
       </c>
       <c r="R83" t="n">
-        <v>6763950</v>
+        <v>6764047</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9477,7 +9472,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,22 +9487,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127294716</v>
+        <v>127290717</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9515,37 +9510,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437199</v>
+        <v>437108</v>
       </c>
       <c r="R84" t="n">
-        <v>6764063</v>
+        <v>6763809</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,44 +9599,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127293504</v>
+        <v>127293090</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437136</v>
+        <v>437081</v>
       </c>
       <c r="R85" t="n">
-        <v>6763963</v>
+        <v>6763901</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9718,48 +9718,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127290757</v>
+        <v>127292822</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437058</v>
+        <v>436992</v>
       </c>
       <c r="R86" t="n">
-        <v>6763741</v>
+        <v>6763834</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,60 +9813,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127295863</v>
+        <v>127292999</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437221</v>
+        <v>437093</v>
       </c>
       <c r="R87" t="n">
-        <v>6763950</v>
+        <v>6763880</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9920,44 +9920,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127291960</v>
+        <v>127295269</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9967,10 +9967,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437015</v>
+        <v>437297</v>
       </c>
       <c r="R88" t="n">
-        <v>6763762</v>
+        <v>6763935</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127295035</v>
+        <v>127290757</v>
       </c>
       <c r="B89" t="n">
         <v>79018</v>
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437297</v>
+        <v>437058</v>
       </c>
       <c r="R89" t="n">
-        <v>6763951</v>
+        <v>6763741</v>
       </c>
       <c r="S89" t="n">
         <v>9</v>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10146,32 +10146,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127292822</v>
+        <v>127295596</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436992</v>
+        <v>437169</v>
       </c>
       <c r="R90" t="n">
-        <v>6763834</v>
+        <v>6763904</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10253,48 +10253,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127292999</v>
+        <v>127295863</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437093</v>
+        <v>437221</v>
       </c>
       <c r="R91" t="n">
-        <v>6763880</v>
+        <v>6763950</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,60 +10348,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127295269</v>
+        <v>127292924</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437297</v>
+        <v>437037</v>
       </c>
       <c r="R92" t="n">
-        <v>6763935</v>
+        <v>6763860</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10455,19 +10455,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127295596</v>
+        <v>127291960</v>
       </c>
       <c r="B93" t="n">
         <v>79018</v>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437169</v>
+        <v>437015</v>
       </c>
       <c r="R93" t="n">
-        <v>6763904</v>
+        <v>6763762</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127292924</v>
+        <v>127295035</v>
       </c>
       <c r="B94" t="n">
         <v>79018</v>
@@ -10609,10 +10609,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437037</v>
+        <v>437297</v>
       </c>
       <c r="R94" t="n">
-        <v>6763860</v>
+        <v>6763951</v>
       </c>
       <c r="S94" t="n">
         <v>9</v>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293348</v>
+        <v>127293586</v>
       </c>
       <c r="B96" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,42 +10799,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437154</v>
+        <v>437163</v>
       </c>
       <c r="R96" t="n">
-        <v>6763925</v>
+        <v>6763902</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10863,7 +10858,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10873,7 +10868,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10888,22 +10883,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293371</v>
+        <v>127293953</v>
       </c>
       <c r="B97" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10911,37 +10906,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437140</v>
+        <v>437190</v>
       </c>
       <c r="R97" t="n">
-        <v>6763931</v>
+        <v>6763937</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10970,7 +10974,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10980,7 +10984,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10995,19 +10999,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293249</v>
+        <v>127293371</v>
       </c>
       <c r="B98" t="n">
         <v>79018</v>
@@ -11038,17 +11042,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437134</v>
+        <v>437140</v>
       </c>
       <c r="R98" t="n">
-        <v>6763889</v>
+        <v>6763931</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11077,7 +11081,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11087,7 +11091,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11102,19 +11106,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293586</v>
+        <v>127293249</v>
       </c>
       <c r="B99" t="n">
         <v>79018</v>
@@ -11149,10 +11153,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437163</v>
+        <v>437134</v>
       </c>
       <c r="R99" t="n">
-        <v>6763902</v>
+        <v>6763889</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -11184,7 +11188,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11194,7 +11198,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11221,10 +11225,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293953</v>
+        <v>127293029</v>
       </c>
       <c r="B100" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11232,46 +11236,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437190</v>
+        <v>437074</v>
       </c>
       <c r="R100" t="n">
-        <v>6763937</v>
+        <v>6763890</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11300,7 +11295,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11310,7 +11305,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11325,19 +11320,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293029</v>
+        <v>127290978</v>
       </c>
       <c r="B101" t="n">
         <v>79018</v>
@@ -11372,10 +11367,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437074</v>
+        <v>437098</v>
       </c>
       <c r="R101" t="n">
-        <v>6763890</v>
+        <v>6763850</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11444,10 +11439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127290978</v>
+        <v>127293348</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11455,34 +11450,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437098</v>
+        <v>437154</v>
       </c>
       <c r="R102" t="n">
-        <v>6763850</v>
+        <v>6763925</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12422,10 +12422,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127291177</v>
+        <v>127293290</v>
       </c>
       <c r="B111" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12433,21 +12433,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437081</v>
+        <v>437138</v>
       </c>
       <c r="R111" t="n">
-        <v>6763837</v>
+        <v>6763901</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12503,6 +12503,11 @@
       <c r="AB111" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12529,10 +12534,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127293290</v>
+        <v>127291177</v>
       </c>
       <c r="B112" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12540,21 +12545,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12564,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437138</v>
+        <v>437081</v>
       </c>
       <c r="R112" t="n">
-        <v>6763901</v>
+        <v>6763837</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12610,11 +12615,6 @@
       <c r="AB112" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12641,48 +12641,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293262</v>
+        <v>127293766</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437131</v>
+        <v>437187</v>
       </c>
       <c r="R113" t="n">
-        <v>6763892</v>
+        <v>6763964</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,19 +12736,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127290747</v>
+        <v>127293262</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437064</v>
+        <v>437131</v>
       </c>
       <c r="R114" t="n">
-        <v>6763744</v>
+        <v>6763892</v>
       </c>
       <c r="S114" t="n">
         <v>9</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12855,10 +12855,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127293240</v>
+        <v>127290747</v>
       </c>
       <c r="B115" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437122</v>
+        <v>437064</v>
       </c>
       <c r="R115" t="n">
-        <v>6763905</v>
+        <v>6763744</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127294788</v>
+        <v>127293240</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437274</v>
+        <v>437122</v>
       </c>
       <c r="R116" t="n">
-        <v>6764023</v>
+        <v>6763905</v>
       </c>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,19 +13057,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127291635</v>
+        <v>127294788</v>
       </c>
       <c r="B117" t="n">
         <v>79018</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437032</v>
+        <v>437274</v>
       </c>
       <c r="R117" t="n">
-        <v>6763776</v>
+        <v>6764023</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,44 +13164,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127293766</v>
+        <v>127291635</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437187</v>
+        <v>437032</v>
       </c>
       <c r="R118" t="n">
-        <v>6763964</v>
+        <v>6763776</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13390,32 +13390,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127290203</v>
+        <v>127293427</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13425,10 +13425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437188</v>
+        <v>437147</v>
       </c>
       <c r="R120" t="n">
-        <v>6763793</v>
+        <v>6763942</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13471,11 +13471,6 @@
       <c r="AB120" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13502,32 +13497,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127290773</v>
+        <v>127293635</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13537,10 +13532,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437081</v>
+        <v>437130</v>
       </c>
       <c r="R121" t="n">
-        <v>6763812</v>
+        <v>6763988</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13609,10 +13604,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127293427</v>
+        <v>127290001</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13620,37 +13615,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437147</v>
+        <v>437239</v>
       </c>
       <c r="R122" t="n">
-        <v>6763942</v>
+        <v>6763818</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127293635</v>
+        <v>127290203</v>
       </c>
       <c r="B123" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437130</v>
+        <v>437188</v>
       </c>
       <c r="R123" t="n">
-        <v>6763988</v>
+        <v>6763793</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,6 +13797,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13823,53 +13828,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290001</v>
+        <v>127290773</v>
       </c>
       <c r="B124" t="n">
-        <v>57821</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437239</v>
+        <v>437081</v>
       </c>
       <c r="R124" t="n">
-        <v>6763818</v>
+        <v>6763812</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14602,32 +14602,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127295386</v>
+        <v>127292761</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437233</v>
+        <v>436992</v>
       </c>
       <c r="R131" t="n">
-        <v>6763867</v>
+        <v>6763834</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14709,48 +14709,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127294021</v>
+        <v>127294311</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437191</v>
+        <v>437170</v>
       </c>
       <c r="R132" t="n">
-        <v>6763952</v>
+        <v>6764043</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14789,7 +14789,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14804,19 +14809,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295217</v>
+        <v>127295386</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -14851,10 +14856,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437312</v>
+        <v>437233</v>
       </c>
       <c r="R133" t="n">
-        <v>6763984</v>
+        <v>6763867</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14923,7 +14928,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127293270</v>
+        <v>127294021</v>
       </c>
       <c r="B134" t="n">
         <v>8450</v>
@@ -14958,10 +14963,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437124</v>
+        <v>437191</v>
       </c>
       <c r="R134" t="n">
-        <v>6763885</v>
+        <v>6763952</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
@@ -14993,7 +14998,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15003,7 +15008,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15030,32 +15035,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127292761</v>
+        <v>127295217</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15065,10 +15070,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436992</v>
+        <v>437312</v>
       </c>
       <c r="R135" t="n">
-        <v>6763834</v>
+        <v>6763984</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15137,48 +15142,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127294311</v>
+        <v>127293270</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437170</v>
+        <v>437124</v>
       </c>
       <c r="R136" t="n">
-        <v>6764043</v>
+        <v>6763885</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15207,7 +15212,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15217,12 +15222,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -3039,53 +3039,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293820</v>
+        <v>127293241</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437201</v>
+        <v>437135</v>
       </c>
       <c r="R24" t="n">
-        <v>6763976</v>
+        <v>6763885</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,62 +3139,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295384</v>
+        <v>127293161</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437233</v>
+        <v>437098</v>
       </c>
       <c r="R25" t="n">
-        <v>6763867</v>
+        <v>6763941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3258,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127293161</v>
+        <v>127292736</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3298,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437098</v>
+        <v>436991</v>
       </c>
       <c r="R26" t="n">
-        <v>6763941</v>
+        <v>6763816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,32 +3365,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127292736</v>
+        <v>127293735</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436991</v>
+        <v>437156</v>
       </c>
       <c r="R27" t="n">
-        <v>6763816</v>
+        <v>6763978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3472,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127293735</v>
+        <v>127295078</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3508,17 +3503,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437156</v>
+        <v>437293</v>
       </c>
       <c r="R28" t="n">
-        <v>6763978</v>
+        <v>6763940</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3547,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,19 +3567,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295078</v>
+        <v>127294346</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3619,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437293</v>
+        <v>437187</v>
       </c>
       <c r="R29" t="n">
-        <v>6763940</v>
+        <v>6764029</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3654,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3664,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,10 +3686,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127294346</v>
+        <v>127293820</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,37 +3697,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437187</v>
+        <v>437201</v>
       </c>
       <c r="R30" t="n">
-        <v>6764029</v>
+        <v>6763976</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3786,65 +3786,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127293241</v>
+        <v>127295384</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437135</v>
+        <v>437233</v>
       </c>
       <c r="R31" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,12 +3898,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5306,32 +5306,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127292927</v>
+        <v>127290540</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437032</v>
+        <v>437113</v>
       </c>
       <c r="R45" t="n">
-        <v>6763858</v>
+        <v>6763817</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,32 +5413,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127294741</v>
+        <v>127294782</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437209</v>
+        <v>437273</v>
       </c>
       <c r="R46" t="n">
-        <v>6764061</v>
+        <v>6764025</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,7 +5520,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292980</v>
+        <v>127292927</v>
       </c>
       <c r="B47" t="n">
         <v>79018</v>
@@ -5551,17 +5551,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437068</v>
+        <v>437032</v>
       </c>
       <c r="R47" t="n">
         <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295897</v>
+        <v>127294741</v>
       </c>
       <c r="B48" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,37 +5638,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437244</v>
+        <v>437209</v>
       </c>
       <c r="R48" t="n">
-        <v>6763890</v>
+        <v>6764061</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127293956</v>
+        <v>127292980</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5765,17 +5765,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437202</v>
+        <v>437068</v>
       </c>
       <c r="R49" t="n">
-        <v>6764007</v>
+        <v>6763858</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5829,22 +5829,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127291031</v>
+        <v>127295897</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437097</v>
+        <v>437244</v>
       </c>
       <c r="R50" t="n">
-        <v>6763850</v>
+        <v>6763890</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,32 +5948,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290540</v>
+        <v>127293956</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437113</v>
+        <v>437202</v>
       </c>
       <c r="R51" t="n">
-        <v>6763817</v>
+        <v>6764007</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,48 +6055,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127294782</v>
+        <v>127291031</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437273</v>
+        <v>437097</v>
       </c>
       <c r="R52" t="n">
-        <v>6764025</v>
+        <v>6763850</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6150,12 +6150,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293586</v>
+        <v>127293348</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10799,37 +10799,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437163</v>
+        <v>437154</v>
       </c>
       <c r="R96" t="n">
-        <v>6763902</v>
+        <v>6763925</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10858,7 +10863,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10868,7 +10873,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10883,22 +10888,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293953</v>
+        <v>127293586</v>
       </c>
       <c r="B97" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10906,43 +10911,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437190</v>
+        <v>437163</v>
       </c>
       <c r="R97" t="n">
-        <v>6763937</v>
+        <v>6763902</v>
       </c>
       <c r="S97" t="n">
         <v>9</v>
@@ -10974,7 +10970,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10984,7 +10980,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11011,10 +11007,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293371</v>
+        <v>127293953</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11022,37 +11018,46 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437140</v>
+        <v>437190</v>
       </c>
       <c r="R98" t="n">
-        <v>6763931</v>
+        <v>6763937</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11081,7 +11086,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11091,7 +11096,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11106,19 +11111,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293249</v>
+        <v>127293371</v>
       </c>
       <c r="B99" t="n">
         <v>79018</v>
@@ -11149,17 +11154,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437134</v>
+        <v>437140</v>
       </c>
       <c r="R99" t="n">
-        <v>6763889</v>
+        <v>6763931</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11188,7 +11193,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11198,7 +11203,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11213,19 +11218,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293029</v>
+        <v>127293249</v>
       </c>
       <c r="B100" t="n">
         <v>79018</v>
@@ -11256,17 +11261,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437074</v>
+        <v>437134</v>
       </c>
       <c r="R100" t="n">
-        <v>6763890</v>
+        <v>6763889</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11295,7 +11300,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11305,7 +11310,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11320,19 +11325,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127290978</v>
+        <v>127293029</v>
       </c>
       <c r="B101" t="n">
         <v>79018</v>
@@ -11367,10 +11372,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437098</v>
+        <v>437074</v>
       </c>
       <c r="R101" t="n">
-        <v>6763850</v>
+        <v>6763890</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11439,10 +11444,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293348</v>
+        <v>127290978</v>
       </c>
       <c r="B102" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11450,39 +11455,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437154</v>
+        <v>437098</v>
       </c>
       <c r="R102" t="n">
-        <v>6763925</v>
+        <v>6763850</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12641,48 +12641,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293766</v>
+        <v>127293262</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437187</v>
+        <v>437131</v>
       </c>
       <c r="R113" t="n">
-        <v>6763964</v>
+        <v>6763892</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,19 +12736,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293262</v>
+        <v>127290747</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437131</v>
+        <v>437064</v>
       </c>
       <c r="R114" t="n">
-        <v>6763892</v>
+        <v>6763744</v>
       </c>
       <c r="S114" t="n">
         <v>9</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12855,10 +12855,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127290747</v>
+        <v>127293240</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437064</v>
+        <v>437122</v>
       </c>
       <c r="R115" t="n">
-        <v>6763744</v>
+        <v>6763905</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127293240</v>
+        <v>127294788</v>
       </c>
       <c r="B116" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437122</v>
+        <v>437274</v>
       </c>
       <c r="R116" t="n">
-        <v>6763905</v>
+        <v>6764023</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,19 +13057,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127294788</v>
+        <v>127291635</v>
       </c>
       <c r="B117" t="n">
         <v>79018</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437274</v>
+        <v>437032</v>
       </c>
       <c r="R117" t="n">
-        <v>6764023</v>
+        <v>6763776</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,44 +13164,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127291635</v>
+        <v>127293766</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13211,10 +13211,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437032</v>
+        <v>437187</v>
       </c>
       <c r="R118" t="n">
-        <v>6763776</v>
+        <v>6763964</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13283,48 +13283,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127291536</v>
+        <v>127290203</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436972</v>
+        <v>437188</v>
       </c>
       <c r="R119" t="n">
-        <v>6763733</v>
+        <v>6763793</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,7 +13363,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13378,44 +13383,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127293427</v>
+        <v>127290773</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13425,10 +13430,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437147</v>
+        <v>437081</v>
       </c>
       <c r="R120" t="n">
-        <v>6763942</v>
+        <v>6763812</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13497,7 +13502,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127293635</v>
+        <v>127291536</v>
       </c>
       <c r="B121" t="n">
         <v>79018</v>
@@ -13528,17 +13533,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437130</v>
+        <v>436972</v>
       </c>
       <c r="R121" t="n">
-        <v>6763988</v>
+        <v>6763733</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13567,7 +13572,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13577,7 +13582,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13592,22 +13597,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127290001</v>
+        <v>127293427</v>
       </c>
       <c r="B122" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13615,42 +13620,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437239</v>
+        <v>437147</v>
       </c>
       <c r="R122" t="n">
-        <v>6763818</v>
+        <v>6763942</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127290203</v>
+        <v>127293635</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437188</v>
+        <v>437130</v>
       </c>
       <c r="R123" t="n">
-        <v>6763793</v>
+        <v>6763988</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,11 +13797,6 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13828,48 +13823,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290773</v>
+        <v>127290001</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57821</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437081</v>
+        <v>437239</v>
       </c>
       <c r="R124" t="n">
-        <v>6763812</v>
+        <v>6763818</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13935,53 +13935,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127295889</v>
+        <v>127293007</v>
       </c>
       <c r="B125" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437244</v>
+        <v>437076</v>
       </c>
       <c r="R125" t="n">
-        <v>6763890</v>
+        <v>6763849</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14020,7 +14020,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Två torrtallar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14035,62 +14040,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127292816</v>
+        <v>127290736</v>
       </c>
       <c r="B126" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436992</v>
+        <v>437102</v>
       </c>
       <c r="R126" t="n">
-        <v>6763834</v>
+        <v>6763801</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127293007</v>
+        <v>127292627</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -14199,10 +14199,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>437076</v>
+        <v>437059</v>
       </c>
       <c r="R127" t="n">
-        <v>6763849</v>
+        <v>6763861</v>
       </c>
       <c r="S127" t="n">
         <v>9</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14244,12 +14244,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Två torrtallar</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14276,45 +14271,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127290736</v>
+        <v>127295889</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437102</v>
+        <v>437244</v>
       </c>
       <c r="R128" t="n">
-        <v>6763801</v>
+        <v>6763890</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14383,53 +14383,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127292627</v>
+        <v>127292816</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>437059</v>
+        <v>436992</v>
       </c>
       <c r="R129" t="n">
-        <v>6763861</v>
+        <v>6763834</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14483,12 +14483,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127290437</v>
+        <v>127293774</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437157</v>
+        <v>437187</v>
       </c>
       <c r="R2" t="n">
-        <v>6763806</v>
+        <v>6763964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295019</v>
+        <v>127294422</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437299</v>
+        <v>437193</v>
       </c>
       <c r="R3" t="n">
-        <v>6763962</v>
+        <v>6764064</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127293337</v>
+        <v>127294146</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437130</v>
+        <v>437131</v>
       </c>
       <c r="R4" t="n">
-        <v>6763889</v>
+        <v>6764010</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295759</v>
+        <v>127295045</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,17 +1027,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437218</v>
+        <v>437295</v>
       </c>
       <c r="R5" t="n">
-        <v>6763878</v>
+        <v>6763947</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127293774</v>
+        <v>127295759</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437187</v>
+        <v>437218</v>
       </c>
       <c r="R6" t="n">
-        <v>6763964</v>
+        <v>6763878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
         <v>127295923</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294146</v>
+        <v>127291489</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437131</v>
+        <v>437044</v>
       </c>
       <c r="R8" t="n">
-        <v>6764010</v>
+        <v>6763790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294422</v>
+        <v>127290437</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,17 +1455,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437193</v>
+        <v>437157</v>
       </c>
       <c r="R9" t="n">
-        <v>6764064</v>
+        <v>6763806</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,60 +1519,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291489</v>
+        <v>127295019</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437044</v>
+        <v>437299</v>
       </c>
       <c r="R10" t="n">
-        <v>6763790</v>
+        <v>6763962</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,57 +1631,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295045</v>
+        <v>127293337</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437295</v>
+        <v>437130</v>
       </c>
       <c r="R11" t="n">
-        <v>6763947</v>
+        <v>6763889</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1758,7 @@
         <v>127294354</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127294721</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127291056</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>127294041</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>127294738</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127291525</v>
+        <v>127293263</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437044</v>
+        <v>437138</v>
       </c>
       <c r="R17" t="n">
-        <v>6763790</v>
+        <v>6763887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293263</v>
+        <v>127293099</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437138</v>
+        <v>437109</v>
       </c>
       <c r="R18" t="n">
-        <v>6763887</v>
+        <v>6763908</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127293099</v>
+        <v>127294351</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437109</v>
+        <v>437151</v>
       </c>
       <c r="R19" t="n">
-        <v>6763908</v>
+        <v>6764039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127294351</v>
+        <v>127295941</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,17 +2642,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437151</v>
+        <v>437223</v>
       </c>
       <c r="R20" t="n">
-        <v>6764039</v>
+        <v>6763922</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,22 +2706,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295941</v>
+        <v>127291525</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,37 +2729,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437223</v>
+        <v>437044</v>
       </c>
       <c r="R21" t="n">
-        <v>6763922</v>
+        <v>6763790</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3039,53 +3039,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293241</v>
+        <v>127293735</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437135</v>
+        <v>437156</v>
       </c>
       <c r="R24" t="n">
-        <v>6763885</v>
+        <v>6763978</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,19 +3134,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127293161</v>
+        <v>127293241</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3180,19 +3175,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437098</v>
+        <v>437135</v>
       </c>
       <c r="R25" t="n">
-        <v>6763941</v>
+        <v>6763885</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,12 +3246,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3365,32 +3365,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293735</v>
+        <v>127293161</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437156</v>
+        <v>437098</v>
       </c>
       <c r="R27" t="n">
-        <v>6763978</v>
+        <v>6763941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,7 +3475,7 @@
         <v>127295078</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>127294346</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>127293820</v>
       </c>
       <c r="B30" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127295384</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,48 +3910,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127293914</v>
+        <v>127294136</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437190</v>
+        <v>437182</v>
       </c>
       <c r="R32" t="n">
-        <v>6763999</v>
+        <v>6763976</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,22 +4010,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293203</v>
+        <v>127293914</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437116</v>
+        <v>437190</v>
       </c>
       <c r="R33" t="n">
-        <v>6763949</v>
+        <v>6763999</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295057</v>
+        <v>127293203</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4155,17 +4160,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437295</v>
+        <v>437116</v>
       </c>
       <c r="R34" t="n">
-        <v>6763942</v>
+        <v>6763949</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,12 +4224,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4234,7 +4239,7 @@
         <v>127293696</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4346,7 @@
         <v>127293981</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4445,50 +4450,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294136</v>
+        <v>127295057</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437182</v>
+        <v>437295</v>
       </c>
       <c r="R37" t="n">
-        <v>6763976</v>
+        <v>6763942</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295245</v>
+        <v>127290586</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4588,17 +4588,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437308</v>
+        <v>437065</v>
       </c>
       <c r="R38" t="n">
-        <v>6763966</v>
+        <v>6763754</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4652,22 +4652,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127292954</v>
+        <v>127292669</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437050</v>
+        <v>437023</v>
       </c>
       <c r="R39" t="n">
-        <v>6763860</v>
+        <v>6763818</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,22 +4759,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127290586</v>
+        <v>127292954</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437065</v>
+        <v>437050</v>
       </c>
       <c r="R40" t="n">
-        <v>6763754</v>
+        <v>6763860</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4878,10 +4878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127292669</v>
+        <v>127295245</v>
       </c>
       <c r="B41" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437023</v>
+        <v>437308</v>
       </c>
       <c r="R41" t="n">
-        <v>6763818</v>
+        <v>6763966</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4988,7 +4988,7 @@
         <v>127291424</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127293212</v>
+        <v>127294037</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5123,17 +5123,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437120</v>
+        <v>437188</v>
       </c>
       <c r="R43" t="n">
-        <v>6763919</v>
+        <v>6763952</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,19 +5187,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127294037</v>
+        <v>127293212</v>
       </c>
       <c r="B44" t="n">
         <v>8450</v>
@@ -5230,17 +5230,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437188</v>
+        <v>437120</v>
       </c>
       <c r="R44" t="n">
-        <v>6763952</v>
+        <v>6763919</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,60 +5294,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127290540</v>
+        <v>127292980</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437113</v>
+        <v>437068</v>
       </c>
       <c r="R45" t="n">
-        <v>6763817</v>
+        <v>6763858</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5401,60 +5401,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127294782</v>
+        <v>127291031</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437273</v>
+        <v>437097</v>
       </c>
       <c r="R46" t="n">
-        <v>6764025</v>
+        <v>6763850</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5508,22 +5508,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292927</v>
+        <v>127290803</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,34 +5531,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437032</v>
+        <v>437091</v>
       </c>
       <c r="R47" t="n">
-        <v>6763858</v>
+        <v>6763822</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5627,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127294741</v>
+        <v>127292927</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5658,17 +5663,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437209</v>
+        <v>437032</v>
       </c>
       <c r="R48" t="n">
-        <v>6764061</v>
+        <v>6763858</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5697,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5707,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,22 +5727,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127292980</v>
+        <v>127294741</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,10 +5774,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437068</v>
+        <v>437209</v>
       </c>
       <c r="R49" t="n">
-        <v>6763858</v>
+        <v>6764061</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5804,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5814,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5844,7 +5849,7 @@
         <v>127295897</v>
       </c>
       <c r="B50" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5951,7 +5956,7 @@
         <v>127293956</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,32 +6060,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127291031</v>
+        <v>127290540</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6090,10 +6095,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437097</v>
+        <v>437113</v>
       </c>
       <c r="R52" t="n">
-        <v>6763850</v>
+        <v>6763817</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6162,53 +6167,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127290803</v>
+        <v>127294782</v>
       </c>
       <c r="B53" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437091</v>
+        <v>437273</v>
       </c>
       <c r="R53" t="n">
-        <v>6763822</v>
+        <v>6764025</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,44 +6262,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127291397</v>
+        <v>127293209</v>
       </c>
       <c r="B54" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437058</v>
+        <v>437116</v>
       </c>
       <c r="R54" t="n">
-        <v>6763796</v>
+        <v>6763949</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127290094</v>
+        <v>127291397</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437239</v>
+        <v>437058</v>
       </c>
       <c r="R55" t="n">
-        <v>6763818</v>
+        <v>6763796</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,11 +6462,6 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6493,10 +6488,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127290996</v>
+        <v>127290094</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6528,13 +6523,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437108</v>
+        <v>437239</v>
       </c>
       <c r="R56" t="n">
-        <v>6763849</v>
+        <v>6763818</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6574,6 +6569,11 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6600,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127293209</v>
+        <v>127290996</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437116</v>
+        <v>437108</v>
       </c>
       <c r="R57" t="n">
-        <v>6763949</v>
+        <v>6763849</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6710,7 +6710,7 @@
         <v>127294772</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>127294736</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294985</v>
+        <v>127294411</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437293</v>
+        <v>437202</v>
       </c>
       <c r="R60" t="n">
-        <v>6763965</v>
+        <v>6764041</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7028,10 +7028,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294411</v>
+        <v>127294985</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7063,10 +7063,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437202</v>
+        <v>437293</v>
       </c>
       <c r="R61" t="n">
-        <v>6764041</v>
+        <v>6763965</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7138,7 +7138,7 @@
         <v>127294416</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>127295806</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>127293072</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>127291537</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290826</v>
+        <v>127290751</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,17 +7813,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437081</v>
+        <v>437062</v>
       </c>
       <c r="R68" t="n">
-        <v>6763837</v>
+        <v>6763738</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,22 +7877,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127290751</v>
+        <v>127290826</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,17 +7920,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437062</v>
+        <v>437081</v>
       </c>
       <c r="R69" t="n">
-        <v>6763738</v>
+        <v>6763837</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,12 +7984,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7999,7 +7999,7 @@
         <v>127290959</v>
       </c>
       <c r="B70" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127290713</v>
+        <v>127292742</v>
       </c>
       <c r="B71" t="n">
         <v>8450</v>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437108</v>
+        <v>437089</v>
       </c>
       <c r="R71" t="n">
-        <v>6763809</v>
+        <v>6763838</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127292742</v>
+        <v>127290713</v>
       </c>
       <c r="B72" t="n">
         <v>8450</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437089</v>
+        <v>437108</v>
       </c>
       <c r="R72" t="n">
-        <v>6763838</v>
+        <v>6763809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8424,53 +8424,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R74" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8524,12 +8519,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8539,7 +8534,7 @@
         <v>127294334</v>
       </c>
       <c r="B75" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8646,7 +8641,7 @@
         <v>127295799</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8750,48 +8745,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R77" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293897</v>
+        <v>127293677</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437180</v>
+        <v>437148</v>
       </c>
       <c r="R78" t="n">
-        <v>6763986</v>
+        <v>6764001</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293677</v>
+        <v>127293789</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437148</v>
+        <v>437218</v>
       </c>
       <c r="R79" t="n">
-        <v>6764001</v>
+        <v>6763950</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293789</v>
+        <v>127294716</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9102,17 +9102,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437218</v>
+        <v>437199</v>
       </c>
       <c r="R80" t="n">
-        <v>6763950</v>
+        <v>6764063</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,22 +9166,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127294716</v>
+        <v>127293504</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9209,17 +9209,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437199</v>
+        <v>437136</v>
       </c>
       <c r="R81" t="n">
-        <v>6764063</v>
+        <v>6763963</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,22 +9273,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293504</v>
+        <v>127290717</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9296,34 +9296,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437136</v>
+        <v>437108</v>
       </c>
       <c r="R82" t="n">
-        <v>6763963</v>
+        <v>6763809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9392,48 +9397,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294433</v>
+        <v>127293090</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437180</v>
+        <v>437081</v>
       </c>
       <c r="R83" t="n">
-        <v>6764047</v>
+        <v>6763901</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9472,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,22 +9492,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127290717</v>
+        <v>127293897</v>
       </c>
       <c r="B84" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9510,39 +9515,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437108</v>
+        <v>437180</v>
       </c>
       <c r="R84" t="n">
-        <v>6763809</v>
+        <v>6763986</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9611,48 +9611,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127293090</v>
+        <v>127294433</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437081</v>
+        <v>437180</v>
       </c>
       <c r="R85" t="n">
-        <v>6763901</v>
+        <v>6764047</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,60 +9706,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127292822</v>
+        <v>127295035</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436992</v>
+        <v>437297</v>
       </c>
       <c r="R86" t="n">
-        <v>6763834</v>
+        <v>6763951</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,60 +9813,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127292999</v>
+        <v>127292924</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437093</v>
+        <v>437037</v>
       </c>
       <c r="R87" t="n">
-        <v>6763880</v>
+        <v>6763860</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9920,60 +9920,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127295269</v>
+        <v>127290757</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437297</v>
+        <v>437058</v>
       </c>
       <c r="R88" t="n">
-        <v>6763935</v>
+        <v>6763741</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,22 +10027,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127290757</v>
+        <v>127295596</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10070,17 +10070,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437058</v>
+        <v>437169</v>
       </c>
       <c r="R89" t="n">
-        <v>6763741</v>
+        <v>6763904</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10134,22 +10134,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127295596</v>
+        <v>127295863</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10177,17 +10177,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437169</v>
+        <v>437221</v>
       </c>
       <c r="R90" t="n">
-        <v>6763904</v>
+        <v>6763950</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10241,22 +10241,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127295863</v>
+        <v>127291960</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10284,17 +10284,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437221</v>
+        <v>437015</v>
       </c>
       <c r="R91" t="n">
-        <v>6763950</v>
+        <v>6763762</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,22 +10348,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127292924</v>
+        <v>127293022</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10391,17 +10391,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437037</v>
+        <v>437081</v>
       </c>
       <c r="R92" t="n">
-        <v>6763860</v>
+        <v>6763901</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10455,44 +10455,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127291960</v>
+        <v>127292822</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437015</v>
+        <v>436992</v>
       </c>
       <c r="R93" t="n">
-        <v>6763762</v>
+        <v>6763834</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,48 +10574,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127295035</v>
+        <v>127295269</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>437297</v>
       </c>
       <c r="R94" t="n">
-        <v>6763951</v>
+        <v>6763935</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,44 +10669,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127293022</v>
+        <v>127292999</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437081</v>
+        <v>437093</v>
       </c>
       <c r="R95" t="n">
-        <v>6763901</v>
+        <v>6763880</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10791,7 +10791,7 @@
         <v>127293348</v>
       </c>
       <c r="B96" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10900,10 +10900,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293586</v>
+        <v>127293249</v>
       </c>
       <c r="B97" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437163</v>
+        <v>437134</v>
       </c>
       <c r="R97" t="n">
-        <v>6763902</v>
+        <v>6763889</v>
       </c>
       <c r="S97" t="n">
         <v>9</v>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11007,10 +11007,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293953</v>
+        <v>127293586</v>
       </c>
       <c r="B98" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11018,43 +11018,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437190</v>
+        <v>437163</v>
       </c>
       <c r="R98" t="n">
-        <v>6763937</v>
+        <v>6763902</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -11086,7 +11077,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11096,7 +11087,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11123,10 +11114,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293371</v>
+        <v>127293953</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11134,37 +11125,46 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437140</v>
+        <v>437190</v>
       </c>
       <c r="R99" t="n">
-        <v>6763931</v>
+        <v>6763937</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11218,22 +11218,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293249</v>
+        <v>127293371</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11261,17 +11261,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437134</v>
+        <v>437140</v>
       </c>
       <c r="R100" t="n">
-        <v>6763889</v>
+        <v>6763931</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11325,12 +11325,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11340,7 +11340,7 @@
         <v>127293029</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>127290978</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>127295309</v>
       </c>
       <c r="B103" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>127294008</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>127292751</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12096,53 +12096,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127292727</v>
+        <v>127291177</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437043</v>
+        <v>437081</v>
       </c>
       <c r="R108" t="n">
-        <v>6763856</v>
+        <v>6763837</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12171,7 +12166,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12181,7 +12176,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12196,12 +12191,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12422,48 +12417,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127293290</v>
+        <v>127292727</v>
       </c>
       <c r="B111" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437138</v>
+        <v>437043</v>
       </c>
       <c r="R111" t="n">
-        <v>6763901</v>
+        <v>6763856</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12502,12 +12502,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12522,22 +12517,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127291177</v>
+        <v>127293290</v>
       </c>
       <c r="B112" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12545,21 +12540,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12569,10 +12564,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437081</v>
+        <v>437138</v>
       </c>
       <c r="R112" t="n">
-        <v>6763837</v>
+        <v>6763901</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12615,6 +12610,11 @@
       <c r="AB112" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12641,10 +12641,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293262</v>
+        <v>127294788</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437131</v>
+        <v>437274</v>
       </c>
       <c r="R113" t="n">
-        <v>6763892</v>
+        <v>6764023</v>
       </c>
       <c r="S113" t="n">
         <v>9</v>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12751,7 +12751,7 @@
         <v>127290747</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12855,10 +12855,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127293240</v>
+        <v>127293262</v>
       </c>
       <c r="B115" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,37 +12866,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437122</v>
+        <v>437131</v>
       </c>
       <c r="R115" t="n">
-        <v>6763905</v>
+        <v>6763892</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127294788</v>
+        <v>127293240</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437274</v>
+        <v>437122</v>
       </c>
       <c r="R116" t="n">
-        <v>6764023</v>
+        <v>6763905</v>
       </c>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,12 +13057,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13072,7 +13072,7 @@
         <v>127291635</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13283,48 +13283,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127290203</v>
+        <v>127291536</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>437188</v>
+        <v>436972</v>
       </c>
       <c r="R119" t="n">
-        <v>6763793</v>
+        <v>6763733</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,12 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Även miljöbilder</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13383,60 +13378,65 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127290773</v>
+        <v>127290001</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>57823</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437081</v>
+        <v>437239</v>
       </c>
       <c r="R120" t="n">
-        <v>6763812</v>
+        <v>6763818</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13502,10 +13502,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127291536</v>
+        <v>127293427</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13533,17 +13533,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436972</v>
+        <v>437147</v>
       </c>
       <c r="R121" t="n">
-        <v>6763733</v>
+        <v>6763942</v>
       </c>
       <c r="S121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13597,22 +13597,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127293427</v>
+        <v>127293635</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437147</v>
+        <v>437130</v>
       </c>
       <c r="R122" t="n">
-        <v>6763942</v>
+        <v>6763988</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127293635</v>
+        <v>127290203</v>
       </c>
       <c r="B123" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437130</v>
+        <v>437188</v>
       </c>
       <c r="R123" t="n">
-        <v>6763988</v>
+        <v>6763793</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13797,6 +13797,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Även miljöbilder</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13823,53 +13828,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127290001</v>
+        <v>127290773</v>
       </c>
       <c r="B124" t="n">
-        <v>57821</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437239</v>
+        <v>437081</v>
       </c>
       <c r="R124" t="n">
-        <v>6763818</v>
+        <v>6763812</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13935,53 +13935,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127293007</v>
+        <v>127295889</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437076</v>
+        <v>437244</v>
       </c>
       <c r="R125" t="n">
-        <v>6763849</v>
+        <v>6763890</v>
       </c>
       <c r="S125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14020,12 +14020,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Två torrtallar</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14040,57 +14035,62 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127290736</v>
+        <v>127292816</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>437102</v>
+        <v>436992</v>
       </c>
       <c r="R126" t="n">
-        <v>6763801</v>
+        <v>6763834</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127292627</v>
+        <v>127293007</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -14199,10 +14199,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>437059</v>
+        <v>437076</v>
       </c>
       <c r="R127" t="n">
-        <v>6763861</v>
+        <v>6763849</v>
       </c>
       <c r="S127" t="n">
         <v>9</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14244,7 +14244,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Två torrtallar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14271,50 +14276,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127295889</v>
+        <v>127290736</v>
       </c>
       <c r="B128" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437244</v>
+        <v>437102</v>
       </c>
       <c r="R128" t="n">
-        <v>6763890</v>
+        <v>6763801</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14383,53 +14383,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127292816</v>
+        <v>127292627</v>
       </c>
       <c r="B129" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436992</v>
+        <v>437059</v>
       </c>
       <c r="R129" t="n">
-        <v>6763834</v>
+        <v>6763861</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14483,22 +14483,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127293305</v>
+        <v>127292761</v>
       </c>
       <c r="B130" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14526,17 +14526,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437137</v>
+        <v>436992</v>
       </c>
       <c r="R130" t="n">
-        <v>6763885</v>
+        <v>6763834</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,22 +14590,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127292761</v>
+        <v>127294311</v>
       </c>
       <c r="B131" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436992</v>
+        <v>437170</v>
       </c>
       <c r="R131" t="n">
-        <v>6763834</v>
+        <v>6764043</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14683,6 +14683,11 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14709,48 +14714,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127294311</v>
+        <v>127293270</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437170</v>
+        <v>437124</v>
       </c>
       <c r="R132" t="n">
-        <v>6764043</v>
+        <v>6763885</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14779,7 +14784,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14789,12 +14794,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14809,19 +14809,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295386</v>
+        <v>127295217</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -14856,10 +14856,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437233</v>
+        <v>437312</v>
       </c>
       <c r="R133" t="n">
-        <v>6763867</v>
+        <v>6763984</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14928,7 +14928,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127294021</v>
+        <v>127295386</v>
       </c>
       <c r="B134" t="n">
         <v>8450</v>
@@ -14959,17 +14959,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437191</v>
+        <v>437233</v>
       </c>
       <c r="R134" t="n">
-        <v>6763952</v>
+        <v>6763867</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15023,19 +15023,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127295217</v>
+        <v>127294021</v>
       </c>
       <c r="B135" t="n">
         <v>8450</v>
@@ -15066,17 +15066,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437312</v>
+        <v>437191</v>
       </c>
       <c r="R135" t="n">
-        <v>6763984</v>
+        <v>6763952</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15130,44 +15130,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127293270</v>
+        <v>127293305</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437124</v>
+        <v>437137</v>
       </c>
       <c r="R136" t="n">
         <v>6763885</v>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15252,7 +15252,7 @@
         <v>127295725</v>
       </c>
       <c r="B137" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127293774</v>
+        <v>127295019</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437187</v>
+        <v>437299</v>
       </c>
       <c r="R2" t="n">
-        <v>6763964</v>
+        <v>6763962</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,57 +775,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127294422</v>
+        <v>127293337</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437193</v>
+        <v>437130</v>
       </c>
       <c r="R3" t="n">
-        <v>6764064</v>
+        <v>6763889</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127294146</v>
+        <v>127295923</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437131</v>
+        <v>437244</v>
       </c>
       <c r="R4" t="n">
-        <v>6764010</v>
+        <v>6763901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295045</v>
+        <v>127293774</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1027,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437295</v>
+        <v>437187</v>
       </c>
       <c r="R5" t="n">
-        <v>6763947</v>
+        <v>6763964</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1101,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295759</v>
+        <v>127290437</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1138,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437218</v>
+        <v>437157</v>
       </c>
       <c r="R6" t="n">
-        <v>6763878</v>
+        <v>6763806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295923</v>
+        <v>127294422</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437244</v>
+        <v>437193</v>
       </c>
       <c r="R7" t="n">
-        <v>6763901</v>
+        <v>6764064</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127291489</v>
+        <v>127295759</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1352,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437044</v>
+        <v>437218</v>
       </c>
       <c r="R8" t="n">
-        <v>6763790</v>
+        <v>6763878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127290437</v>
+        <v>127294146</v>
       </c>
       <c r="B9" t="n">
         <v>79020</v>
@@ -1459,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437157</v>
+        <v>437131</v>
       </c>
       <c r="R9" t="n">
-        <v>6763806</v>
+        <v>6764010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,53 +1541,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295019</v>
+        <v>127291489</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437299</v>
+        <v>437044</v>
       </c>
       <c r="R10" t="n">
-        <v>6763962</v>
+        <v>6763790</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,62 +1636,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127293337</v>
+        <v>127295045</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437130</v>
+        <v>437295</v>
       </c>
       <c r="R11" t="n">
-        <v>6763889</v>
+        <v>6763947</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294354</v>
+        <v>127294041</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437188</v>
+        <v>437152</v>
       </c>
       <c r="R12" t="n">
-        <v>6764029</v>
+        <v>6764014</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,12 +1850,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127291056</v>
+        <v>127294354</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437040</v>
+        <v>437188</v>
       </c>
       <c r="R14" t="n">
-        <v>6763751</v>
+        <v>6764029</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127294041</v>
+        <v>127294738</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437152</v>
+        <v>437220</v>
       </c>
       <c r="R15" t="n">
-        <v>6764014</v>
+        <v>6764061</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127294738</v>
+        <v>127291056</v>
       </c>
       <c r="B16" t="n">
         <v>79020</v>
@@ -2214,17 +2214,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437220</v>
+        <v>437040</v>
       </c>
       <c r="R16" t="n">
-        <v>6764061</v>
+        <v>6763751</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,12 +2278,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293735</v>
+        <v>127295078</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -3070,17 +3070,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437156</v>
+        <v>437293</v>
       </c>
       <c r="R24" t="n">
-        <v>6763978</v>
+        <v>6763940</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,62 +3134,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127293241</v>
+        <v>127294346</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437135</v>
+        <v>437187</v>
       </c>
       <c r="R25" t="n">
-        <v>6763885</v>
+        <v>6764029</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3221,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,32 +3253,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127292736</v>
+        <v>127293735</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436991</v>
+        <v>437156</v>
       </c>
       <c r="R26" t="n">
-        <v>6763816</v>
+        <v>6763978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,45 +3360,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293161</v>
+        <v>127293820</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437098</v>
+        <v>437201</v>
       </c>
       <c r="R27" t="n">
-        <v>6763941</v>
+        <v>6763976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295078</v>
+        <v>127295384</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3483,37 +3483,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437293</v>
+        <v>437233</v>
       </c>
       <c r="R28" t="n">
-        <v>6763940</v>
+        <v>6763867</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,57 +3572,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127294346</v>
+        <v>127293241</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437187</v>
+        <v>437135</v>
       </c>
       <c r="R29" t="n">
-        <v>6764029</v>
+        <v>6763885</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3649,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,50 +3696,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293820</v>
+        <v>127292736</v>
       </c>
       <c r="B30" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437201</v>
+        <v>436991</v>
       </c>
       <c r="R30" t="n">
-        <v>6763976</v>
+        <v>6763816</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,50 +3803,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295384</v>
+        <v>127293161</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437233</v>
+        <v>437098</v>
       </c>
       <c r="R31" t="n">
-        <v>6763867</v>
+        <v>6763941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,53 +3910,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294136</v>
+        <v>127293696</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437182</v>
+        <v>437156</v>
       </c>
       <c r="R32" t="n">
-        <v>6763976</v>
+        <v>6763982</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4010,19 +4005,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127293914</v>
+        <v>127293203</v>
       </c>
       <c r="B33" t="n">
         <v>79020</v>
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437190</v>
+        <v>437116</v>
       </c>
       <c r="R33" t="n">
-        <v>6763999</v>
+        <v>6763949</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4124,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293203</v>
+        <v>127293981</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -4164,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437116</v>
+        <v>437177</v>
       </c>
       <c r="R34" t="n">
-        <v>6763949</v>
+        <v>6764017</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4236,7 +4231,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127293696</v>
+        <v>127295057</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -4267,17 +4262,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437156</v>
+        <v>437295</v>
       </c>
       <c r="R35" t="n">
-        <v>6763982</v>
+        <v>6763942</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4331,19 +4326,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293981</v>
+        <v>127293914</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4378,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437177</v>
+        <v>437190</v>
       </c>
       <c r="R36" t="n">
-        <v>6764017</v>
+        <v>6763999</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,45 +4445,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295057</v>
+        <v>127294136</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437295</v>
+        <v>437182</v>
       </c>
       <c r="R37" t="n">
-        <v>6763942</v>
+        <v>6763976</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127292669</v>
+        <v>127292954</v>
       </c>
       <c r="B39" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437023</v>
+        <v>437050</v>
       </c>
       <c r="R39" t="n">
-        <v>6763818</v>
+        <v>6763860</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,19 +4759,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127292954</v>
+        <v>127295245</v>
       </c>
       <c r="B40" t="n">
         <v>79020</v>
@@ -4802,17 +4802,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437050</v>
+        <v>437308</v>
       </c>
       <c r="R40" t="n">
-        <v>6763860</v>
+        <v>6763966</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,22 +4866,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295245</v>
+        <v>127292669</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437308</v>
+        <v>437023</v>
       </c>
       <c r="R41" t="n">
-        <v>6763966</v>
+        <v>6763818</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5306,10 +5306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127292980</v>
+        <v>127295897</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5317,37 +5317,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437068</v>
+        <v>437244</v>
       </c>
       <c r="R45" t="n">
-        <v>6763858</v>
+        <v>6763890</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5401,19 +5401,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127291031</v>
+        <v>127292980</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -5444,17 +5444,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437097</v>
+        <v>437068</v>
       </c>
       <c r="R46" t="n">
-        <v>6763850</v>
+        <v>6763858</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5508,22 +5508,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127290803</v>
+        <v>127291031</v>
       </c>
       <c r="B47" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,39 +5531,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437091</v>
+        <v>437097</v>
       </c>
       <c r="R47" t="n">
-        <v>6763822</v>
+        <v>6763850</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5627,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127292927</v>
+        <v>127294741</v>
       </c>
       <c r="B48" t="n">
         <v>79020</v>
@@ -5663,17 +5658,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437032</v>
+        <v>437209</v>
       </c>
       <c r="R48" t="n">
-        <v>6763858</v>
+        <v>6764061</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127294741</v>
+        <v>127292927</v>
       </c>
       <c r="B49" t="n">
         <v>79020</v>
@@ -5770,17 +5765,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437209</v>
+        <v>437032</v>
       </c>
       <c r="R49" t="n">
-        <v>6764061</v>
+        <v>6763858</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5814,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5834,22 +5829,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295897</v>
+        <v>127293956</v>
       </c>
       <c r="B50" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,21 +5852,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5881,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437244</v>
+        <v>437202</v>
       </c>
       <c r="R50" t="n">
-        <v>6763890</v>
+        <v>6764007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,10 +5948,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127293956</v>
+        <v>127290803</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,34 +5959,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437202</v>
+        <v>437091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764007</v>
+        <v>6763822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127293209</v>
+        <v>127291397</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437116</v>
+        <v>437058</v>
       </c>
       <c r="R54" t="n">
-        <v>6763949</v>
+        <v>6763796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127291397</v>
+        <v>127290094</v>
       </c>
       <c r="B55" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437058</v>
+        <v>437239</v>
       </c>
       <c r="R55" t="n">
-        <v>6763796</v>
+        <v>6763818</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6462,6 +6462,11 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6488,7 +6493,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127290094</v>
+        <v>127290996</v>
       </c>
       <c r="B56" t="n">
         <v>79020</v>
@@ -6523,13 +6528,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437239</v>
+        <v>437108</v>
       </c>
       <c r="R56" t="n">
-        <v>6763818</v>
+        <v>6763849</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6569,11 +6574,6 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6600,32 +6600,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127290996</v>
+        <v>127293209</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437108</v>
+        <v>437116</v>
       </c>
       <c r="R57" t="n">
-        <v>6763849</v>
+        <v>6763949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127294772</v>
+        <v>127293072</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6718,37 +6718,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437255</v>
+        <v>437081</v>
       </c>
       <c r="R58" t="n">
-        <v>6764049</v>
+        <v>6763901</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,19 +6802,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294736</v>
+        <v>127294772</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437212</v>
+        <v>437255</v>
       </c>
       <c r="R59" t="n">
-        <v>6764065</v>
+        <v>6764049</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6921,7 +6921,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294411</v>
+        <v>127295806</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437202</v>
+        <v>437212</v>
       </c>
       <c r="R60" t="n">
-        <v>6764041</v>
+        <v>6763955</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7028,7 +7028,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294985</v>
+        <v>127294736</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -7063,10 +7063,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437293</v>
+        <v>437212</v>
       </c>
       <c r="R61" t="n">
-        <v>6763965</v>
+        <v>6764065</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7135,7 +7135,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294416</v>
+        <v>127294985</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -7166,17 +7166,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437158</v>
+        <v>437293</v>
       </c>
       <c r="R62" t="n">
-        <v>6764069</v>
+        <v>6763965</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7230,19 +7230,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127295806</v>
+        <v>127294416</v>
       </c>
       <c r="B63" t="n">
         <v>79020</v>
@@ -7273,17 +7273,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437212</v>
+        <v>437158</v>
       </c>
       <c r="R63" t="n">
-        <v>6763955</v>
+        <v>6764069</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7337,22 +7337,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127293072</v>
+        <v>127294411</v>
       </c>
       <c r="B64" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,37 +7360,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437081</v>
+        <v>437202</v>
       </c>
       <c r="R64" t="n">
-        <v>6763901</v>
+        <v>6764041</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7444,12 +7444,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290751</v>
+        <v>127290959</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7793,37 +7793,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437062</v>
+        <v>437097</v>
       </c>
       <c r="R68" t="n">
-        <v>6763738</v>
+        <v>6763868</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,12 +7877,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7996,10 +7996,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127290959</v>
+        <v>127290751</v>
       </c>
       <c r="B70" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8007,37 +8007,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437097</v>
+        <v>437062</v>
       </c>
       <c r="R70" t="n">
-        <v>6763868</v>
+        <v>6763738</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8091,12 +8091,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8424,48 +8424,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R74" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8519,12 +8524,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8745,53 +8750,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127292676</v>
+        <v>127294842</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437043</v>
+        <v>437280</v>
       </c>
       <c r="R77" t="n">
-        <v>6763840</v>
+        <v>6764030</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,22 +8845,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293677</v>
+        <v>127290717</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8868,34 +8868,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437148</v>
+        <v>437108</v>
       </c>
       <c r="R78" t="n">
-        <v>6764001</v>
+        <v>6763809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8964,7 +8969,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127293789</v>
+        <v>127293897</v>
       </c>
       <c r="B79" t="n">
         <v>79020</v>
@@ -8999,10 +9004,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437218</v>
+        <v>437180</v>
       </c>
       <c r="R79" t="n">
-        <v>6763950</v>
+        <v>6763986</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9071,7 +9076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127294716</v>
+        <v>127293504</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -9102,17 +9107,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437199</v>
+        <v>437136</v>
       </c>
       <c r="R80" t="n">
-        <v>6764063</v>
+        <v>6763963</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9141,7 +9146,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9151,7 +9156,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,19 +9171,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127293504</v>
+        <v>127293789</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -9213,10 +9218,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437136</v>
+        <v>437218</v>
       </c>
       <c r="R81" t="n">
-        <v>6763963</v>
+        <v>6763950</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9285,10 +9290,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127290717</v>
+        <v>127293677</v>
       </c>
       <c r="B82" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9296,39 +9301,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437108</v>
+        <v>437148</v>
       </c>
       <c r="R82" t="n">
-        <v>6763809</v>
+        <v>6764001</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9397,48 +9397,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127293090</v>
+        <v>127294433</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437081</v>
+        <v>437180</v>
       </c>
       <c r="R83" t="n">
-        <v>6763901</v>
+        <v>6764047</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,19 +9492,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127293897</v>
+        <v>127294716</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -9535,17 +9535,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437180</v>
+        <v>437199</v>
       </c>
       <c r="R84" t="n">
-        <v>6763986</v>
+        <v>6764063</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,60 +9599,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127294433</v>
+        <v>127293090</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437180</v>
+        <v>437081</v>
       </c>
       <c r="R85" t="n">
-        <v>6764047</v>
+        <v>6763901</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,60 +9706,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127295035</v>
+        <v>127292822</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437297</v>
+        <v>436992</v>
       </c>
       <c r="R86" t="n">
-        <v>6763951</v>
+        <v>6763834</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,60 +9813,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127292924</v>
+        <v>127295269</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437037</v>
+        <v>437297</v>
       </c>
       <c r="R87" t="n">
-        <v>6763860</v>
+        <v>6763935</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9920,60 +9920,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127290757</v>
+        <v>127292999</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437058</v>
+        <v>437093</v>
       </c>
       <c r="R88" t="n">
-        <v>6763741</v>
+        <v>6763880</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,19 +10027,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127295596</v>
+        <v>127293022</v>
       </c>
       <c r="B89" t="n">
         <v>79020</v>
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437169</v>
+        <v>437081</v>
       </c>
       <c r="R89" t="n">
-        <v>6763904</v>
+        <v>6763901</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127295863</v>
+        <v>127295035</v>
       </c>
       <c r="B90" t="n">
         <v>79020</v>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437221</v>
+        <v>437297</v>
       </c>
       <c r="R90" t="n">
-        <v>6763950</v>
+        <v>6763951</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10253,7 +10253,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127291960</v>
+        <v>127295863</v>
       </c>
       <c r="B91" t="n">
         <v>79020</v>
@@ -10284,17 +10284,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437015</v>
+        <v>437221</v>
       </c>
       <c r="R91" t="n">
-        <v>6763762</v>
+        <v>6763950</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10348,19 +10348,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127293022</v>
+        <v>127291960</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437081</v>
+        <v>437015</v>
       </c>
       <c r="R92" t="n">
-        <v>6763901</v>
+        <v>6763762</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10467,32 +10467,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127292822</v>
+        <v>127295596</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436992</v>
+        <v>437169</v>
       </c>
       <c r="R93" t="n">
-        <v>6763834</v>
+        <v>6763904</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,48 +10574,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127295269</v>
+        <v>127292924</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437297</v>
+        <v>437037</v>
       </c>
       <c r="R94" t="n">
-        <v>6763935</v>
+        <v>6763860</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,60 +10669,60 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127292999</v>
+        <v>127290757</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437093</v>
+        <v>437058</v>
       </c>
       <c r="R95" t="n">
-        <v>6763880</v>
+        <v>6763741</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10776,39 +10776,39 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127293348</v>
+        <v>127295309</v>
       </c>
       <c r="B96" t="n">
-        <v>57660</v>
+        <v>58033</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10819,7 +10819,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10828,13 +10828,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437154</v>
+        <v>437289</v>
       </c>
       <c r="R96" t="n">
-        <v>6763925</v>
+        <v>6763874</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127293249</v>
+        <v>127290978</v>
       </c>
       <c r="B97" t="n">
         <v>79020</v>
@@ -10931,17 +10931,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437134</v>
+        <v>437098</v>
       </c>
       <c r="R97" t="n">
-        <v>6763889</v>
+        <v>6763850</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10995,19 +10995,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293586</v>
+        <v>127293029</v>
       </c>
       <c r="B98" t="n">
         <v>79020</v>
@@ -11038,17 +11038,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437163</v>
+        <v>437074</v>
       </c>
       <c r="R98" t="n">
-        <v>6763902</v>
+        <v>6763890</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11102,22 +11102,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127293953</v>
+        <v>127293249</v>
       </c>
       <c r="B99" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11125,43 +11125,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437190</v>
+        <v>437134</v>
       </c>
       <c r="R99" t="n">
-        <v>6763937</v>
+        <v>6763889</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -11193,7 +11184,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11203,7 +11194,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11337,7 +11328,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293029</v>
+        <v>127293586</v>
       </c>
       <c r="B101" t="n">
         <v>79020</v>
@@ -11368,17 +11359,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437074</v>
+        <v>437163</v>
       </c>
       <c r="R101" t="n">
-        <v>6763890</v>
+        <v>6763902</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11407,7 +11398,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11417,7 +11408,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11432,22 +11423,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127290978</v>
+        <v>127293953</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11455,37 +11446,46 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437098</v>
+        <v>437190</v>
       </c>
       <c r="R102" t="n">
-        <v>6763850</v>
+        <v>6763937</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,39 +11539,39 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127295309</v>
+        <v>127293348</v>
       </c>
       <c r="B103" t="n">
-        <v>58033</v>
+        <v>57660</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11582,7 +11582,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437289</v>
+        <v>437154</v>
       </c>
       <c r="R103" t="n">
-        <v>6763874</v>
+        <v>6763925</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11663,45 +11663,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127294008</v>
+        <v>127294074</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437190</v>
+        <v>437189</v>
       </c>
       <c r="R104" t="n">
-        <v>6763955</v>
+        <v>6763951</v>
       </c>
       <c r="S104" t="n">
         <v>9</v>
@@ -11733,7 +11738,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11743,7 +11748,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11770,32 +11775,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127292751</v>
+        <v>127293475</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11805,10 +11810,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436974</v>
+        <v>437136</v>
       </c>
       <c r="R105" t="n">
-        <v>6763823</v>
+        <v>6763963</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11877,53 +11882,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127294074</v>
+        <v>127292751</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>437189</v>
+        <v>436974</v>
       </c>
       <c r="R106" t="n">
-        <v>6763951</v>
+        <v>6763823</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11977,60 +11977,60 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127293475</v>
+        <v>127294008</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>437136</v>
+        <v>437190</v>
       </c>
       <c r="R107" t="n">
-        <v>6763963</v>
+        <v>6763955</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12084,22 +12084,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127291177</v>
+        <v>127293290</v>
       </c>
       <c r="B108" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12107,21 +12107,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437081</v>
+        <v>437138</v>
       </c>
       <c r="R108" t="n">
-        <v>6763837</v>
+        <v>6763901</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12177,6 +12177,11 @@
       <c r="AB108" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12203,32 +12208,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127290265</v>
+        <v>127291177</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437187</v>
+        <v>437081</v>
       </c>
       <c r="R109" t="n">
-        <v>6763801</v>
+        <v>6763837</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12310,7 +12315,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127294388</v>
+        <v>127290265</v>
       </c>
       <c r="B110" t="n">
         <v>8450</v>
@@ -12341,17 +12346,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437183</v>
+        <v>437187</v>
       </c>
       <c r="R110" t="n">
-        <v>6764033</v>
+        <v>6763801</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12380,7 +12385,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12390,7 +12395,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12405,19 +12410,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127292727</v>
+        <v>127294388</v>
       </c>
       <c r="B111" t="n">
         <v>8450</v>
@@ -12446,21 +12451,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437043</v>
+        <v>437183</v>
       </c>
       <c r="R111" t="n">
-        <v>6763856</v>
+        <v>6764033</v>
       </c>
       <c r="S111" t="n">
         <v>9</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12529,48 +12529,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127293290</v>
+        <v>127292727</v>
       </c>
       <c r="B112" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437138</v>
+        <v>437043</v>
       </c>
       <c r="R112" t="n">
-        <v>6763901</v>
+        <v>6763856</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12599,7 +12604,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12609,12 +12614,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12629,22 +12629,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127294788</v>
+        <v>127293240</v>
       </c>
       <c r="B113" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12652,37 +12652,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437274</v>
+        <v>437122</v>
       </c>
       <c r="R113" t="n">
-        <v>6764023</v>
+        <v>6763905</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,60 +12736,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127290747</v>
+        <v>127293766</v>
       </c>
       <c r="B114" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437064</v>
+        <v>437187</v>
       </c>
       <c r="R114" t="n">
-        <v>6763744</v>
+        <v>6763964</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12843,19 +12843,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127293262</v>
+        <v>127291635</v>
       </c>
       <c r="B115" t="n">
         <v>79020</v>
@@ -12886,17 +12886,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437131</v>
+        <v>437032</v>
       </c>
       <c r="R115" t="n">
-        <v>6763892</v>
+        <v>6763776</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12950,22 +12950,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127293240</v>
+        <v>127294788</v>
       </c>
       <c r="B116" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,37 +12973,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437122</v>
+        <v>437274</v>
       </c>
       <c r="R116" t="n">
-        <v>6763905</v>
+        <v>6764023</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,19 +13057,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127291635</v>
+        <v>127293262</v>
       </c>
       <c r="B117" t="n">
         <v>79020</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437032</v>
+        <v>437131</v>
       </c>
       <c r="R117" t="n">
-        <v>6763776</v>
+        <v>6763892</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,60 +13164,60 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127293766</v>
+        <v>127290747</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437187</v>
+        <v>437064</v>
       </c>
       <c r="R118" t="n">
-        <v>6763964</v>
+        <v>6763744</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13271,19 +13271,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127291536</v>
+        <v>127293427</v>
       </c>
       <c r="B119" t="n">
         <v>79020</v>
@@ -13314,17 +13314,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436972</v>
+        <v>437147</v>
       </c>
       <c r="R119" t="n">
-        <v>6763733</v>
+        <v>6763942</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13378,22 +13378,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127290001</v>
+        <v>127293635</v>
       </c>
       <c r="B120" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13401,42 +13401,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437239</v>
+        <v>437130</v>
       </c>
       <c r="R120" t="n">
-        <v>6763818</v>
+        <v>6763988</v>
       </c>
       <c r="S120" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13502,7 +13497,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127293427</v>
+        <v>127291536</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -13533,17 +13528,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437147</v>
+        <v>436972</v>
       </c>
       <c r="R121" t="n">
-        <v>6763942</v>
+        <v>6763733</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13572,7 +13567,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13582,7 +13577,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13597,22 +13592,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127293635</v>
+        <v>127290001</v>
       </c>
       <c r="B122" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13620,37 +13615,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437130</v>
+        <v>437239</v>
       </c>
       <c r="R122" t="n">
-        <v>6763988</v>
+        <v>6763818</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13935,53 +13935,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127295889</v>
+        <v>127293007</v>
       </c>
       <c r="B125" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437244</v>
+        <v>437076</v>
       </c>
       <c r="R125" t="n">
-        <v>6763890</v>
+        <v>6763849</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14020,7 +14020,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Två torrtallar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14035,62 +14040,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127292816</v>
+        <v>127290736</v>
       </c>
       <c r="B126" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436992</v>
+        <v>437102</v>
       </c>
       <c r="R126" t="n">
-        <v>6763834</v>
+        <v>6763801</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127293007</v>
+        <v>127292627</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -14199,10 +14199,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>437076</v>
+        <v>437059</v>
       </c>
       <c r="R127" t="n">
-        <v>6763849</v>
+        <v>6763861</v>
       </c>
       <c r="S127" t="n">
         <v>9</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14244,12 +14244,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Två torrtallar</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14276,45 +14271,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127290736</v>
+        <v>127295889</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437102</v>
+        <v>437244</v>
       </c>
       <c r="R128" t="n">
-        <v>6763801</v>
+        <v>6763890</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14383,53 +14383,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127292627</v>
+        <v>127292816</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>437059</v>
+        <v>436992</v>
       </c>
       <c r="R129" t="n">
-        <v>6763861</v>
+        <v>6763834</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14483,60 +14483,60 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127292761</v>
+        <v>127293270</v>
       </c>
       <c r="B130" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436992</v>
+        <v>437124</v>
       </c>
       <c r="R130" t="n">
-        <v>6763834</v>
+        <v>6763885</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,44 +14590,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127294311</v>
+        <v>127295217</v>
       </c>
       <c r="B131" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437170</v>
+        <v>437312</v>
       </c>
       <c r="R131" t="n">
-        <v>6764043</v>
+        <v>6763984</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14683,11 +14683,6 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14714,7 +14709,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127293270</v>
+        <v>127295386</v>
       </c>
       <c r="B132" t="n">
         <v>8450</v>
@@ -14745,17 +14740,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437124</v>
+        <v>437233</v>
       </c>
       <c r="R132" t="n">
-        <v>6763885</v>
+        <v>6763867</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14784,7 +14779,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14794,7 +14789,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14809,19 +14804,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127295217</v>
+        <v>127294021</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -14852,17 +14847,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437312</v>
+        <v>437191</v>
       </c>
       <c r="R133" t="n">
-        <v>6763984</v>
+        <v>6763952</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14891,7 +14886,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14901,7 +14896,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14916,60 +14911,60 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127295386</v>
+        <v>127293305</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437233</v>
+        <v>437137</v>
       </c>
       <c r="R134" t="n">
-        <v>6763867</v>
+        <v>6763885</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14998,7 +14993,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15008,7 +15003,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15023,60 +15018,60 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127294021</v>
+        <v>127292761</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437191</v>
+        <v>436992</v>
       </c>
       <c r="R135" t="n">
-        <v>6763952</v>
+        <v>6763834</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15105,7 +15100,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15115,7 +15110,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15130,19 +15125,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127293305</v>
+        <v>127294311</v>
       </c>
       <c r="B136" t="n">
         <v>79020</v>
@@ -15173,17 +15168,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437137</v>
+        <v>437170</v>
       </c>
       <c r="R136" t="n">
-        <v>6763885</v>
+        <v>6764043</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15212,7 +15207,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15222,7 +15217,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -3039,45 +3039,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295078</v>
+        <v>127293241</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437293</v>
+        <v>437135</v>
       </c>
       <c r="R24" t="n">
-        <v>6763940</v>
+        <v>6763885</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3109,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,48 +3151,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294346</v>
+        <v>127292736</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437187</v>
+        <v>436991</v>
       </c>
       <c r="R25" t="n">
-        <v>6764029</v>
+        <v>6763816</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,44 +3246,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127293735</v>
+        <v>127293161</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437156</v>
+        <v>437098</v>
       </c>
       <c r="R26" t="n">
-        <v>6763978</v>
+        <v>6763941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,50 +3589,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127293241</v>
+        <v>127295078</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437135</v>
+        <v>437293</v>
       </c>
       <c r="R29" t="n">
-        <v>6763885</v>
+        <v>6763940</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,48 +3696,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127292736</v>
+        <v>127294346</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436991</v>
+        <v>437187</v>
       </c>
       <c r="R30" t="n">
-        <v>6763816</v>
+        <v>6764029</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,44 +3791,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127293161</v>
+        <v>127293735</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437098</v>
+        <v>437156</v>
       </c>
       <c r="R31" t="n">
-        <v>6763941</v>
+        <v>6763978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -5948,50 +5948,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290803</v>
+        <v>127290540</v>
       </c>
       <c r="B51" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437091</v>
+        <v>437113</v>
       </c>
       <c r="R51" t="n">
-        <v>6763822</v>
+        <v>6763817</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127290540</v>
+        <v>127294782</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6091,17 +6086,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437113</v>
+        <v>437273</v>
       </c>
       <c r="R52" t="n">
-        <v>6763817</v>
+        <v>6764025</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6130,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6140,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6155,60 +6150,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127294782</v>
+        <v>127290803</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437273</v>
+        <v>437091</v>
       </c>
       <c r="R53" t="n">
-        <v>6764025</v>
+        <v>6763822</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,12 +6262,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -8857,50 +8857,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127290717</v>
+        <v>127293090</v>
       </c>
       <c r="B78" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R78" t="n">
-        <v>6763809</v>
+        <v>6763901</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9611,45 +9606,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127293090</v>
+        <v>127290717</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437081</v>
+        <v>437108</v>
       </c>
       <c r="R85" t="n">
-        <v>6763901</v>
+        <v>6763809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11663,53 +11663,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127294074</v>
+        <v>127292751</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437189</v>
+        <v>436974</v>
       </c>
       <c r="R104" t="n">
-        <v>6763951</v>
+        <v>6763823</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11738,7 +11733,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11748,7 +11743,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11763,60 +11758,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127293475</v>
+        <v>127294008</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>437136</v>
+        <v>437190</v>
       </c>
       <c r="R105" t="n">
-        <v>6763963</v>
+        <v>6763955</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11845,7 +11840,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11855,7 +11850,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11870,60 +11865,65 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127292751</v>
+        <v>127294074</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436974</v>
+        <v>437189</v>
       </c>
       <c r="R106" t="n">
-        <v>6763823</v>
+        <v>6763951</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11977,60 +11977,60 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127294008</v>
+        <v>127293475</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>437190</v>
+        <v>437136</v>
       </c>
       <c r="R107" t="n">
-        <v>6763955</v>
+        <v>6763963</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12084,44 +12084,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127293290</v>
+        <v>127290265</v>
       </c>
       <c r="B108" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437138</v>
+        <v>437187</v>
       </c>
       <c r="R108" t="n">
-        <v>6763901</v>
+        <v>6763801</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12177,11 +12177,6 @@
       <c r="AB108" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12208,48 +12203,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127291177</v>
+        <v>127294388</v>
       </c>
       <c r="B109" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437081</v>
+        <v>437183</v>
       </c>
       <c r="R109" t="n">
-        <v>6763837</v>
+        <v>6764033</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12278,7 +12273,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12288,7 +12283,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12303,19 +12298,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127290265</v>
+        <v>127292727</v>
       </c>
       <c r="B110" t="n">
         <v>8450</v>
@@ -12344,19 +12339,24 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437187</v>
+        <v>437043</v>
       </c>
       <c r="R110" t="n">
-        <v>6763801</v>
+        <v>6763856</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12410,60 +12410,60 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127294388</v>
+        <v>127293290</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437183</v>
+        <v>437138</v>
       </c>
       <c r="R111" t="n">
-        <v>6764033</v>
+        <v>6763901</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12502,7 +12502,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12517,65 +12522,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127292727</v>
+        <v>127291177</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437043</v>
+        <v>437081</v>
       </c>
       <c r="R112" t="n">
-        <v>6763856</v>
+        <v>6763837</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12629,44 +12629,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293240</v>
+        <v>127293766</v>
       </c>
       <c r="B113" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437122</v>
+        <v>437187</v>
       </c>
       <c r="R113" t="n">
-        <v>6763905</v>
+        <v>6763964</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12748,32 +12748,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293766</v>
+        <v>127293240</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12783,10 +12783,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437187</v>
+        <v>437122</v>
       </c>
       <c r="R114" t="n">
-        <v>6763964</v>
+        <v>6763905</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295019</v>
+        <v>127295759</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437299</v>
+        <v>437218</v>
       </c>
       <c r="R2" t="n">
-        <v>6763962</v>
+        <v>6763878</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127293337</v>
+        <v>127293774</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437130</v>
+        <v>437187</v>
       </c>
       <c r="R3" t="n">
-        <v>6763889</v>
+        <v>6763964</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1006,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127293774</v>
+        <v>127294146</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1041,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437187</v>
+        <v>437131</v>
       </c>
       <c r="R5" t="n">
-        <v>6763964</v>
+        <v>6764010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127290437</v>
+        <v>127294422</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1144,17 +1134,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437157</v>
+        <v>437193</v>
       </c>
       <c r="R6" t="n">
-        <v>6763806</v>
+        <v>6764064</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,19 +1198,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127294422</v>
+        <v>127291489</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1251,17 +1241,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437193</v>
+        <v>437044</v>
       </c>
       <c r="R7" t="n">
-        <v>6764064</v>
+        <v>6763790</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,19 +1305,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295759</v>
+        <v>127290437</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1362,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437218</v>
+        <v>437157</v>
       </c>
       <c r="R8" t="n">
-        <v>6763878</v>
+        <v>6763806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294146</v>
+        <v>127295045</v>
       </c>
       <c r="B9" t="n">
         <v>79020</v>
@@ -1465,17 +1455,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437131</v>
+        <v>437295</v>
       </c>
       <c r="R9" t="n">
-        <v>6764010</v>
+        <v>6763947</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,60 +1519,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291489</v>
+        <v>127293337</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437044</v>
+        <v>437130</v>
       </c>
       <c r="R10" t="n">
-        <v>6763790</v>
+        <v>6763889</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,57 +1631,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295045</v>
+        <v>127295019</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437295</v>
+        <v>437299</v>
       </c>
       <c r="R11" t="n">
-        <v>6763947</v>
+        <v>6763962</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294041</v>
+        <v>127294354</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1786,17 +1786,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437152</v>
+        <v>437188</v>
       </c>
       <c r="R12" t="n">
-        <v>6764014</v>
+        <v>6764029</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,12 +1850,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294354</v>
+        <v>127294041</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437188</v>
+        <v>437152</v>
       </c>
       <c r="R14" t="n">
-        <v>6764029</v>
+        <v>6764014</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,12 +2064,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127291525</v>
+        <v>127295240</v>
       </c>
       <c r="B21" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437044</v>
+        <v>437308</v>
       </c>
       <c r="R21" t="n">
-        <v>6763790</v>
+        <v>6763966</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,32 +2932,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295240</v>
+        <v>127291525</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437308</v>
+        <v>437044</v>
       </c>
       <c r="R23" t="n">
-        <v>6763966</v>
+        <v>6763790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,53 +3039,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293241</v>
+        <v>127293820</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437135</v>
+        <v>437201</v>
       </c>
       <c r="R24" t="n">
-        <v>6763885</v>
+        <v>6763976</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,57 +3139,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127292736</v>
+        <v>127295384</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436991</v>
+        <v>437233</v>
       </c>
       <c r="R25" t="n">
-        <v>6763816</v>
+        <v>6763867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127293161</v>
+        <v>127293735</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437098</v>
+        <v>437156</v>
       </c>
       <c r="R26" t="n">
-        <v>6763941</v>
+        <v>6763978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,10 +3370,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293820</v>
+        <v>127295078</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,42 +3381,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437201</v>
+        <v>437293</v>
       </c>
       <c r="R27" t="n">
-        <v>6763976</v>
+        <v>6763940</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,22 +3465,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295384</v>
+        <v>127294346</v>
       </c>
       <c r="B28" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,42 +3488,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437233</v>
+        <v>437187</v>
       </c>
       <c r="R28" t="n">
-        <v>6763867</v>
+        <v>6764029</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,57 +3572,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295078</v>
+        <v>127293241</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437293</v>
+        <v>437135</v>
       </c>
       <c r="R29" t="n">
-        <v>6763940</v>
+        <v>6763885</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,48 +3696,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127294346</v>
+        <v>127293161</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437187</v>
+        <v>437098</v>
       </c>
       <c r="R30" t="n">
-        <v>6764029</v>
+        <v>6763941</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,44 +3791,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127293735</v>
+        <v>127292736</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437156</v>
+        <v>436991</v>
       </c>
       <c r="R31" t="n">
-        <v>6763978</v>
+        <v>6763816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127293696</v>
+        <v>127293914</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437156</v>
+        <v>437190</v>
       </c>
       <c r="R32" t="n">
-        <v>6763982</v>
+        <v>6763999</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127293981</v>
+        <v>127295057</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -4155,17 +4155,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437177</v>
+        <v>437295</v>
       </c>
       <c r="R34" t="n">
-        <v>6764017</v>
+        <v>6763942</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,19 +4219,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295057</v>
+        <v>127293696</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -4262,17 +4262,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437295</v>
+        <v>437156</v>
       </c>
       <c r="R35" t="n">
-        <v>6763942</v>
+        <v>6763982</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,19 +4326,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293914</v>
+        <v>127293981</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437190</v>
+        <v>437177</v>
       </c>
       <c r="R36" t="n">
-        <v>6763999</v>
+        <v>6764017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127290586</v>
+        <v>127295245</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4588,17 +4588,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437065</v>
+        <v>437308</v>
       </c>
       <c r="R38" t="n">
-        <v>6763754</v>
+        <v>6763966</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4652,12 +4652,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295245</v>
+        <v>127292669</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437308</v>
+        <v>437023</v>
       </c>
       <c r="R40" t="n">
-        <v>6763966</v>
+        <v>6763818</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127292669</v>
+        <v>127290586</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,37 +4889,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437023</v>
+        <v>437065</v>
       </c>
       <c r="R41" t="n">
-        <v>6763818</v>
+        <v>6763754</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,60 +4973,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127291424</v>
+        <v>127294037</v>
       </c>
       <c r="B42" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437058</v>
+        <v>437188</v>
       </c>
       <c r="R42" t="n">
-        <v>6763796</v>
+        <v>6763952</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,19 +5080,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127294037</v>
+        <v>127293212</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5123,17 +5123,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437188</v>
+        <v>437120</v>
       </c>
       <c r="R43" t="n">
-        <v>6763952</v>
+        <v>6763919</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,44 +5187,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127293212</v>
+        <v>127291424</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437120</v>
+        <v>437058</v>
       </c>
       <c r="R44" t="n">
-        <v>6763919</v>
+        <v>6763796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,10 +5306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295897</v>
+        <v>127292927</v>
       </c>
       <c r="B45" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5317,21 +5317,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437244</v>
+        <v>437032</v>
       </c>
       <c r="R45" t="n">
-        <v>6763890</v>
+        <v>6763858</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127292980</v>
+        <v>127294741</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437068</v>
+        <v>437209</v>
       </c>
       <c r="R46" t="n">
-        <v>6763858</v>
+        <v>6764061</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,7 +5520,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127291031</v>
+        <v>127292980</v>
       </c>
       <c r="B47" t="n">
         <v>79020</v>
@@ -5551,17 +5551,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437097</v>
+        <v>437068</v>
       </c>
       <c r="R47" t="n">
-        <v>6763850</v>
+        <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127294741</v>
+        <v>127295897</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,37 +5638,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437209</v>
+        <v>437244</v>
       </c>
       <c r="R48" t="n">
-        <v>6764061</v>
+        <v>6763890</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127292927</v>
+        <v>127293956</v>
       </c>
       <c r="B49" t="n">
         <v>79020</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437032</v>
+        <v>437202</v>
       </c>
       <c r="R49" t="n">
-        <v>6763858</v>
+        <v>6764007</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127293956</v>
+        <v>127291031</v>
       </c>
       <c r="B50" t="n">
         <v>79020</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437202</v>
+        <v>437097</v>
       </c>
       <c r="R50" t="n">
-        <v>6764007</v>
+        <v>6763850</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,45 +5948,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290540</v>
+        <v>127290803</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437113</v>
+        <v>437091</v>
       </c>
       <c r="R51" t="n">
-        <v>6763817</v>
+        <v>6763822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,7 +6060,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127294782</v>
+        <v>127290540</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6086,17 +6091,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437273</v>
+        <v>437113</v>
       </c>
       <c r="R52" t="n">
-        <v>6764025</v>
+        <v>6763817</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6125,7 +6130,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6135,7 +6140,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6150,65 +6155,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127290803</v>
+        <v>127294782</v>
       </c>
       <c r="B53" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437091</v>
+        <v>437273</v>
       </c>
       <c r="R53" t="n">
-        <v>6763822</v>
+        <v>6764025</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,12 +6262,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6707,32 +6707,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127293072</v>
+        <v>127293858</v>
       </c>
       <c r="B58" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437081</v>
+        <v>437201</v>
       </c>
       <c r="R58" t="n">
-        <v>6763901</v>
+        <v>6763976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,45 +6814,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294772</v>
+        <v>127290454</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437255</v>
+        <v>437078</v>
       </c>
       <c r="R59" t="n">
-        <v>6764049</v>
+        <v>6763737</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -6884,7 +6889,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6899,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6921,10 +6926,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127295806</v>
+        <v>127291537</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6932,37 +6937,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437212</v>
+        <v>437044</v>
       </c>
       <c r="R60" t="n">
-        <v>6763955</v>
+        <v>6763790</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6991,7 +6996,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7006,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7016,19 +7021,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127294736</v>
+        <v>127294772</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -7063,10 +7068,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437212</v>
+        <v>437255</v>
       </c>
       <c r="R61" t="n">
-        <v>6764065</v>
+        <v>6764049</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7098,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7135,7 +7140,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127294985</v>
+        <v>127294736</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -7170,10 +7175,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437293</v>
+        <v>437212</v>
       </c>
       <c r="R62" t="n">
-        <v>6763965</v>
+        <v>6764065</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7205,7 +7210,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7215,7 +7220,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7242,7 +7247,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127294416</v>
+        <v>127294985</v>
       </c>
       <c r="B63" t="n">
         <v>79020</v>
@@ -7273,17 +7278,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437158</v>
+        <v>437293</v>
       </c>
       <c r="R63" t="n">
-        <v>6764069</v>
+        <v>6763965</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,7 +7317,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7322,7 +7327,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7337,12 +7342,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7456,32 +7461,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127293858</v>
+        <v>127294416</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7491,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437201</v>
+        <v>437158</v>
       </c>
       <c r="R65" t="n">
-        <v>6763976</v>
+        <v>6764069</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7563,50 +7568,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127290454</v>
+        <v>127295806</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437078</v>
+        <v>437212</v>
       </c>
       <c r="R66" t="n">
-        <v>6763737</v>
+        <v>6763955</v>
       </c>
       <c r="S66" t="n">
         <v>9</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,10 +7675,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127291537</v>
+        <v>127293072</v>
       </c>
       <c r="B67" t="n">
-        <v>79609</v>
+        <v>91352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437044</v>
+        <v>437081</v>
       </c>
       <c r="R67" t="n">
-        <v>6763790</v>
+        <v>6763901</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127290959</v>
+        <v>127290713</v>
       </c>
       <c r="B68" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437097</v>
+        <v>437108</v>
       </c>
       <c r="R68" t="n">
-        <v>6763868</v>
+        <v>6763809</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7889,32 +7889,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127290826</v>
+        <v>127294714</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437081</v>
+        <v>437204</v>
       </c>
       <c r="R69" t="n">
-        <v>6763837</v>
+        <v>6764046</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7996,48 +7996,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127290751</v>
+        <v>127292742</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437062</v>
+        <v>437089</v>
       </c>
       <c r="R70" t="n">
-        <v>6763738</v>
+        <v>6763838</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8091,44 +8091,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127292742</v>
+        <v>127290826</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437089</v>
+        <v>437081</v>
       </c>
       <c r="R71" t="n">
-        <v>6763838</v>
+        <v>6763837</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,48 +8210,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127290713</v>
+        <v>127290751</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437108</v>
+        <v>437062</v>
       </c>
       <c r="R72" t="n">
-        <v>6763809</v>
+        <v>6763738</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8305,44 +8305,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127294714</v>
+        <v>127290959</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437204</v>
+        <v>437097</v>
       </c>
       <c r="R73" t="n">
-        <v>6764046</v>
+        <v>6763868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,53 +8424,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127292676</v>
+        <v>127294334</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437043</v>
+        <v>437170</v>
       </c>
       <c r="R74" t="n">
-        <v>6763840</v>
+        <v>6764043</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8509,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8524,22 +8519,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127294334</v>
+        <v>127295799</v>
       </c>
       <c r="B75" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8547,21 +8542,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437170</v>
+        <v>437234</v>
       </c>
       <c r="R75" t="n">
-        <v>6764043</v>
+        <v>6763858</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8643,7 +8638,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127295799</v>
+        <v>127294842</v>
       </c>
       <c r="B76" t="n">
         <v>79020</v>
@@ -8678,10 +8673,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437234</v>
+        <v>437280</v>
       </c>
       <c r="R76" t="n">
-        <v>6763858</v>
+        <v>6764030</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8750,48 +8745,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127294842</v>
+        <v>127292676</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437280</v>
+        <v>437043</v>
       </c>
       <c r="R77" t="n">
-        <v>6764030</v>
+        <v>6763840</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,57 +8845,62 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127293090</v>
+        <v>127290717</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437081</v>
+        <v>437108</v>
       </c>
       <c r="R78" t="n">
-        <v>6763901</v>
+        <v>6763809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9071,7 +9076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127293504</v>
+        <v>127293677</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -9106,10 +9111,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437136</v>
+        <v>437148</v>
       </c>
       <c r="R80" t="n">
-        <v>6763963</v>
+        <v>6764001</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,7 +9290,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127293677</v>
+        <v>127294716</v>
       </c>
       <c r="B82" t="n">
         <v>79020</v>
@@ -9316,17 +9321,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437148</v>
+        <v>437199</v>
       </c>
       <c r="R82" t="n">
-        <v>6764001</v>
+        <v>6764063</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9355,7 +9360,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9365,7 +9370,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,19 +9385,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127294433</v>
+        <v>127293504</v>
       </c>
       <c r="B83" t="n">
         <v>79020</v>
@@ -9423,17 +9428,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437180</v>
+        <v>437136</v>
       </c>
       <c r="R83" t="n">
-        <v>6764047</v>
+        <v>6763963</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9472,7 +9477,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,19 +9492,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127294716</v>
+        <v>127294433</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -9534,10 +9539,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437199</v>
+        <v>437180</v>
       </c>
       <c r="R84" t="n">
-        <v>6764063</v>
+        <v>6764047</v>
       </c>
       <c r="S84" t="n">
         <v>9</v>
@@ -9569,7 +9574,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9579,7 +9584,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9606,50 +9611,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127290717</v>
+        <v>127293090</v>
       </c>
       <c r="B85" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437108</v>
+        <v>437081</v>
       </c>
       <c r="R85" t="n">
-        <v>6763809</v>
+        <v>6763901</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9718,48 +9718,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127292822</v>
+        <v>127290757</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436992</v>
+        <v>437058</v>
       </c>
       <c r="R86" t="n">
-        <v>6763834</v>
+        <v>6763741</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,44 +9813,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127295269</v>
+        <v>127295596</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437297</v>
+        <v>437169</v>
       </c>
       <c r="R87" t="n">
-        <v>6763935</v>
+        <v>6763904</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9932,48 +9932,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127292999</v>
+        <v>127295863</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437093</v>
+        <v>437221</v>
       </c>
       <c r="R88" t="n">
-        <v>6763880</v>
+        <v>6763950</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,19 +10027,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127293022</v>
+        <v>127292924</v>
       </c>
       <c r="B89" t="n">
         <v>79020</v>
@@ -10070,17 +10070,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437081</v>
+        <v>437037</v>
       </c>
       <c r="R89" t="n">
-        <v>6763901</v>
+        <v>6763860</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10134,19 +10134,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127295035</v>
+        <v>127291960</v>
       </c>
       <c r="B90" t="n">
         <v>79020</v>
@@ -10177,17 +10177,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437297</v>
+        <v>437015</v>
       </c>
       <c r="R90" t="n">
-        <v>6763951</v>
+        <v>6763762</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10241,19 +10241,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127295863</v>
+        <v>127295035</v>
       </c>
       <c r="B91" t="n">
         <v>79020</v>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437221</v>
+        <v>437297</v>
       </c>
       <c r="R91" t="n">
-        <v>6763950</v>
+        <v>6763951</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10360,7 +10360,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127291960</v>
+        <v>127293022</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437015</v>
+        <v>437081</v>
       </c>
       <c r="R92" t="n">
-        <v>6763762</v>
+        <v>6763901</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10467,32 +10467,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127295596</v>
+        <v>127292999</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437169</v>
+        <v>437093</v>
       </c>
       <c r="R93" t="n">
-        <v>6763904</v>
+        <v>6763880</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,48 +10574,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127292924</v>
+        <v>127292822</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437037</v>
+        <v>436992</v>
       </c>
       <c r="R94" t="n">
-        <v>6763860</v>
+        <v>6763834</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10669,60 +10669,60 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127290757</v>
+        <v>127295269</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437058</v>
+        <v>437297</v>
       </c>
       <c r="R95" t="n">
-        <v>6763741</v>
+        <v>6763935</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10776,65 +10776,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127295309</v>
+        <v>127293586</v>
       </c>
       <c r="B96" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437289</v>
+        <v>437163</v>
       </c>
       <c r="R96" t="n">
-        <v>6763874</v>
+        <v>6763902</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10863,7 +10858,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10873,7 +10868,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10888,22 +10883,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127290978</v>
+        <v>127293953</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10911,37 +10906,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437098</v>
+        <v>437190</v>
       </c>
       <c r="R97" t="n">
-        <v>6763850</v>
+        <v>6763937</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10970,7 +10974,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10980,7 +10984,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10995,19 +10999,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127293029</v>
+        <v>127293371</v>
       </c>
       <c r="B98" t="n">
         <v>79020</v>
@@ -11042,10 +11046,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437074</v>
+        <v>437140</v>
       </c>
       <c r="R98" t="n">
-        <v>6763890</v>
+        <v>6763931</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11221,7 +11225,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127293371</v>
+        <v>127293029</v>
       </c>
       <c r="B100" t="n">
         <v>79020</v>
@@ -11256,10 +11260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437140</v>
+        <v>437074</v>
       </c>
       <c r="R100" t="n">
-        <v>6763931</v>
+        <v>6763890</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11328,7 +11332,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127293586</v>
+        <v>127290978</v>
       </c>
       <c r="B101" t="n">
         <v>79020</v>
@@ -11359,17 +11363,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437163</v>
+        <v>437098</v>
       </c>
       <c r="R101" t="n">
-        <v>6763902</v>
+        <v>6763850</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11398,7 +11402,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11408,7 +11412,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11423,69 +11427,65 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127293953</v>
+        <v>127295309</v>
       </c>
       <c r="B102" t="n">
-        <v>91352</v>
+        <v>58033</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437190</v>
+        <v>437289</v>
       </c>
       <c r="R102" t="n">
-        <v>6763937</v>
+        <v>6763874</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,12 +11539,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11663,32 +11663,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127292751</v>
+        <v>127293475</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436974</v>
+        <v>437136</v>
       </c>
       <c r="R104" t="n">
-        <v>6763823</v>
+        <v>6763963</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11770,45 +11770,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127294008</v>
+        <v>127294074</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>437190</v>
+        <v>437189</v>
       </c>
       <c r="R105" t="n">
-        <v>6763955</v>
+        <v>6763951</v>
       </c>
       <c r="S105" t="n">
         <v>9</v>
@@ -11840,7 +11845,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11850,7 +11855,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11877,50 +11882,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127294074</v>
+        <v>127294008</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>437189</v>
+        <v>437190</v>
       </c>
       <c r="R106" t="n">
-        <v>6763951</v>
+        <v>6763955</v>
       </c>
       <c r="S106" t="n">
         <v>9</v>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11989,32 +11989,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127293475</v>
+        <v>127292751</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>437136</v>
+        <v>436974</v>
       </c>
       <c r="R107" t="n">
-        <v>6763963</v>
+        <v>6763823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12096,32 +12096,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127290265</v>
+        <v>127291177</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437187</v>
+        <v>437081</v>
       </c>
       <c r="R108" t="n">
-        <v>6763801</v>
+        <v>6763837</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12203,48 +12203,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127294388</v>
+        <v>127293290</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437183</v>
+        <v>437138</v>
       </c>
       <c r="R109" t="n">
-        <v>6764033</v>
+        <v>6763901</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12283,7 +12283,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Fyra synliga tickor</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12298,19 +12303,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127292727</v>
+        <v>127294388</v>
       </c>
       <c r="B110" t="n">
         <v>8450</v>
@@ -12339,21 +12344,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437043</v>
+        <v>437183</v>
       </c>
       <c r="R110" t="n">
-        <v>6763856</v>
+        <v>6764033</v>
       </c>
       <c r="S110" t="n">
         <v>9</v>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12422,48 +12422,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127293290</v>
+        <v>127292727</v>
       </c>
       <c r="B111" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437138</v>
+        <v>437043</v>
       </c>
       <c r="R111" t="n">
-        <v>6763901</v>
+        <v>6763856</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12492,7 +12497,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12502,12 +12507,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Fyra synliga tickor</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12522,44 +12522,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127291177</v>
+        <v>127290265</v>
       </c>
       <c r="B112" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437081</v>
+        <v>437187</v>
       </c>
       <c r="R112" t="n">
-        <v>6763837</v>
+        <v>6763801</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12641,48 +12641,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127293766</v>
+        <v>127293262</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437187</v>
+        <v>437131</v>
       </c>
       <c r="R113" t="n">
-        <v>6763964</v>
+        <v>6763892</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12736,22 +12736,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127293240</v>
+        <v>127290747</v>
       </c>
       <c r="B114" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12759,37 +12759,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>437122</v>
+        <v>437064</v>
       </c>
       <c r="R114" t="n">
-        <v>6763905</v>
+        <v>6763744</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12843,22 +12843,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127291635</v>
+        <v>127293240</v>
       </c>
       <c r="B115" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12866,21 +12866,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437032</v>
+        <v>437122</v>
       </c>
       <c r="R115" t="n">
-        <v>6763776</v>
+        <v>6763905</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13069,7 +13069,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127293262</v>
+        <v>127291635</v>
       </c>
       <c r="B117" t="n">
         <v>79020</v>
@@ -13100,17 +13100,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437131</v>
+        <v>437032</v>
       </c>
       <c r="R117" t="n">
-        <v>6763892</v>
+        <v>6763776</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13164,60 +13164,60 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127290747</v>
+        <v>127293766</v>
       </c>
       <c r="B118" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>437064</v>
+        <v>437187</v>
       </c>
       <c r="R118" t="n">
-        <v>6763744</v>
+        <v>6763964</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13271,19 +13271,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127293427</v>
+        <v>127291536</v>
       </c>
       <c r="B119" t="n">
         <v>79020</v>
@@ -13314,17 +13314,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>437147</v>
+        <v>436972</v>
       </c>
       <c r="R119" t="n">
-        <v>6763942</v>
+        <v>6763733</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13378,19 +13378,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127293635</v>
+        <v>127293427</v>
       </c>
       <c r="B120" t="n">
         <v>79020</v>
@@ -13425,10 +13425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437130</v>
+        <v>437147</v>
       </c>
       <c r="R120" t="n">
-        <v>6763988</v>
+        <v>6763942</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13497,7 +13497,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127291536</v>
+        <v>127293635</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -13528,17 +13528,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436972</v>
+        <v>437130</v>
       </c>
       <c r="R121" t="n">
-        <v>6763733</v>
+        <v>6763988</v>
       </c>
       <c r="S121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13592,12 +13592,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13935,53 +13935,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127293007</v>
+        <v>127295889</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437076</v>
+        <v>437244</v>
       </c>
       <c r="R125" t="n">
-        <v>6763849</v>
+        <v>6763890</v>
       </c>
       <c r="S125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14020,12 +14020,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Två torrtallar</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14040,57 +14035,62 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127290736</v>
+        <v>127292816</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>437102</v>
+        <v>436992</v>
       </c>
       <c r="R126" t="n">
-        <v>6763801</v>
+        <v>6763834</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14271,53 +14271,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127295889</v>
+        <v>127293007</v>
       </c>
       <c r="B128" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437244</v>
+        <v>437076</v>
       </c>
       <c r="R128" t="n">
-        <v>6763890</v>
+        <v>6763849</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14356,7 +14356,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Två torrtallar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14371,62 +14376,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127292816</v>
+        <v>127290736</v>
       </c>
       <c r="B129" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436992</v>
+        <v>437102</v>
       </c>
       <c r="R129" t="n">
-        <v>6763834</v>
+        <v>6763801</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14495,32 +14495,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127293270</v>
+        <v>127293305</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437124</v>
+        <v>437137</v>
       </c>
       <c r="R130" t="n">
         <v>6763885</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14602,32 +14602,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127295217</v>
+        <v>127294311</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437312</v>
+        <v>437170</v>
       </c>
       <c r="R131" t="n">
-        <v>6763984</v>
+        <v>6764043</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14683,6 +14683,11 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Garnlav på flera träd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14709,32 +14714,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127295386</v>
+        <v>127292761</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14744,10 +14749,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437233</v>
+        <v>436992</v>
       </c>
       <c r="R132" t="n">
-        <v>6763867</v>
+        <v>6763834</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14816,7 +14821,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127294021</v>
+        <v>127293270</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -14851,10 +14856,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437191</v>
+        <v>437124</v>
       </c>
       <c r="R133" t="n">
-        <v>6763952</v>
+        <v>6763885</v>
       </c>
       <c r="S133" t="n">
         <v>9</v>
@@ -14886,7 +14891,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14896,7 +14901,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14923,48 +14928,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127293305</v>
+        <v>127295217</v>
       </c>
       <c r="B134" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437137</v>
+        <v>437312</v>
       </c>
       <c r="R134" t="n">
-        <v>6763885</v>
+        <v>6763984</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14993,7 +14998,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15003,7 +15008,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15018,44 +15023,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127292761</v>
+        <v>127295386</v>
       </c>
       <c r="B135" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15065,10 +15070,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436992</v>
+        <v>437233</v>
       </c>
       <c r="R135" t="n">
-        <v>6763834</v>
+        <v>6763867</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15137,48 +15142,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127294311</v>
+        <v>127294021</v>
       </c>
       <c r="B136" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437170</v>
+        <v>437191</v>
       </c>
       <c r="R136" t="n">
-        <v>6764043</v>
+        <v>6763952</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15207,7 +15212,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15217,12 +15222,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flera träd</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15237,12 +15237,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -15252,7 +15252,7 @@
         <v>127295725</v>
       </c>
       <c r="B137" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 30904-2025 artfynd.xlsx
+++ b/artfynd/A 30904-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295923</v>
+        <v>127291489</v>
       </c>
       <c r="B2" t="n">
-        <v>91371</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437244</v>
+        <v>437044</v>
       </c>
       <c r="R2" t="n">
-        <v>6763901</v>
+        <v>6763790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295759</v>
+        <v>127290437</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437218</v>
+        <v>437157</v>
       </c>
       <c r="R3" t="n">
-        <v>6763878</v>
+        <v>6763806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127293774</v>
+        <v>127295759</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437187</v>
+        <v>437218</v>
       </c>
       <c r="R4" t="n">
-        <v>6763964</v>
+        <v>6763878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294146</v>
+        <v>127295923</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437131</v>
+        <v>437244</v>
       </c>
       <c r="R5" t="n">
-        <v>6764010</v>
+        <v>6763901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
         <v>127294422</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,48 +1210,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127291489</v>
+        <v>127295019</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437044</v>
+        <v>437299</v>
       </c>
       <c r="R7" t="n">
-        <v>6763790</v>
+        <v>6763962</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,60 +1310,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127290437</v>
+        <v>127293337</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437157</v>
+        <v>437130</v>
       </c>
       <c r="R8" t="n">
-        <v>6763806</v>
+        <v>6763889</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,12 +1422,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1427,7 +1437,7 @@
         <v>127295045</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,53 +1541,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295019</v>
+        <v>127293774</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437299</v>
+        <v>437187</v>
       </c>
       <c r="R10" t="n">
-        <v>6763962</v>
+        <v>6763964</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,65 +1636,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127293337</v>
+        <v>127294146</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437130</v>
+        <v>437131</v>
       </c>
       <c r="R11" t="n">
-        <v>6763889</v>
+        <v>6764010</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294728</v>
+        <v>127294041</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437204</v>
+        <v>437152</v>
       </c>
       <c r="R12" t="n">
-        <v>6764046</v>
+        <v>6764014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294354</v>
+        <v>127294721</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437188</v>
+        <v>437204</v>
       </c>
       <c r="R13" t="n">
-        <v>6764029</v>
+        <v>6764046</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +1957,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127291056</v>
+        <v>127294738</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437040</v>
+        <v>437220</v>
       </c>
       <c r="R14" t="n">
-        <v>6763751</v>
+        <v>6764061</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,22 +2064,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127294041</v>
+        <v>127294354</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,17 +2107,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437152</v>
+        <v>437188</v>
       </c>
       <c r="R15" t="n">
-        <v>6764014</v>
+        <v>6764029</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,22 +2171,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127294738</v>
+        <v>127291056</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,17 +2214,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437220</v>
+        <v>437040</v>
       </c>
       <c r="R16" t="n">
-        <v>6764061</v>
+        <v>6763751</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,22 +2278,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127293263</v>
+        <v>127291525</v>
       </c>
       <c r="B17" t="n">
-        <v>91371</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437138</v>
+        <v>437044</v>
       </c>
       <c r="R17" t="n">
-        <v>6763887</v>
+        <v>6763790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127293099</v>
+        <v>127293263</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>91339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437109</v>
+        <v>437138</v>
       </c>
       <c r="R18" t="n">
-        <v>6763908</v>
+        <v>6763887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127291525</v>
+        <v>127293099</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437044</v>
+        <v>437109</v>
       </c>
       <c r="R19" t="n">
-        <v>6763790</v>
+        <v>6763908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>127294351</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,48 +2718,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295941</v>
+        <v>127295240</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437223</v>
+        <v>437308</v>
       </c>
       <c r="R21" t="n">
-        <v>6763922</v>
+        <v>6763966</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>127290331</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,48 +2932,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295240</v>
+        <v>127295941</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437308</v>
+        <v>437223</v>
       </c>
       <c r="R23" t="n">
-        <v>6763966</v>
+        <v>6763922</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,22 +3027,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127293735</v>
+        <v>127293820</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,34 +3050,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437156</v>
+        <v>437201</v>
       </c>
       <c r="R24" t="n">
-        <v>6763978</v>
+        <v>6763976</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,48 +3151,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295078</v>
+        <v>127292736</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437293</v>
+        <v>436991</v>
       </c>
       <c r="R25" t="n">
-        <v>6763940</v>
+        <v>6763816</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,22 +3246,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294346</v>
+        <v>127293735</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3284,17 +3289,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437187</v>
+        <v>437156</v>
       </c>
       <c r="R26" t="n">
-        <v>6764029</v>
+        <v>6763978</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3323,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,22 +3353,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127293241</v>
+        <v>127293161</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,24 +3394,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437135</v>
+        <v>437098</v>
       </c>
       <c r="R27" t="n">
-        <v>6763885</v>
+        <v>6763941</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,22 +3460,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127293161</v>
+        <v>127293241</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3501,19 +3501,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437098</v>
+        <v>437135</v>
       </c>
       <c r="R28" t="n">
-        <v>6763941</v>
+        <v>6763885</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,60 +3572,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127292736</v>
+        <v>127295078</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436991</v>
+        <v>437293</v>
       </c>
       <c r="R29" t="n">
-        <v>6763816</v>
+        <v>6763940</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3649,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,22 +3679,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127293820</v>
+        <v>127295384</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3717,7 +3722,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3726,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437201</v>
+        <v>437233</v>
       </c>
       <c r="R30" t="n">
-        <v>6763976</v>
+        <v>6763867</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295384</v>
+        <v>127294346</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,42 +3814,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437233</v>
+        <v>437187</v>
       </c>
       <c r="R31" t="n">
-        <v>6763867</v>
+        <v>6764029</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,12 +3898,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
         <v>127293914</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>127293203</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295057</v>
+        <v>127293696</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4155,17 +4155,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437295</v>
+        <v>437156</v>
       </c>
       <c r="R34" t="n">
-        <v>6763942</v>
+        <v>6763982</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,22 +4219,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127293696</v>
+        <v>127293981</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437156</v>
+        <v>437177</v>
       </c>
       <c r="R35" t="n">
-        <v>6763982</v>
+        <v>6764017</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,48 +4338,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127293981</v>
+        <v>127294136</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437177</v>
+        <v>437182</v>
       </c>
       <c r="R36" t="n">
-        <v>6764017</v>
+        <v>6763976</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4418,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,62 +4438,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294136</v>
+        <v>127295057</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437182</v>
+        <v>437295</v>
       </c>
       <c r="R37" t="n">
-        <v>6763976</v>
+        <v>6763942</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,32 +4557,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127293212</v>
+        <v>127291424</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437120</v>
+        <v>437058</v>
       </c>
       <c r="R38" t="n">
-        <v>6763919</v>
+        <v>6763796</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294037</v>
+        <v>127293212</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4695,17 +4695,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437188</v>
+        <v>437120</v>
       </c>
       <c r="R39" t="n">
-        <v>6763952</v>
+        <v>6763919</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,22 +4759,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295245</v>
+        <v>127292669</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437308</v>
+        <v>437023</v>
       </c>
       <c r="R40" t="n">
-        <v>6763966</v>
+        <v>6763818</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127292954</v>
+        <v>127295245</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,17 +4909,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437050</v>
+        <v>437308</v>
       </c>
       <c r="R41" t="n">
-        <v>6763860</v>
+        <v>6763966</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,22 +4973,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127292669</v>
+        <v>127292954</v>
       </c>
       <c r="B42" t="n">
-        <v>79647</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4996,37 +4996,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437023</v>
+        <v>437050</v>
       </c>
       <c r="R42" t="n">
-        <v>6763818</v>
+        <v>6763860</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,12 +5080,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
         <v>127290586</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5199,48 +5199,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127291424</v>
+        <v>127294037</v>
       </c>
       <c r="B44" t="n">
-        <v>79647</v>
+        <v>8447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437058</v>
+        <v>437188</v>
       </c>
       <c r="R44" t="n">
-        <v>6763796</v>
+        <v>6763952</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,22 +5294,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127292927</v>
+        <v>127291031</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437032</v>
+        <v>437097</v>
       </c>
       <c r="R45" t="n">
-        <v>6763858</v>
+        <v>6763850</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127294741</v>
+        <v>127293956</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5444,17 +5444,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437209</v>
+        <v>437202</v>
       </c>
       <c r="R46" t="n">
-        <v>6764061</v>
+        <v>6764007</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5508,22 +5508,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127292980</v>
+        <v>127292927</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,17 +5551,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437068</v>
+        <v>437032</v>
       </c>
       <c r="R47" t="n">
         <v>6763858</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,44 +5615,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127293956</v>
+        <v>127290540</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437202</v>
+        <v>437113</v>
       </c>
       <c r="R48" t="n">
-        <v>6764007</v>
+        <v>6763817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127291031</v>
+        <v>127290803</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>57654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,34 +5745,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437097</v>
+        <v>437091</v>
       </c>
       <c r="R49" t="n">
-        <v>6763850</v>
+        <v>6763822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295897</v>
+        <v>127294741</v>
       </c>
       <c r="B50" t="n">
-        <v>91371</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,37 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437244</v>
+        <v>437209</v>
       </c>
       <c r="R50" t="n">
-        <v>6763890</v>
+        <v>6764061</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5911,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5921,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5936,22 +5941,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127290803</v>
+        <v>127292980</v>
       </c>
       <c r="B51" t="n">
-        <v>57669</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5959,42 +5964,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437091</v>
+        <v>437068</v>
       </c>
       <c r="R51" t="n">
-        <v>6763822</v>
+        <v>6763858</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6048,44 +6048,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127290540</v>
+        <v>127295897</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>91339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437113</v>
+        <v>437244</v>
       </c>
       <c r="R52" t="n">
-        <v>6763817</v>
+        <v>6763890</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
         <v>127294782</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6274,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127291397</v>
+        <v>127293209</v>
       </c>
       <c r="B54" t="n">
-        <v>91371</v>
+        <v>8447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437058</v>
+        <v>437116</v>
       </c>
       <c r="R54" t="n">
-        <v>6763796</v>
+        <v>6763949</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6381,32 +6381,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127293209</v>
+        <v>127291397</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>91339</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437116</v>
+        <v>437058</v>
       </c>
       <c r="R55" t="n">
-        <v>6763949</v>
+        <v>6763796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,10 +6488,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127290094</v>
+        <v>127290996</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6523,13 +6523,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437239</v>
+        <v>437108</v>
       </c>
       <c r="R56" t="n">
-        <v>6763818</v>
+        <v>6763849</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6569,11 +6569,6 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6600,10 +6595,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127290996</v>
+        <v>127290094</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6635,13 +6630,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437108</v>
+        <v>437239</v>
       </c>
       <c r="R57" t="n">
-        <v>6763849</v>
+        <v>6763818</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6681,6 +6676,11 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild på äldre tallar samt garnlav</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6707,10 +6707,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127294772</v>
+        <v>127291537</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79600</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6718,37 +6718,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437255</v>
+        <v>437044</v>
       </c>
       <c r="R58" t="n">
-        <v>6764049</v>
+        <v>6763790</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,60 +6802,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127294736</v>
+        <v>127293858</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437212</v>
+        <v>437201</v>
       </c>
       <c r="R59" t="n">
-        <v>6764065</v>
+        <v>6763976</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6909,22 +6909,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127294411</v>
+        <v>127293072</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>91339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6932,37 +6932,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437202</v>
+        <v>437081</v>
       </c>
       <c r="R60" t="n">
-        <v>6764041</v>
+        <v>6763901</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7016,22 +7016,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127295806</v>
+        <v>127294416</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7059,17 +7059,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fagerlok, Fagerlok, Dlr</t>
+          <t>Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437212</v>
+        <v>437158</v>
       </c>
       <c r="R61" t="n">
-        <v>6763955</v>
+        <v>6764069</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7123,60 +7123,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127293858</v>
+        <v>127294772</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagerlok, Dlr</t>
+          <t>Fagerlok, Fagerlok, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437201</v>
+        <v>437255</v>
       </c>
       <c r="R62" t="n">
-        <v>6763976</v>
+        <v>6764049</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7230,62 +7230,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127290454</v>
+        <v>127294736</v>
       </c>
       <c r="B63" t="n">
-        <v>84